--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="240">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -750,6 +750,27 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1331-064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REY S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0887-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1334-066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0000-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1333-303</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1070,7 +1091,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1142,9 +1163,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -1659,67 +1677,128 @@
       <x:c r="N6" s="7" t="s"/>
       <x:c r="O6" s="9" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
+      <x:c r="B7" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H7" s="12">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I7" s="13">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="21" t="s">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I8" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K8" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C9" s="22" t="s"/>
-      <x:c r="D9" s="22" t="s"/>
-      <x:c r="E9" s="23" t="s"/>
-      <x:c r="F9" s="23" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="24" t="s">
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="23" t="s"/>
+      <x:c r="F11" s="23" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="24" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C10" s="25" t="s"/>
-      <x:c r="D10" s="25" t="s"/>
-      <x:c r="E10" s="25" t="s"/>
-      <x:c r="F10" s="26" t="s">
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="28" t="s"/>
-      <x:c r="D11" s="28" t="s"/>
-      <x:c r="E11" s="28" t="s"/>
-      <x:c r="F11" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="C13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="28" t="s"/>
+      <x:c r="F13" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C12" s="31" t="s"/>
-      <x:c r="D12" s="31" t="s"/>
-      <x:c r="E12" s="31" t="s"/>
-      <x:c r="F12" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C14" s="31" t="s"/>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="31" t="s"/>
+      <x:c r="F14" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2703,10 +2782,10 @@
   <x:mergeCells count="6">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -740,6 +740,27 @@
     <x:t>61-2-2026-1319-115</x:t>
   </x:si>
   <x:si>
+    <x:t>AL S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FB-0878-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1354-796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0877-18(ren)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1340-327</x:t>
+  </x:si>
+  <x:si>
     <x:t>JUDELYN B. AMANIA</x:t>
   </x:si>
   <x:si>
@@ -752,10 +773,67 @@
     <x:t>61-2-2026-1331-064</x:t>
   </x:si>
   <x:si>
+    <x:t>LUCERO R. ALBARACIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Balintawak, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1307-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1352-743</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REMEGIO T. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0884-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1364-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0879-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1344-597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0880-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1343-619</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REMEGIO T. BURBURAN JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS-4878-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1362-288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk.daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0881-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1342-435</x:t>
+  </x:si>
+  <x:si>
     <x:t>REY S. BURBURAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
     <x:t>MS9/FV-0887-18</x:t>
@@ -1657,19 +1735,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I6" s="13">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K6" s="14" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>19</x:v>
@@ -1683,34 +1761,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>243</x:v>
-      </x:c>
       <x:c r="H7" s="12">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0333449074</x:v>
       </x:c>
       <x:c r="I7" s="13">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216156</x:v>
       </x:c>
       <x:c r="K7" s="14" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2584837963</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>19</x:v>
@@ -1722,7 +1800,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D8" s="16" t="s">
         <x:v>15</x:v>
@@ -1737,76 +1815,372 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I8" s="18">
-        <x:v>46058</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C9" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46076.1139583333</x:v>
+      </x:c>
+      <x:c r="I9" s="18">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="n">
+        <x:v>1216146</x:v>
+      </x:c>
+      <x:c r="K9" s="19" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>46090.1919444444</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46077.2598726852</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="n">
+        <x:v>1216158</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>46090.2758680556</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46072.1089467593</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1216152</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L11" s="20">
+        <x:v>46090.2365046296</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46072.0792939815</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1216150</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>46090.220787037</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46077.2024189815</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1216154</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="20">
+        <x:v>46090.2495949074</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46072.0497337963</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1216148</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>46090.2102430556</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I16" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="23" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C22" s="31" t="s"/>
+      <x:c r="D22" s="31" t="s"/>
+      <x:c r="E22" s="31" t="s"/>
+      <x:c r="F22" s="32" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2782,10 +3156,10 @@
   <x:mergeCells count="6">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B19:F19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -816,6 +816,24 @@
   </x:si>
   <x:si>
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK DAISY 2, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0882-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1369-049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1077-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1367-348</x:t>
   </x:si>
   <x:si>
     <x:t>MS-4878-23</x:t>
@@ -1996,28 +2014,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="15" t="s">
-        <x:v>258</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F13" s="15" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G13" s="15" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I13" s="18">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>19</x:v>
@@ -2034,28 +2052,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F14" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I14" s="18">
-        <x:v>46058</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>19</x:v>
@@ -2066,7 +2084,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>267</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
@@ -2081,19 +2099,19 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>19</x:v>
@@ -2104,7 +2122,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
-        <x:v>267</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
@@ -2119,70 +2137,144 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I16" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="23" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="24" t="s">
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="23" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="24" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="s">
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="30" t="s">
+      <x:c r="C23" s="28" t="s"/>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="28" t="s"/>
+      <x:c r="F23" s="29" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C22" s="31" t="s"/>
-      <x:c r="D22" s="31" t="s"/>
-      <x:c r="E22" s="31" t="s"/>
-      <x:c r="F22" s="32" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="31" t="s"/>
+      <x:c r="D24" s="31" t="s"/>
+      <x:c r="E24" s="31" t="s"/>
+      <x:c r="F24" s="32" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3156,10 +3248,10 @@
   <x:mergeCells count="6">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B21:F21"/>
     <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="283">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -759,6 +759,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1340-327</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FEY S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0886-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1332-813</x:t>
   </x:si>
   <x:si>
     <x:t>JUDELYN B. AMANIA</x:t>
@@ -1833,19 +1845,19 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46070.1768402778</x:v>
+        <x:v>46071.1677662037</x:v>
       </x:c>
       <x:c r="I8" s="18">
-        <x:v>46123</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1216138</x:v>
+        <x:v>1216165</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>46084.1495138889</x:v>
+        <x:v>46091.1948842593</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>19</x:v>
@@ -1871,19 +1883,19 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46070.1768402778</x:v>
       </x:c>
       <x:c r="I9" s="18">
-        <x:v>46084</x:v>
+        <x:v>46123</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216138</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46084.1495138889</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>19</x:v>
@@ -1909,19 +1921,19 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I10" s="18">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>19</x:v>
@@ -1932,34 +1944,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>251</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="F11" s="15" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G11" s="15" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I11" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>19</x:v>
@@ -1970,34 +1982,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
-        <x:v>251</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="15" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F12" s="15" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G12" s="15" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I12" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>19</x:v>
@@ -2008,7 +2020,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D13" s="16" t="s">
         <x:v>15</x:v>
@@ -2023,19 +2035,19 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I13" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>19</x:v>
@@ -2046,34 +2058,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F14" s="15" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I14" s="18">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>19</x:v>
@@ -2084,34 +2096,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="15" t="s">
-        <x:v>258</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="F15" s="15" t="s">
-        <x:v>268</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G15" s="15" t="s">
-        <x:v>269</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>45948</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>19</x:v>
@@ -2122,34 +2134,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
-        <x:v>270</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F16" s="15" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>19</x:v>
@@ -2160,34 +2172,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>273</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>258</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="F17" s="15" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="G17" s="15" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I17" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>19</x:v>
@@ -2198,84 +2210,121 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>273</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D18" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>276</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F18" s="15" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G18" s="15" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I18" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="23" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="24" t="s">
+      <x:c r="C22" s="22" t="s"/>
+      <x:c r="D22" s="22" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="23" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B23" s="24" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="s">
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="27" t="s">
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="28" t="s"/>
-      <x:c r="D23" s="28" t="s"/>
-      <x:c r="E23" s="28" t="s"/>
-      <x:c r="F23" s="29" t="n">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="30" t="s">
+      <x:c r="C24" s="28" t="s"/>
+      <x:c r="D24" s="28" t="s"/>
+      <x:c r="E24" s="28" t="s"/>
+      <x:c r="F24" s="29" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B25" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C24" s="31" t="s"/>
-      <x:c r="D24" s="31" t="s"/>
-      <x:c r="E24" s="31" t="s"/>
-      <x:c r="F24" s="32" t="n">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C25" s="31" t="s"/>
+      <x:c r="D25" s="31" t="s"/>
+      <x:c r="E25" s="31" t="s"/>
+      <x:c r="F25" s="32" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3248,10 +3297,10 @@
   <x:mergeCells count="6">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B21:F21"/>
-    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B22:F22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="283">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -879,6 +879,21 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1333-303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zone 9, tiguma, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1281-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1372-847</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1283-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-11-2025-1252-294</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2281,52 +2296,126 @@
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="21" t="s">
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46079.0151851852</x:v>
+      </x:c>
+      <x:c r="I20" s="18">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1216174</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>46093.1514351852</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1216173</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>46093.1383912037</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="23" t="s"/>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="24" t="s">
+      <x:c r="C24" s="22" t="s"/>
+      <x:c r="D24" s="22" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="23" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="24" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="s">
+      <x:c r="C25" s="25" t="s"/>
+      <x:c r="D25" s="25" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="26" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="27" t="s">
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C24" s="28" t="s"/>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="28" t="s"/>
-      <x:c r="F24" s="29" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="30" t="s">
+      <x:c r="C26" s="28" t="s"/>
+      <x:c r="D26" s="28" t="s"/>
+      <x:c r="E26" s="28" t="s"/>
+      <x:c r="F26" s="29" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C25" s="31" t="s"/>
-      <x:c r="D25" s="31" t="s"/>
-      <x:c r="E25" s="31" t="s"/>
-      <x:c r="F25" s="32" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C27" s="31" t="s"/>
+      <x:c r="D27" s="31" t="s"/>
+      <x:c r="E27" s="31" t="s"/>
+      <x:c r="F27" s="32" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3297,10 +3386,10 @@
   <x:mergeCells count="6">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B24:F24"/>
     <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -795,6 +795,15 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1352-743</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRK. KAMANGGAHAN, CURVADA, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1006-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1337-307</x:t>
   </x:si>
   <x:si>
     <x:t>REMEGIO T. BURBURAN</x:t>
@@ -1959,34 +1968,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>255</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>258</x:v>
-      </x:c>
       <x:c r="H11" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46071.3305671296</x:v>
       </x:c>
       <x:c r="I11" s="18">
-        <x:v>46058</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J11" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216193</x:v>
       </x:c>
       <x:c r="K11" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L11" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46094.1906365741</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>19</x:v>
@@ -1997,7 +2006,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
         <x:v>15</x:v>
@@ -2012,19 +2021,19 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I12" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>19</x:v>
@@ -2035,7 +2044,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D13" s="16" t="s">
         <x:v>15</x:v>
@@ -2050,19 +2059,19 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I13" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>19</x:v>
@@ -2073,34 +2082,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>268</x:v>
-      </x:c>
       <x:c r="H14" s="17">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I14" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>19</x:v>
@@ -2111,7 +2120,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D15" s="16" t="s">
         <x:v>15</x:v>
@@ -2126,19 +2135,19 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="H15" s="17">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I15" s="18">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J15" s="16" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L15" s="20">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M15" s="15" t="s">
         <x:v>19</x:v>
@@ -2149,34 +2158,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="15" t="s">
-        <x:v>262</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="F16" s="15" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G16" s="15" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="H16" s="17">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I16" s="18">
-        <x:v>45948</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J16" s="16" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L16" s="20">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M16" s="15" t="s">
         <x:v>19</x:v>
@@ -2187,13 +2196,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D17" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>274</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F17" s="15" t="s">
         <x:v>275</x:v>
@@ -2202,19 +2211,19 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="H17" s="17">
-        <x:v>46072.0497337963</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I17" s="18">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J17" s="16" t="n">
-        <x:v>1216148</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K17" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L17" s="20">
-        <x:v>46090.2102430556</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M17" s="15" t="s">
         <x:v>19</x:v>
@@ -2225,13 +2234,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C18" s="15" t="s">
-        <x:v>277</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D18" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="s">
-        <x:v>262</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="F18" s="15" t="s">
         <x:v>278</x:v>
@@ -2240,19 +2249,19 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H18" s="17">
-        <x:v>46071.2285416667</x:v>
+        <x:v>46072.0497337963</x:v>
       </x:c>
       <x:c r="I18" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J18" s="16" t="n">
-        <x:v>1216143</x:v>
+        <x:v>1216148</x:v>
       </x:c>
       <x:c r="K18" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L18" s="20">
-        <x:v>46090.0772916667</x:v>
+        <x:v>46090.2102430556</x:v>
       </x:c>
       <x:c r="M18" s="15" t="s">
         <x:v>19</x:v>
@@ -2263,13 +2272,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="15" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D19" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>280</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F19" s="15" t="s">
         <x:v>281</x:v>
@@ -2278,19 +2287,19 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="H19" s="17">
-        <x:v>46071.2072569444</x:v>
+        <x:v>46071.2285416667</x:v>
       </x:c>
       <x:c r="I19" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J19" s="16" t="n">
-        <x:v>1216142</x:v>
+        <x:v>1216143</x:v>
       </x:c>
       <x:c r="K19" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L19" s="20">
-        <x:v>46090.0616666667</x:v>
+        <x:v>46090.0772916667</x:v>
       </x:c>
       <x:c r="M19" s="15" t="s">
         <x:v>19</x:v>
@@ -2301,7 +2310,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C20" s="15" t="s">
-        <x:v>134</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D20" s="16" t="s">
         <x:v>15</x:v>
@@ -2316,19 +2325,19 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="H20" s="17">
-        <x:v>46079.0151851852</x:v>
+        <x:v>46071.2072569444</x:v>
       </x:c>
       <x:c r="I20" s="18">
-        <x:v>45602</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J20" s="16" t="n">
-        <x:v>1216174</x:v>
+        <x:v>1216142</x:v>
       </x:c>
       <x:c r="K20" s="19" t="n">
-        <x:v>3990</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L20" s="20">
-        <x:v>46093.1514351852</x:v>
+        <x:v>46090.0616666667</x:v>
       </x:c>
       <x:c r="M20" s="15" t="s">
         <x:v>19</x:v>
@@ -2345,78 +2354,115 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="15" t="s">
-        <x:v>135</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="F21" s="15" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="G21" s="15" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H21" s="17">
-        <x:v>45988.1893402778</x:v>
+        <x:v>46079.0151851852</x:v>
       </x:c>
       <x:c r="I21" s="18">
-        <x:v>45973</x:v>
+        <x:v>45602</x:v>
       </x:c>
       <x:c r="J21" s="16" t="n">
-        <x:v>1216173</x:v>
+        <x:v>1216174</x:v>
       </x:c>
       <x:c r="K21" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>3990</x:v>
       </x:c>
       <x:c r="L21" s="20">
-        <x:v>46093.1383912037</x:v>
+        <x:v>46093.1514351852</x:v>
       </x:c>
       <x:c r="M21" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I22" s="18">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1216173</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L22" s="20">
+        <x:v>46093.1383912037</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="21" t="s">
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C24" s="22" t="s"/>
-      <x:c r="D24" s="22" t="s"/>
-      <x:c r="E24" s="23" t="s"/>
-      <x:c r="F24" s="23" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="24" t="s">
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="23" t="s"/>
+      <x:c r="F25" s="23" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="24" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C25" s="25" t="s"/>
-      <x:c r="D25" s="25" t="s"/>
-      <x:c r="E25" s="25" t="s"/>
-      <x:c r="F25" s="26" t="s">
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="27" t="s">
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C26" s="28" t="s"/>
-      <x:c r="D26" s="28" t="s"/>
-      <x:c r="E26" s="28" t="s"/>
-      <x:c r="F26" s="29" t="n">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="30" t="s">
+      <x:c r="C27" s="28" t="s"/>
+      <x:c r="D27" s="28" t="s"/>
+      <x:c r="E27" s="28" t="s"/>
+      <x:c r="F27" s="29" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B28" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C27" s="31" t="s"/>
-      <x:c r="D27" s="31" t="s"/>
-      <x:c r="E27" s="31" t="s"/>
-      <x:c r="F27" s="32" t="n">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C28" s="31" t="s"/>
+      <x:c r="D28" s="31" t="s"/>
+      <x:c r="E28" s="31" t="s"/>
+      <x:c r="F28" s="32" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3386,10 +3432,10 @@
   <x:mergeCells count="6">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B24:F24"/>
-    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -146,6 +146,51 @@
     <x:t>Neil Jon Angeles</x:t>
   </x:si>
   <x:si>
+    <x:t>Radio Station License (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENSHIN SALES AND SERVICES OPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GONZALEZ ST. CORNER GEN. LUNA, CENTRAL, Dipolog City (Capital), Zamboanga Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RSL-ROIX-01116-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alexander Tomales</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Station License (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GODOFREDO M. LIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zone II, La Purisima, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RPTR-II-00018-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THUNDER BRAVO NETWORK, INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lanote Bliss, City Of Isabela, City Of Isabela</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FB-II-00041-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1140</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radio Station License - WDN (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -161,51 +206,6 @@
     <x:t>61-8-2025-1114</x:t>
   </x:si>
   <x:si>
-    <x:t>Radio Station License (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENSHIN SALES AND SERVICES OPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GONZALEZ ST. CORNER GEN. LUNA, CENTRAL, Dipolog City (Capital), Zamboanga Del Norte</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RSL-ROIX-01116-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alexander Tomales</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Radio Station License (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GODOFREDO M. LIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Zone II, La Purisima, Zamboanga City, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RPTR-II-00018-01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THUNDER BRAVO NETWORK, INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lanote Bliss, City Of Isabela, City Of Isabela</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FB-II-00041-19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1140</x:t>
-  </x:si>
-  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (MODIFICATION)</x:t>
   </x:si>
   <x:si>
@@ -809,6 +809,15 @@
     <x:t>REMEGIO T. BURBURAN</x:t>
   </x:si>
   <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0880-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1343-619</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -825,15 +834,6 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1344-597</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-0880-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1343-619</x:t>
   </x:si>
   <x:si>
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
@@ -2021,19 +2021,19 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46072.0792939815</x:v>
       </x:c>
       <x:c r="I12" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J12" s="16" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216150</x:v>
       </x:c>
       <x:c r="K12" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="20">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.220787037</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>19</x:v>
@@ -2059,19 +2059,19 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46072.1089467593</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I13" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J13" s="16" t="n">
-        <x:v>1216152</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="20">
-        <x:v>46090.2365046296</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>19</x:v>
@@ -2097,19 +2097,19 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46072.0792939815</x:v>
+        <x:v>46072.1089467593</x:v>
       </x:c>
       <x:c r="I14" s="18">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J14" s="16" t="n">
-        <x:v>1216150</x:v>
+        <x:v>1216152</x:v>
       </x:c>
       <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="20">
-        <x:v>46090.220787037</x:v>
+        <x:v>46090.2365046296</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>19</x:v>
@@ -2202,7 +2202,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F17" s="15" t="s">
         <x:v>275</x:v>
@@ -2278,7 +2278,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F19" s="15" t="s">
         <x:v>281</x:v>
@@ -4960,7 +4960,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>40</x:v>
@@ -4972,96 +4972,96 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>45881.3064236111</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45871</x:v>
+        <x:v>45882.0658796296</x:v>
+      </x:c>
+      <x:c r="I7" s="12">
+        <x:v>45882.0658912037</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1195693</x:v>
+        <x:v>1195701</x:v>
       </x:c>
       <x:c r="K7" s="14" t="n">
-        <x:v>4275</x:v>
+        <x:v>2496</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>45897.0449189815</x:v>
+        <x:v>45883.2549537037</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="15" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D8" s="16" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="15" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F8" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G8" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>45882.0658796296</x:v>
-      </x:c>
-      <x:c r="I8" s="17">
-        <x:v>45882.0658912037</x:v>
+        <x:v>45881.0630902778</x:v>
+      </x:c>
+      <x:c r="I8" s="18">
+        <x:v>45885</x:v>
       </x:c>
       <x:c r="J8" s="16" t="n">
-        <x:v>1195701</x:v>
+        <x:v>1346453</x:v>
       </x:c>
       <x:c r="K8" s="19" t="n">
-        <x:v>2496</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L8" s="20">
-        <x:v>45883.2549537037</x:v>
+        <x:v>45881.0887037037</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="D9" s="16" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="H9" s="17">
-        <x:v>45881.0630902778</x:v>
+        <x:v>45897.2535648148</x:v>
       </x:c>
       <x:c r="I9" s="18">
-        <x:v>45885</x:v>
+        <x:v>45847</x:v>
       </x:c>
       <x:c r="J9" s="16" t="n">
-        <x:v>1346453</x:v>
+        <x:v>1346494</x:v>
       </x:c>
       <x:c r="K9" s="19" t="n">
-        <x:v>1830</x:v>
+        <x:v>2490</x:v>
       </x:c>
       <x:c r="L9" s="20">
-        <x:v>45881.0887037037</x:v>
+        <x:v>45897.2982407407</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>37</x:v>
@@ -5069,7 +5069,7 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="15" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
         <x:v>54</x:v>
@@ -5087,19 +5087,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>45897.2535648148</x:v>
+        <x:v>45881.3064236111</x:v>
       </x:c>
       <x:c r="I10" s="18">
-        <x:v>45847</x:v>
+        <x:v>45871</x:v>
       </x:c>
       <x:c r="J10" s="16" t="n">
-        <x:v>1346494</x:v>
+        <x:v>1195693</x:v>
       </x:c>
       <x:c r="K10" s="19" t="n">
-        <x:v>2490</x:v>
+        <x:v>4275</x:v>
       </x:c>
       <x:c r="L10" s="20">
-        <x:v>45897.2982407407</x:v>
+        <x:v>45897.0449189815</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>37</x:v>
@@ -5520,7 +5520,7 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="27" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C26" s="28" t="s"/>
       <x:c r="D26" s="28" t="s"/>
@@ -5531,7 +5531,7 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="27" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="28" t="s"/>
       <x:c r="D27" s="28" t="s"/>
@@ -5542,7 +5542,7 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
       <x:c r="B28" s="27" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C28" s="28" t="s"/>
       <x:c r="D28" s="28" t="s"/>
@@ -6776,7 +6776,7 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>105</x:v>
@@ -7038,7 +7038,7 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="27" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="28" t="s"/>
       <x:c r="D18" s="28" t="s"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -17,58 +17,22 @@
     <x:sheet name="March 2026" sheetId="15" r:id="rId15"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Ship Station License DOMESTIC Trade (RENEWAL)</x:t>
@@ -912,7 +876,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -939,12 +903,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -952,6 +910,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -966,13 +945,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -1017,6 +989,17 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
@@ -1031,17 +1014,6 @@
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -1223,7 +1195,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1234,76 +1206,91 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
@@ -1311,113 +1298,126 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1681,785 +1681,761 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46076.1792361111</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216147</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46090.2042708333</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46072.0333449074</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216156</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46090.2584837963</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>46071.1677662037</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1216165</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>46091.1948842593</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="F9" s="21" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="H9" s="22">
+        <x:v>46070.1768402778</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1216138</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="22">
+        <x:v>46084.1495138889</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46076.1792361111</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46076.1139583333</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216146</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>46090.1919444444</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46071.3305671296</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1216193</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>46094.1906365741</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46072.0792939815</x:v>
+      </x:c>
+      <x:c r="I12" s="14">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216147</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="J12" s="12" t="n">
+        <x:v>1216150</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46090.2042708333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46072.0333449074</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="L12" s="16">
+        <x:v>46090.220787037</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46077.2598726852</x:v>
+      </x:c>
+      <x:c r="I13" s="14">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216156</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="J13" s="12" t="n">
+        <x:v>1216158</x:v>
+      </x:c>
+      <x:c r="K13" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46090.2584837963</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="L13" s="16">
+        <x:v>46090.2758680556</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="H8" s="17">
-        <x:v>46071.1677662037</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
+      <x:c r="D14" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46072.1089467593</x:v>
+      </x:c>
+      <x:c r="I14" s="14">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1216165</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
+      <x:c r="J14" s="12" t="n">
+        <x:v>1216152</x:v>
+      </x:c>
+      <x:c r="K14" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46091.1948842593</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="L14" s="16">
+        <x:v>46090.2365046296</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46077.5191782407</x:v>
+      </x:c>
+      <x:c r="I15" s="14">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1216163</x:v>
+      </x:c>
+      <x:c r="K15" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L15" s="16">
+        <x:v>46090.3154976852</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46077.4722337963</x:v>
+      </x:c>
+      <x:c r="I16" s="14">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1216161</x:v>
+      </x:c>
+      <x:c r="K16" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L16" s="16">
+        <x:v>46090.2963078704</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>46070.1768402778</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1216138</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>46084.1495138889</x:v>
-      </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46076.1139583333</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216146</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>46090.1919444444</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F17" s="11" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46077.2024189815</x:v>
+      </x:c>
+      <x:c r="I17" s="14">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1216154</x:v>
+      </x:c>
+      <x:c r="K17" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L17" s="16">
+        <x:v>46090.2495949074</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46071.3305671296</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1216193</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L11" s="20">
-        <x:v>46094.1906365741</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46072.0792939815</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="D18" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>46072.0497337963</x:v>
+      </x:c>
+      <x:c r="I18" s="14">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1216150</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="J18" s="12" t="n">
+        <x:v>1216148</x:v>
+      </x:c>
+      <x:c r="K18" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="20">
-        <x:v>46090.220787037</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46077.2598726852</x:v>
-      </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="L18" s="16">
+        <x:v>46090.2102430556</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I19" s="14">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1216158</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="J19" s="12" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K19" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="20">
-        <x:v>46090.2758680556</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46072.1089467593</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
+      <x:c r="L19" s="16">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I20" s="14">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1216152</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="J20" s="12" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K20" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="20">
-        <x:v>46090.2365046296</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46077.5191782407</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1216163</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="L20" s="16">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46079.0151851852</x:v>
+      </x:c>
+      <x:c r="I21" s="14">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="n">
+        <x:v>1216174</x:v>
+      </x:c>
+      <x:c r="K21" s="15" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L21" s="16">
+        <x:v>46093.1514351852</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E22" s="11" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I22" s="14">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="n">
+        <x:v>1216173</x:v>
+      </x:c>
+      <x:c r="K22" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="20">
-        <x:v>46090.3154976852</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46077.4722337963</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1216161</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
-        <x:v>46090.2963078704</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46077.2024189815</x:v>
-      </x:c>
-      <x:c r="I17" s="18">
-        <x:v>45948</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1216154</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L17" s="20">
-        <x:v>46090.2495949074</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46072.0497337963</x:v>
-      </x:c>
-      <x:c r="I18" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1216148</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L18" s="20">
-        <x:v>46090.2102430556</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46071.2285416667</x:v>
-      </x:c>
-      <x:c r="I19" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1216143</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L19" s="20">
-        <x:v>46090.0772916667</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46071.2072569444</x:v>
-      </x:c>
-      <x:c r="I20" s="18">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1216142</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L20" s="20">
-        <x:v>46090.0616666667</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46079.0151851852</x:v>
-      </x:c>
-      <x:c r="I21" s="18">
-        <x:v>45602</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1216174</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
-        <x:v>3990</x:v>
-      </x:c>
-      <x:c r="L21" s="20">
-        <x:v>46093.1514351852</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>45988.1893402778</x:v>
-      </x:c>
-      <x:c r="I22" s="18">
-        <x:v>45973</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1216173</x:v>
-      </x:c>
-      <x:c r="K22" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L22" s="20">
+      <x:c r="L22" s="16">
         <x:v>46093.1383912037</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M22" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="23" t="s"/>
-      <x:c r="F25" s="23" t="s"/>
+      <x:c r="B25" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="27" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C26" s="25" t="s"/>
-      <x:c r="D26" s="25" t="s"/>
-      <x:c r="E26" s="25" t="s"/>
-      <x:c r="F26" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B26" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="B27" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" s="32" t="s"/>
+      <x:c r="D27" s="32" t="s"/>
+      <x:c r="E27" s="32" t="s"/>
+      <x:c r="F27" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B28" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C28" s="31" t="s"/>
-      <x:c r="D28" s="31" t="s"/>
-      <x:c r="E28" s="31" t="s"/>
-      <x:c r="F28" s="32" t="n">
+      <x:c r="B28" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C28" s="35" t="s"/>
+      <x:c r="D28" s="35" t="s"/>
+      <x:c r="E28" s="35" t="s"/>
+      <x:c r="F28" s="36" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3511,253 +3487,242 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>45862.256875</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45908</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215838</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45862.3066319444</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="F7" s="17" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="G7" s="17" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="H7" s="18">
+        <x:v>45861.1595717593</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1215833</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45862.1034606481</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="F8" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="G8" s="21" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45862.256875</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45908</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215838</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45862.3066319444</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45861.1595717593</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215833</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45862.1034606481</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="22">
         <x:v>45861.1361574074</x:v>
       </x:c>
-      <x:c r="I8" s="18">
+      <x:c r="I8" s="23">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="n">
+      <x:c r="J8" s="21" t="n">
         <x:v>1215836</x:v>
       </x:c>
-      <x:c r="K8" s="19" t="n">
+      <x:c r="K8" s="24" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L8" s="22">
         <x:v>45862.1391203704</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="23" t="s"/>
-      <x:c r="F11" s="23" t="s"/>
+      <x:c r="B11" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="26" t="s"/>
+      <x:c r="D11" s="26" t="s"/>
+      <x:c r="E11" s="27" t="s"/>
+      <x:c r="F11" s="27" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B12" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="s"/>
+      <x:c r="D12" s="29" t="s"/>
+      <x:c r="E12" s="29" t="s"/>
+      <x:c r="F12" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="28" t="s"/>
-      <x:c r="F13" s="29" t="n">
+      <x:c r="B13" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="32" t="s"/>
+      <x:c r="D13" s="32" t="s"/>
+      <x:c r="E13" s="32" t="s"/>
+      <x:c r="F13" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="B14" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C14" s="35" t="s"/>
+      <x:c r="D14" s="35" t="s"/>
+      <x:c r="E14" s="35" t="s"/>
+      <x:c r="F14" s="36" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -4823,775 +4788,751 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45877.1309490741</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>45877.1309606481</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1346451</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45877.1897222222</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45882.0658796296</x:v>
+      </x:c>
+      <x:c r="I7" s="18">
+        <x:v>45882.0658912037</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1195701</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>2496</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45883.2549537037</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>45881.0630902778</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>45885</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1346453</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>45881.0887037037</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H9" s="22">
+        <x:v>45897.2535648148</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>45847</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1346494</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
+        <x:v>2490</x:v>
+      </x:c>
+      <x:c r="L9" s="22">
+        <x:v>45897.2982407407</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>45881.3064236111</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45871</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1195693</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>4275</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>45897.0449189815</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>45870.3069328704</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>46186</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1346441</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>45883.1603356482</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>45874.1403125</x:v>
+      </x:c>
+      <x:c r="I12" s="14">
+        <x:v>46159</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1346447</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="n">
+        <x:v>4230</x:v>
+      </x:c>
+      <x:c r="L12" s="16">
+        <x:v>45874.2281365741</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>45883.1346180556</x:v>
+      </x:c>
+      <x:c r="I13" s="13">
+        <x:v>45883.1346296296</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1346466</x:v>
+      </x:c>
+      <x:c r="K13" s="15" t="n">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="L13" s="16">
+        <x:v>45883.1693055556</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C14" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E14" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>45887.5652430556</x:v>
+      </x:c>
+      <x:c r="I14" s="14">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1215872</x:v>
+      </x:c>
+      <x:c r="K14" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L14" s="16">
+        <x:v>45896.2365393518</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45877.1309490741</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>45877.1309606481</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1346451</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45877.1897222222</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45882.0658796296</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>45882.0658912037</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1195701</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>2496</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45883.2549537037</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>45881.0630902778</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>45885</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1346453</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>45873.2842013889</x:v>
+      </x:c>
+      <x:c r="I15" s="14">
+        <x:v>45544</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1346446</x:v>
+      </x:c>
+      <x:c r="K15" s="15" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L15" s="16">
+        <x:v>45873.3539814815</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>45891.1735648148</x:v>
+      </x:c>
+      <x:c r="I16" s="14">
+        <x:v>45765</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1215865</x:v>
+      </x:c>
+      <x:c r="K16" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45881.0887037037</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>45897.2535648148</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>45847</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1346494</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>2490</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>45897.2982407407</x:v>
-      </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45881.3064236111</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>45871</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1195693</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>4275</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>45897.0449189815</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="L16" s="16">
+        <x:v>45898.0611111111</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>45883.1535763889</x:v>
+      </x:c>
+      <x:c r="I17" s="14">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1346468</x:v>
+      </x:c>
+      <x:c r="K17" s="15" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="L17" s="16">
+        <x:v>45883.2560300926</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>45879.4885069444</x:v>
+      </x:c>
+      <x:c r="I18" s="14">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1215863</x:v>
+      </x:c>
+      <x:c r="K18" s="15" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L18" s="16">
+        <x:v>45884.277650463</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45870.3069328704</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>46186</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1346441</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L11" s="20">
-        <x:v>45883.1603356482</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45874.1403125</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>46159</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1346447</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
-        <x:v>4230</x:v>
-      </x:c>
-      <x:c r="L12" s="20">
-        <x:v>45874.2281365741</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45883.1346180556</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45883.1346296296</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1346466</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
-        <x:v>2070</x:v>
-      </x:c>
-      <x:c r="L13" s="20">
-        <x:v>45883.1693055556</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>45887.5652430556</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1215872</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L14" s="20">
-        <x:v>45896.2365393518</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>45873.2842013889</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>45544</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1346446</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L15" s="20">
-        <x:v>45873.3539814815</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="F19" s="11" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="G19" s="11" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="H19" s="13">
+        <x:v>45887.5590162037</x:v>
+      </x:c>
+      <x:c r="I19" s="14">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1215870</x:v>
+      </x:c>
+      <x:c r="K19" s="15" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L19" s="16">
+        <x:v>45896.237962963</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H16" s="17">
-        <x:v>45891.1735648148</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>45765</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
-        <x:v>45898.0611111111</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="D20" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="F20" s="11" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="G20" s="11" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>45883.1535763889</x:v>
-      </x:c>
-      <x:c r="I17" s="18">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1346468</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>4350</x:v>
-      </x:c>
-      <x:c r="L17" s="20">
-        <x:v>45883.2560300926</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>45879.4885069444</x:v>
-      </x:c>
-      <x:c r="I18" s="18">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1215863</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L18" s="20">
-        <x:v>45884.277650463</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>45887.5590162037</x:v>
-      </x:c>
-      <x:c r="I19" s="18">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1215870</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
+      <x:c r="H20" s="13">
+        <x:v>45881.2806365741</x:v>
+      </x:c>
+      <x:c r="I20" s="14">
+        <x:v>45892</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1346470</x:v>
+      </x:c>
+      <x:c r="K20" s="15" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L19" s="20">
-        <x:v>45896.237962963</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>45881.2806365741</x:v>
-      </x:c>
-      <x:c r="I20" s="18">
-        <x:v>45892</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L20" s="20">
+      <x:c r="L20" s="16">
         <x:v>45883.2976041667</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>37</x:v>
+      <x:c r="M20" s="11" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="s"/>
-      <x:c r="D23" s="22" t="s"/>
-      <x:c r="E23" s="23" t="s"/>
-      <x:c r="F23" s="23" t="s"/>
+      <x:c r="B23" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="27" t="s"/>
     </x:row>
     <x:row r="24" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B24" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B24" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="27" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C25" s="28" t="s"/>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="28" t="s"/>
-      <x:c r="F25" s="29" t="n">
+      <x:c r="B25" s="31" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C25" s="32" t="s"/>
+      <x:c r="D25" s="32" t="s"/>
+      <x:c r="E25" s="32" t="s"/>
+      <x:c r="F25" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="27" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C26" s="28" t="s"/>
-      <x:c r="D26" s="28" t="s"/>
-      <x:c r="E26" s="28" t="s"/>
-      <x:c r="F26" s="29" t="n">
+      <x:c r="B26" s="31" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C26" s="32" t="s"/>
+      <x:c r="D26" s="32" t="s"/>
+      <x:c r="E26" s="32" t="s"/>
+      <x:c r="F26" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="27" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="B27" s="31" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C27" s="32" t="s"/>
+      <x:c r="D27" s="32" t="s"/>
+      <x:c r="E27" s="32" t="s"/>
+      <x:c r="F27" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="27" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="n">
+      <x:c r="B28" s="31" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C28" s="32" t="s"/>
+      <x:c r="D28" s="32" t="s"/>
+      <x:c r="E28" s="32" t="s"/>
+      <x:c r="F28" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="27" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
+      <x:c r="B29" s="31" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C29" s="32" t="s"/>
+      <x:c r="D29" s="32" t="s"/>
+      <x:c r="E29" s="32" t="s"/>
+      <x:c r="F29" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="27" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C30" s="28" t="s"/>
-      <x:c r="D30" s="28" t="s"/>
-      <x:c r="E30" s="28" t="s"/>
-      <x:c r="F30" s="29" t="n">
+      <x:c r="B30" s="31" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C30" s="32" t="s"/>
+      <x:c r="D30" s="32" t="s"/>
+      <x:c r="E30" s="32" t="s"/>
+      <x:c r="F30" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C31" s="28" t="s"/>
-      <x:c r="D31" s="28" t="s"/>
-      <x:c r="E31" s="28" t="s"/>
-      <x:c r="F31" s="29" t="n">
+      <x:c r="B31" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C31" s="32" t="s"/>
+      <x:c r="D31" s="32" t="s"/>
+      <x:c r="E31" s="32" t="s"/>
+      <x:c r="F31" s="33" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C32" s="31" t="s"/>
-      <x:c r="D32" s="31" t="s"/>
-      <x:c r="E32" s="31" t="s"/>
-      <x:c r="F32" s="32" t="n">
+      <x:c r="B32" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C32" s="35" t="s"/>
+      <x:c r="D32" s="35" t="s"/>
+      <x:c r="E32" s="35" t="s"/>
+      <x:c r="F32" s="36" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -6645,427 +6586,403 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45883.0291898148</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1346465</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45929.2261805556</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45883.0965162037</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>2592.56</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45930.3001388889</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C8" s="21" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E8" s="21" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>45908.5003472222</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>45790</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1215888</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>45911.952650463</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="F9" s="21" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45883.0291898148</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45651</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1346465</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45929.2261805556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="H9" s="22">
+        <x:v>45916.1691666667</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>45949</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1215908</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="22">
+        <x:v>45929.1383449074</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F10" s="11" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45883.0965162037</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="G10" s="11" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>2592.56</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45930.3001388889</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="H10" s="13">
+        <x:v>45888.154375</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1215874</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>45902.050775463</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F11" s="11" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H8" s="17">
-        <x:v>45908.5003472222</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>45790</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1215888</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45911.952650463</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="H11" s="13">
+        <x:v>45877.1361111111</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>45909</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1346508</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>45908.1453009259</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D12" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F12" s="11" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G12" s="11" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H9" s="17">
-        <x:v>45916.1691666667</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>45949</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1215908</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>45929.1383449074</x:v>
-      </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45888.154375</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>45870</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1215874</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>45902.050775463</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45877.1361111111</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>45909</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1346508</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="L11" s="20">
-        <x:v>45908.1453009259</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="13">
         <x:v>45924.1162962963</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="14">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="12" t="n">
         <x:v>1215911</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="15" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="16">
         <x:v>45930.063912037</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M12" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="23" t="s"/>
+      <x:c r="B15" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="27" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B16" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="B17" s="31" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C17" s="32" t="s"/>
+      <x:c r="D17" s="32" t="s"/>
+      <x:c r="E17" s="32" t="s"/>
+      <x:c r="F17" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="B18" s="31" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="B19" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C20" s="31" t="s"/>
-      <x:c r="D20" s="31" t="s"/>
-      <x:c r="E20" s="31" t="s"/>
-      <x:c r="F20" s="32" t="n">
+      <x:c r="B20" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C20" s="35" t="s"/>
+      <x:c r="D20" s="35" t="s"/>
+      <x:c r="E20" s="35" t="s"/>
+      <x:c r="F20" s="36" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8127,300 +8044,276 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45931</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45947.5768287037</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>43437</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215960</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>17766</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45954.2191782407</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C7" s="17" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E7" s="17" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s"/>
+      <x:c r="H7" s="18">
+        <x:v>45925.0601967593</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>45922</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1215919</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45933.3037152778</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>45912.3032407407</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>45879</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1215920</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>4710</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>45933.3105324074</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45947.5768287037</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>43437</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215960</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>17766</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45954.2191782407</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s"/>
-      <x:c r="H7" s="12">
-        <x:v>45925.0601967593</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45922</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215919</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="H9" s="22">
+        <x:v>45931.5665277778</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1215945</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45933.3037152778</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>45912.3032407407</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>45879</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1215920</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>4710</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45933.3105324074</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>45931.5665277778</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1215945</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L9" s="22">
         <x:v>45940.1382060185</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="s"/>
+      <x:c r="D12" s="26" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="27" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B13" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s"/>
+      <x:c r="D13" s="29" t="s"/>
+      <x:c r="E13" s="29" t="s"/>
+      <x:c r="F13" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="31" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="s"/>
+      <x:c r="D14" s="32" t="s"/>
+      <x:c r="E14" s="32" t="s"/>
+      <x:c r="F14" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="32" t="s"/>
+      <x:c r="D15" s="32" t="s"/>
+      <x:c r="E15" s="32" t="s"/>
+      <x:c r="F15" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C16" s="35" t="s"/>
+      <x:c r="D16" s="35" t="s"/>
+      <x:c r="E16" s="35" t="s"/>
+      <x:c r="F16" s="36" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -9485,367 +9378,343 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45974.6184490741</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45682</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216021</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45986.0239236111</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45965.4411342593</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>45974</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216001</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45973.0179398148</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>45971.2507291667</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1216006</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>45975.0756134259</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="F9" s="21" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45974.6184490741</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45682</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216021</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45986.0239236111</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="H9" s="22">
+        <x:v>45958.3516898148</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1215976</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L9" s="22">
+        <x:v>45967.2412384259</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="F10" s="11" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="G10" s="11" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45965.4411342593</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45974</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216001</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="H10" s="13">
+        <x:v>45954.2913425926</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216013</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45973.0179398148</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="L10" s="16">
+        <x:v>45975.3213541667</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F11" s="11" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H8" s="17">
-        <x:v>45971.2507291667</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>45991</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1216006</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45975.0756134259</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>45958.3516898148</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1215976</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>3990</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>45967.2412384259</x:v>
-      </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45954.2913425926</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216013</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>45975.3213541667</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="13">
         <x:v>45953.3174884259</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="14">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="12" t="n">
         <x:v>1215996</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="16">
         <x:v>45971.2990162037</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="B14" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="27" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B15" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="29" t="s"/>
+      <x:c r="F15" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="32" t="s"/>
+      <x:c r="D16" s="32" t="s"/>
+      <x:c r="E16" s="32" t="s"/>
+      <x:c r="F16" s="33" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
+      <x:c r="B17" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C17" s="35" t="s"/>
+      <x:c r="D17" s="35" t="s"/>
+      <x:c r="E17" s="35" t="s"/>
+      <x:c r="F17" s="36" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -10908,302 +10777,278 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46000.4750694444</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216048</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46013.2950462963</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C7" s="17" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E7" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46000.180775463</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46006.2645138889</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>45972.0386111111</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>46337</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1216033</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>46006.0795717593</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46000.4750694444</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216048</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46013.2950462963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46000.180775463</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46006.2645138889</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>45972.0386111111</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>46337</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1216033</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46006.0795717593</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="22">
         <x:v>45980.2173958333</x:v>
       </x:c>
-      <x:c r="I9" s="18">
+      <x:c r="I9" s="23">
         <x:v>45852</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="n">
+      <x:c r="J9" s="21" t="n">
         <x:v>1216027</x:v>
       </x:c>
-      <x:c r="K9" s="19" t="n">
+      <x:c r="K9" s="24" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L9" s="22">
         <x:v>45992.1151851852</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="s"/>
+      <x:c r="D12" s="26" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="27" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B13" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s"/>
+      <x:c r="D13" s="29" t="s"/>
+      <x:c r="E13" s="29" t="s"/>
+      <x:c r="F13" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="31" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="s"/>
+      <x:c r="D14" s="32" t="s"/>
+      <x:c r="E14" s="32" t="s"/>
+      <x:c r="F14" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="32" t="s"/>
+      <x:c r="D15" s="32" t="s"/>
+      <x:c r="E15" s="32" t="s"/>
+      <x:c r="F15" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C16" s="35" t="s"/>
+      <x:c r="D16" s="35" t="s"/>
+      <x:c r="E16" s="35" t="s"/>
+      <x:c r="F16" s="36" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12268,291 +12113,267 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46007.1341435185</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216069</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46035.3042476852</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46034.1687615741</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216081</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46044.263275463</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>46014.1352083333</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1216066</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>46035.0802662037</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="F9" s="21" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46007.1341435185</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216069</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46035.3042476852</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46034.1687615741</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216081</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46044.263275463</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>46014.1352083333</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1216066</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46035.0802662037</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>185</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="22">
         <x:v>46014.4844097222</x:v>
       </x:c>
-      <x:c r="I9" s="18">
+      <x:c r="I9" s="23">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="n">
+      <x:c r="J9" s="21" t="n">
         <x:v>1216060</x:v>
       </x:c>
-      <x:c r="K9" s="19" t="n">
+      <x:c r="K9" s="24" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L9" s="22">
         <x:v>46031.0514583333</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>185</x:v>
+      <x:c r="M9" s="21" t="s">
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="s"/>
+      <x:c r="D12" s="26" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="27" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B13" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="s"/>
+      <x:c r="D13" s="29" t="s"/>
+      <x:c r="E13" s="29" t="s"/>
+      <x:c r="F13" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="32" t="s"/>
+      <x:c r="D14" s="32" t="s"/>
+      <x:c r="E14" s="32" t="s"/>
+      <x:c r="F14" s="33" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="31" t="s"/>
-      <x:c r="D15" s="31" t="s"/>
-      <x:c r="E15" s="31" t="s"/>
-      <x:c r="F15" s="32" t="n">
+      <x:c r="B15" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C15" s="35" t="s"/>
+      <x:c r="D15" s="35" t="s"/>
+      <x:c r="E15" s="35" t="s"/>
+      <x:c r="F15" s="36" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13617,568 +13438,544 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46051.2691319444</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46051.2691550926</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216103</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46057.9587152778</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C7" s="17" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E7" s="17" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46051.1259722222</x:v>
+      </x:c>
+      <x:c r="I7" s="19">
+        <x:v>46053</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216112</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46062.966400463</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="21" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H8" s="22">
+        <x:v>46050.2853935185</x:v>
+      </x:c>
+      <x:c r="I8" s="23">
+        <x:v>45945</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="n">
+        <x:v>1216106</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="22">
+        <x:v>46058.0440046296</x:v>
+      </x:c>
+      <x:c r="M8" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="21" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="21" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="D9" s="21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="F9" s="21" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="G9" s="21" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46051.2691319444</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46051.2691550926</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216103</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>2070</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46057.9587152778</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="H9" s="22">
+        <x:v>46066.1892939815</x:v>
+      </x:c>
+      <x:c r="I9" s="23">
+        <x:v>45695</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="n">
+        <x:v>1216131</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L9" s="22">
+        <x:v>46076.0521180556</x:v>
+      </x:c>
+      <x:c r="M9" s="21" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="G10" s="11" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="H10" s="13">
+        <x:v>46066.186087963</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45695</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216130</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>46076.0476273148</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46051.1259722222</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="F11" s="11" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46057.2800462963</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1216117</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>46065.2796412037</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46057.272025463</x:v>
+      </x:c>
+      <x:c r="I12" s="14">
+        <x:v>46045</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1216121</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L12" s="16">
+        <x:v>46065.2951388889</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46057.2657523148</x:v>
+      </x:c>
+      <x:c r="I13" s="14">
+        <x:v>46039</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1216119</x:v>
+      </x:c>
+      <x:c r="K13" s="15" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="16">
+        <x:v>46065.285474537</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46056.1690046296</x:v>
+      </x:c>
+      <x:c r="I14" s="14">
+        <x:v>45716</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1216107</x:v>
+      </x:c>
+      <x:c r="K14" s="15" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L14" s="16">
+        <x:v>46058.1034490741</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46065.2312962963</x:v>
+      </x:c>
+      <x:c r="I15" s="14">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216112</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="J15" s="12" t="n">
+        <x:v>1216134</x:v>
+      </x:c>
+      <x:c r="K15" s="15" t="n">
+        <x:v>2190</x:v>
+      </x:c>
+      <x:c r="L15" s="16">
+        <x:v>46076.0858333333</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46063.0357060185</x:v>
+      </x:c>
+      <x:c r="I16" s="14">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1216123</x:v>
+      </x:c>
+      <x:c r="K16" s="15" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46062.966400463</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H8" s="17">
-        <x:v>46050.2853935185</x:v>
-      </x:c>
-      <x:c r="I8" s="18">
-        <x:v>45945</x:v>
-      </x:c>
-      <x:c r="J8" s="16" t="n">
-        <x:v>1216106</x:v>
-      </x:c>
-      <x:c r="K8" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>46058.0440046296</x:v>
-      </x:c>
-      <x:c r="M8" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F9" s="15" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>46066.1892939815</x:v>
-      </x:c>
-      <x:c r="I9" s="18">
-        <x:v>45695</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="n">
-        <x:v>1216131</x:v>
-      </x:c>
-      <x:c r="K9" s="19" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>46076.0521180556</x:v>
-      </x:c>
-      <x:c r="M9" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46066.186087963</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>45695</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1216130</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>46076.0476273148</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46057.2800462963</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1216117</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L11" s="20">
-        <x:v>46065.2796412037</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46057.272025463</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>46045</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1216121</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L12" s="20">
-        <x:v>46065.2951388889</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46057.2657523148</x:v>
-      </x:c>
-      <x:c r="I13" s="18">
-        <x:v>46039</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1216119</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L13" s="20">
-        <x:v>46065.285474537</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46056.1690046296</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>45716</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1216107</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L14" s="20">
-        <x:v>46058.1034490741</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46065.2312962963</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>46053</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1216134</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
-        <x:v>2190</x:v>
-      </x:c>
-      <x:c r="L15" s="20">
-        <x:v>46076.0858333333</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46063.0357060185</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1216123</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
+      <x:c r="L16" s="16">
         <x:v>46066.0203819444</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>19</x:v>
+      <x:c r="M16" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="23" t="s"/>
+      <x:c r="B19" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="27" t="s"/>
     </x:row>
     <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="s">
-        <x:v>29</x:v>
+      <x:c r="B20" s="28" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
+      <x:c r="B21" s="31" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C21" s="32" t="s"/>
+      <x:c r="D21" s="32" t="s"/>
+      <x:c r="E21" s="32" t="s"/>
+      <x:c r="F21" s="33" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="29" t="n">
+      <x:c r="B22" s="31" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C22" s="32" t="s"/>
+      <x:c r="D22" s="32" t="s"/>
+      <x:c r="E22" s="32" t="s"/>
+      <x:c r="F22" s="33" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C23" s="31" t="s"/>
-      <x:c r="D23" s="31" t="s"/>
-      <x:c r="E23" s="31" t="s"/>
-      <x:c r="F23" s="32" t="n">
+      <x:c r="B23" s="34" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C23" s="35" t="s"/>
+      <x:c r="D23" s="35" t="s"/>
+      <x:c r="E23" s="35" t="s"/>
+      <x:c r="F23" s="36" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1746,7 +1746,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1816,7 +1816,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -3579,7 +3579,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3649,7 +3649,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -4894,7 +4894,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -4964,7 +4964,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>26</x:v>
@@ -6719,7 +6719,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -6789,7 +6789,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>32</x:v>
@@ -8204,7 +8204,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -8274,7 +8274,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -9565,7 +9565,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -9635,7 +9635,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -10991,7 +10991,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -11061,7 +11061,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -12354,7 +12354,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -12424,7 +12424,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -13706,7 +13706,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -13776,7 +13776,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,9 +30,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <x:si>
     <x:t>LICENSE SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Ship Station License DOMESTIC Trade (RENEWAL)</x:t>
@@ -876,7 +912,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -921,21 +957,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -945,6 +966,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -1195,7 +1223,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1206,10 +1234,16 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1221,68 +1255,50 @@
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1313,124 +1329,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1449,8 +1349,76 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1748,18 +1716,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1777,725 +1733,737 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46076.1792361111</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216147</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46090.2042708333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46072.0333449074</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216156</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46090.2584837963</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46076.1792361111</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216147</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46090.2042708333</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46072.0333449074</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216156</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46090.2584837963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46071.1677662037</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1216165</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>46091.1948842593</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46070.1768402778</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1216138</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>46084.1495138889</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
         <x:v>46076.1139583333</x:v>
       </x:c>
-      <x:c r="I10" s="42">
+      <x:c r="I12" s="18">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1216146</x:v>
       </x:c>
-      <x:c r="K10" s="43" t="n">
+      <x:c r="K12" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="44">
+      <x:c r="L12" s="20">
         <x:v>46090.1919444444</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
+      <x:c r="M12" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>46071.3305671296</x:v>
       </x:c>
-      <x:c r="I11" s="42">
+      <x:c r="I13" s="18">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1216193</x:v>
       </x:c>
-      <x:c r="K11" s="43" t="n">
+      <x:c r="K13" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="44">
+      <x:c r="L13" s="20">
         <x:v>46094.1906365741</x:v>
       </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="39" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D12" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="F12" s="39" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="G12" s="39" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H12" s="41">
+      <x:c r="M13" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
         <x:v>46072.0792939815</x:v>
       </x:c>
-      <x:c r="I12" s="42">
+      <x:c r="I14" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J12" s="40" t="n">
+      <x:c r="J14" s="16" t="n">
         <x:v>1216150</x:v>
       </x:c>
-      <x:c r="K12" s="43" t="n">
+      <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="44">
+      <x:c r="L14" s="20">
         <x:v>46090.220787037</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="39" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E13" s="39" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="F13" s="39" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="G13" s="39" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="H13" s="41">
+      <x:c r="M14" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
         <x:v>46077.2598726852</x:v>
       </x:c>
-      <x:c r="I13" s="42">
+      <x:c r="I15" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>1216158</x:v>
       </x:c>
-      <x:c r="K13" s="43" t="n">
+      <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="44">
+      <x:c r="L15" s="20">
         <x:v>46090.2758680556</x:v>
       </x:c>
-      <x:c r="M13" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="39" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D14" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="39" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="F14" s="39" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="G14" s="39" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="H14" s="41">
+      <x:c r="M15" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
         <x:v>46072.1089467593</x:v>
       </x:c>
-      <x:c r="I14" s="42">
+      <x:c r="I16" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="40" t="n">
+      <x:c r="J16" s="16" t="n">
         <x:v>1216152</x:v>
       </x:c>
-      <x:c r="K14" s="43" t="n">
+      <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="44">
+      <x:c r="L16" s="20">
         <x:v>46090.2365046296</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="39" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D15" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E15" s="39" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F15" s="39" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="G15" s="39" t="s">
+      <x:c r="M16" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46077.5191782407</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1216163</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>46090.3154976852</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46077.4722337963</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1216161</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>46090.2963078704</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="H15" s="41">
-        <x:v>46077.5191782407</x:v>
-      </x:c>
-      <x:c r="I15" s="42">
+      <x:c r="F19" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46077.2024189815</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1216154</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>46090.2495949074</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46072.0497337963</x:v>
+      </x:c>
+      <x:c r="I20" s="18">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
-        <x:v>1216163</x:v>
-      </x:c>
-      <x:c r="K15" s="43" t="n">
+      <x:c r="J20" s="16" t="n">
+        <x:v>1216148</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="44">
-        <x:v>46090.3154976852</x:v>
-      </x:c>
-      <x:c r="M15" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="39" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D16" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E16" s="39" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="F16" s="39" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="G16" s="39" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="H16" s="41">
-        <x:v>46077.4722337963</x:v>
-      </x:c>
-      <x:c r="I16" s="42">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J16" s="40" t="n">
-        <x:v>1216161</x:v>
-      </x:c>
-      <x:c r="K16" s="43" t="n">
+      <x:c r="L20" s="20">
+        <x:v>46090.2102430556</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="44">
-        <x:v>46090.2963078704</x:v>
-      </x:c>
-      <x:c r="M16" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="39" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D17" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E17" s="39" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="F17" s="39" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G17" s="39" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H17" s="41">
-        <x:v>46077.2024189815</x:v>
-      </x:c>
-      <x:c r="I17" s="42">
-        <x:v>45948</x:v>
-      </x:c>
-      <x:c r="J17" s="40" t="n">
-        <x:v>1216154</x:v>
-      </x:c>
-      <x:c r="K17" s="43" t="n">
+      <x:c r="L21" s="20">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I22" s="18">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="44">
-        <x:v>46090.2495949074</x:v>
-      </x:c>
-      <x:c r="M17" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="39" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D18" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E18" s="39" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="F18" s="39" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="G18" s="39" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="H18" s="41">
-        <x:v>46072.0497337963</x:v>
-      </x:c>
-      <x:c r="I18" s="42">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J18" s="40" t="n">
-        <x:v>1216148</x:v>
-      </x:c>
-      <x:c r="K18" s="43" t="n">
+      <x:c r="L22" s="20">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46079.0151851852</x:v>
+      </x:c>
+      <x:c r="I23" s="18">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
+        <x:v>1216174</x:v>
+      </x:c>
+      <x:c r="K23" s="19" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L23" s="20">
+        <x:v>46093.1514351852</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I24" s="18">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>1216173</x:v>
+      </x:c>
+      <x:c r="K24" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L18" s="44">
-        <x:v>46090.2102430556</x:v>
-      </x:c>
-      <x:c r="M18" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="39" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D19" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E19" s="39" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="F19" s="39" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="G19" s="39" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="H19" s="41">
-        <x:v>46071.2285416667</x:v>
-      </x:c>
-      <x:c r="I19" s="42">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J19" s="40" t="n">
-        <x:v>1216143</x:v>
-      </x:c>
-      <x:c r="K19" s="43" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L19" s="44">
-        <x:v>46090.0772916667</x:v>
-      </x:c>
-      <x:c r="M19" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="39" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D20" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E20" s="39" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F20" s="39" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G20" s="39" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H20" s="41">
-        <x:v>46071.2072569444</x:v>
-      </x:c>
-      <x:c r="I20" s="42">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J20" s="40" t="n">
-        <x:v>1216142</x:v>
-      </x:c>
-      <x:c r="K20" s="43" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L20" s="44">
-        <x:v>46090.0616666667</x:v>
-      </x:c>
-      <x:c r="M20" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="39" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D21" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E21" s="39" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="F21" s="39" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G21" s="39" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H21" s="41">
-        <x:v>46079.0151851852</x:v>
-      </x:c>
-      <x:c r="I21" s="42">
-        <x:v>45602</x:v>
-      </x:c>
-      <x:c r="J21" s="40" t="n">
-        <x:v>1216174</x:v>
-      </x:c>
-      <x:c r="K21" s="43" t="n">
-        <x:v>3990</x:v>
-      </x:c>
-      <x:c r="L21" s="44">
-        <x:v>46093.1514351852</x:v>
-      </x:c>
-      <x:c r="M21" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="39" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D22" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E22" s="39" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F22" s="39" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="G22" s="39" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="H22" s="41">
-        <x:v>45988.1893402778</x:v>
-      </x:c>
-      <x:c r="I22" s="42">
-        <x:v>45973</x:v>
-      </x:c>
-      <x:c r="J22" s="40" t="n">
-        <x:v>1216173</x:v>
-      </x:c>
-      <x:c r="K22" s="43" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L22" s="44">
+      <x:c r="L24" s="20">
         <x:v>46093.1383912037</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B23" s="26" t="s"/>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="26" t="s"/>
-      <x:c r="G23" s="26" t="s"/>
-      <x:c r="H23" s="26" t="s"/>
-      <x:c r="I23" s="26" t="s"/>
-      <x:c r="J23" s="26" t="s"/>
-      <x:c r="K23" s="26" t="s"/>
-      <x:c r="L23" s="26" t="s"/>
-      <x:c r="M23" s="26" t="s"/>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B24" s="26" t="s"/>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="26" t="s"/>
-      <x:c r="G24" s="26" t="s"/>
-      <x:c r="H24" s="26" t="s"/>
-      <x:c r="I24" s="26" t="s"/>
-      <x:c r="J24" s="26" t="s"/>
-      <x:c r="K24" s="26" t="s"/>
-      <x:c r="L24" s="26" t="s"/>
-      <x:c r="M24" s="26" t="s"/>
+      <x:c r="M24" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="29" t="s"/>
+      <x:c r="B27" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C27" s="22" t="s"/>
+      <x:c r="D27" s="22" t="s"/>
+      <x:c r="E27" s="23" t="s"/>
+      <x:c r="F27" s="23" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C28" s="31" t="s"/>
-      <x:c r="D28" s="31" t="s"/>
-      <x:c r="E28" s="31" t="s"/>
-      <x:c r="F28" s="32" t="s">
+      <x:c r="B28" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="34" t="s"/>
-      <x:c r="D29" s="34" t="s"/>
-      <x:c r="E29" s="34" t="s"/>
-      <x:c r="F29" s="35" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
     <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C30" s="37" t="s"/>
-      <x:c r="D30" s="37" t="s"/>
-      <x:c r="E30" s="37" t="s"/>
-      <x:c r="F30" s="38" t="n">
+      <x:c r="B30" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="s"/>
+      <x:c r="D30" s="31" t="s"/>
+      <x:c r="E30" s="31" t="s"/>
+      <x:c r="F30" s="32" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3581,18 +3549,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3610,193 +3566,205 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45862.256875</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45908</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215838</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45862.3066319444</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F7" s="17" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45861.1595717593</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1215833</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45862.1034606481</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>7</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="G8" s="21" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45862.256875</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45908</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215838</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45862.3066319444</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45861.1595717593</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215833</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45862.1034606481</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45861.1361574074</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1215836</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>45862.1391203704</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="25" t="s"/>
-      <x:c r="C9" s="25" t="s"/>
-      <x:c r="D9" s="25" t="s"/>
-      <x:c r="E9" s="25" t="s"/>
-      <x:c r="F9" s="25" t="s"/>
-      <x:c r="G9" s="25" t="s"/>
-      <x:c r="H9" s="25" t="s"/>
-      <x:c r="I9" s="25" t="s"/>
-      <x:c r="J9" s="25" t="s"/>
-      <x:c r="K9" s="25" t="s"/>
-      <x:c r="L9" s="25" t="s"/>
-      <x:c r="M9" s="25" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="26" t="s"/>
-      <x:c r="C10" s="26" t="s"/>
-      <x:c r="D10" s="26" t="s"/>
-      <x:c r="E10" s="26" t="s"/>
-      <x:c r="F10" s="26" t="s"/>
-      <x:c r="G10" s="26" t="s"/>
-      <x:c r="H10" s="26" t="s"/>
-      <x:c r="I10" s="26" t="s"/>
-      <x:c r="J10" s="26" t="s"/>
-      <x:c r="K10" s="26" t="s"/>
-      <x:c r="L10" s="26" t="s"/>
-      <x:c r="M10" s="26" t="s"/>
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s"/>
-      <x:c r="D13" s="28" t="s"/>
-      <x:c r="E13" s="29" t="s"/>
-      <x:c r="F13" s="29" t="s"/>
+      <x:c r="B13" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="23" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C14" s="31" t="s"/>
-      <x:c r="D14" s="31" t="s"/>
-      <x:c r="E14" s="31" t="s"/>
-      <x:c r="F14" s="32" t="s">
-        <x:v>17</x:v>
+      <x:c r="B14" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="34" t="s"/>
-      <x:c r="D15" s="34" t="s"/>
-      <x:c r="E15" s="34" t="s"/>
-      <x:c r="F15" s="35" t="n">
+      <x:c r="B15" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C16" s="37" t="s"/>
-      <x:c r="D16" s="37" t="s"/>
-      <x:c r="E16" s="37" t="s"/>
-      <x:c r="F16" s="38" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -4896,18 +4864,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4925,715 +4881,727 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45877.1309490741</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45877.1309606481</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346451</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45877.1897222222</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45882.0658796296</x:v>
-      </x:c>
-      <x:c r="I7" s="18">
-        <x:v>45882.0658912037</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1195701</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>2496</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45883.2549537037</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>31</x:v>
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C8" s="21" t="s">
+      <x:c r="D8" s="11" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
+      <x:c r="E8" s="11" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F8" s="21" t="s">
+      <x:c r="F8" s="11" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G8" s="21" t="s">
+      <x:c r="G8" s="11" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="H8" s="12">
+        <x:v>45877.1309490741</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45877.1309606481</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346451</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45877.1897222222</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45882.0658796296</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>45882.0658912037</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1195701</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>2496</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45883.2549537037</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45881.0630902778</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>45885</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1346453</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>45881.0887037037</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
+      <x:c r="M10" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>45897.2535648148</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>45847</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1346494</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>45897.2982407407</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
         <x:v>45881.3064236111</x:v>
       </x:c>
-      <x:c r="I10" s="42">
+      <x:c r="I12" s="18">
         <x:v>45871</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1195693</x:v>
       </x:c>
-      <x:c r="K10" s="43" t="n">
+      <x:c r="K12" s="19" t="n">
         <x:v>4275</x:v>
       </x:c>
-      <x:c r="L10" s="44">
+      <x:c r="L12" s="20">
         <x:v>45897.0449189815</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
+      <x:c r="M12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>45870.3069328704</x:v>
       </x:c>
-      <x:c r="I11" s="42">
+      <x:c r="I13" s="18">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1346441</x:v>
       </x:c>
-      <x:c r="K11" s="43" t="n">
+      <x:c r="K13" s="19" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="44">
+      <x:c r="L13" s="20">
         <x:v>45883.1603356482</x:v>
       </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="39" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C12" s="39" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D12" s="40" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F12" s="39" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G12" s="39" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H12" s="41">
+      <x:c r="M13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
         <x:v>45874.1403125</x:v>
       </x:c>
-      <x:c r="I12" s="42">
+      <x:c r="I14" s="18">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="J12" s="40" t="n">
+      <x:c r="J14" s="16" t="n">
         <x:v>1346447</x:v>
       </x:c>
-      <x:c r="K12" s="43" t="n">
+      <x:c r="K14" s="19" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L12" s="44">
+      <x:c r="L14" s="20">
         <x:v>45874.2281365741</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="39" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C13" s="39" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E13" s="39" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F13" s="39" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G13" s="39" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H13" s="41">
+      <x:c r="M14" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
         <x:v>45883.1346180556</x:v>
       </x:c>
-      <x:c r="I13" s="41">
+      <x:c r="I15" s="17">
         <x:v>45883.1346296296</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>1346466</x:v>
       </x:c>
-      <x:c r="K13" s="43" t="n">
+      <x:c r="K15" s="19" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L13" s="44">
+      <x:c r="L15" s="20">
         <x:v>45883.1693055556</x:v>
       </x:c>
-      <x:c r="M13" s="39" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="39" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D14" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="39" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F14" s="39" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G14" s="39" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H14" s="41">
+      <x:c r="M15" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
         <x:v>45887.5652430556</x:v>
       </x:c>
-      <x:c r="I14" s="42">
+      <x:c r="I16" s="18">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J14" s="40" t="n">
+      <x:c r="J16" s="16" t="n">
         <x:v>1215872</x:v>
       </x:c>
-      <x:c r="K14" s="43" t="n">
+      <x:c r="K16" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="44">
+      <x:c r="L16" s="20">
         <x:v>45896.2365393518</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="39" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D15" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E15" s="39" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F15" s="39" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G15" s="39" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H15" s="41">
+      <x:c r="M16" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
         <x:v>45873.2842013889</x:v>
       </x:c>
-      <x:c r="I15" s="42">
+      <x:c r="I17" s="18">
         <x:v>45544</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J17" s="16" t="n">
         <x:v>1346446</x:v>
       </x:c>
-      <x:c r="K15" s="43" t="n">
+      <x:c r="K17" s="19" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L15" s="44">
+      <x:c r="L17" s="20">
         <x:v>45873.3539814815</x:v>
       </x:c>
-      <x:c r="M15" s="39" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="39" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D16" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E16" s="39" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F16" s="39" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G16" s="39" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H16" s="41">
+      <x:c r="M17" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
         <x:v>45891.1735648148</x:v>
       </x:c>
-      <x:c r="I16" s="42">
+      <x:c r="I18" s="18">
         <x:v>45765</x:v>
       </x:c>
-      <x:c r="J16" s="40" t="n">
+      <x:c r="J18" s="16" t="n">
         <x:v>1215865</x:v>
       </x:c>
-      <x:c r="K16" s="43" t="n">
+      <x:c r="K18" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="44">
+      <x:c r="L18" s="20">
         <x:v>45898.0611111111</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="39" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D17" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E17" s="39" t="s">
+      <x:c r="M18" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>45883.1535763889</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1346468</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>45883.2560300926</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>45879.4885069444</x:v>
+      </x:c>
+      <x:c r="I20" s="18">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1215863</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>45884.277650463</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F17" s="39" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G17" s="39" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H17" s="41">
-        <x:v>45883.1535763889</x:v>
-      </x:c>
-      <x:c r="I17" s="42">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J17" s="40" t="n">
-        <x:v>1346468</x:v>
-      </x:c>
-      <x:c r="K17" s="43" t="n">
-        <x:v>4350</x:v>
-      </x:c>
-      <x:c r="L17" s="44">
-        <x:v>45883.2560300926</x:v>
-      </x:c>
-      <x:c r="M17" s="39" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="39" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D18" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E18" s="39" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F18" s="39" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G18" s="39" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H18" s="41">
-        <x:v>45879.4885069444</x:v>
-      </x:c>
-      <x:c r="I18" s="42">
+      <x:c r="F21" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>45887.5590162037</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J18" s="40" t="n">
-        <x:v>1215863</x:v>
-      </x:c>
-      <x:c r="K18" s="43" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L18" s="44">
-        <x:v>45884.277650463</x:v>
-      </x:c>
-      <x:c r="M18" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="39" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D19" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E19" s="39" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F19" s="39" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G19" s="39" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H19" s="41">
-        <x:v>45887.5590162037</x:v>
-      </x:c>
-      <x:c r="I19" s="42">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J21" s="16" t="n">
         <x:v>1215870</x:v>
       </x:c>
-      <x:c r="K19" s="43" t="n">
+      <x:c r="K21" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L19" s="44">
+      <x:c r="L21" s="20">
         <x:v>45896.237962963</x:v>
       </x:c>
-      <x:c r="M19" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="39" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D20" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E20" s="39" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F20" s="39" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G20" s="39" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H20" s="41">
+      <x:c r="M21" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
         <x:v>45881.2806365741</x:v>
       </x:c>
-      <x:c r="I20" s="42">
+      <x:c r="I22" s="18">
         <x:v>45892</x:v>
       </x:c>
-      <x:c r="J20" s="40" t="n">
+      <x:c r="J22" s="16" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K20" s="43" t="n">
+      <x:c r="K22" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L20" s="44">
+      <x:c r="L22" s="20">
         <x:v>45883.2976041667</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B21" s="26" t="s"/>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="26" t="s"/>
-      <x:c r="G21" s="26" t="s"/>
-      <x:c r="H21" s="26" t="s"/>
-      <x:c r="I21" s="26" t="s"/>
-      <x:c r="J21" s="26" t="s"/>
-      <x:c r="K21" s="26" t="s"/>
-      <x:c r="L21" s="26" t="s"/>
-      <x:c r="M21" s="26" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B22" s="26" t="s"/>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="26" t="s"/>
-      <x:c r="G22" s="26" t="s"/>
-      <x:c r="H22" s="26" t="s"/>
-      <x:c r="I22" s="26" t="s"/>
-      <x:c r="J22" s="26" t="s"/>
-      <x:c r="K22" s="26" t="s"/>
-      <x:c r="L22" s="26" t="s"/>
-      <x:c r="M22" s="26" t="s"/>
+      <x:c r="M22" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C25" s="28" t="s"/>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="29" t="s"/>
+      <x:c r="B25" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="23" t="s"/>
+      <x:c r="F25" s="23" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C26" s="31" t="s"/>
-      <x:c r="D26" s="31" t="s"/>
-      <x:c r="E26" s="31" t="s"/>
-      <x:c r="F26" s="32" t="s">
-        <x:v>17</x:v>
+      <x:c r="B26" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="33" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C27" s="34" t="s"/>
-      <x:c r="D27" s="34" t="s"/>
-      <x:c r="E27" s="34" t="s"/>
-      <x:c r="F27" s="35" t="n">
+      <x:c r="B27" s="27" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="s"/>
+      <x:c r="D27" s="28" t="s"/>
+      <x:c r="E27" s="28" t="s"/>
+      <x:c r="F27" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="33" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C28" s="34" t="s"/>
-      <x:c r="D28" s="34" t="s"/>
-      <x:c r="E28" s="34" t="s"/>
-      <x:c r="F28" s="35" t="n">
+      <x:c r="B28" s="27" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="33" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C29" s="34" t="s"/>
-      <x:c r="D29" s="34" t="s"/>
-      <x:c r="E29" s="34" t="s"/>
-      <x:c r="F29" s="35" t="n">
+      <x:c r="B29" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="33" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C30" s="34" t="s"/>
-      <x:c r="D30" s="34" t="s"/>
-      <x:c r="E30" s="34" t="s"/>
-      <x:c r="F30" s="35" t="n">
+      <x:c r="B30" s="27" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C30" s="28" t="s"/>
+      <x:c r="D30" s="28" t="s"/>
+      <x:c r="E30" s="28" t="s"/>
+      <x:c r="F30" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="33" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C31" s="34" t="s"/>
-      <x:c r="D31" s="34" t="s"/>
-      <x:c r="E31" s="34" t="s"/>
-      <x:c r="F31" s="35" t="n">
+      <x:c r="B31" s="27" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C31" s="28" t="s"/>
+      <x:c r="D31" s="28" t="s"/>
+      <x:c r="E31" s="28" t="s"/>
+      <x:c r="F31" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="33" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C32" s="34" t="s"/>
-      <x:c r="D32" s="34" t="s"/>
-      <x:c r="E32" s="34" t="s"/>
-      <x:c r="F32" s="35" t="n">
+      <x:c r="B32" s="27" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C32" s="28" t="s"/>
+      <x:c r="D32" s="28" t="s"/>
+      <x:c r="E32" s="28" t="s"/>
+      <x:c r="F32" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C33" s="34" t="s"/>
-      <x:c r="D33" s="34" t="s"/>
-      <x:c r="E33" s="34" t="s"/>
-      <x:c r="F33" s="35" t="n">
+      <x:c r="B33" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C33" s="28" t="s"/>
+      <x:c r="D33" s="28" t="s"/>
+      <x:c r="E33" s="28" t="s"/>
+      <x:c r="F33" s="29" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C34" s="37" t="s"/>
-      <x:c r="D34" s="37" t="s"/>
-      <x:c r="E34" s="37" t="s"/>
-      <x:c r="F34" s="38" t="n">
+      <x:c r="B34" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C34" s="31" t="s"/>
+      <x:c r="D34" s="31" t="s"/>
+      <x:c r="E34" s="31" t="s"/>
+      <x:c r="F34" s="32" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -6721,18 +6689,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6750,367 +6706,379 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45883.0291898148</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45651</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346465</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45929.2261805556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45883.0965162037</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>2592.56</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45930.3001388889</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>25</x:v>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G8" s="21" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45883.0291898148</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346465</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45929.2261805556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45883.0965162037</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>2592.56</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45930.3001388889</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45908.5003472222</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>45790</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1215888</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>45911.952650463</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>45916.1691666667</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1215908</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>45929.1383449074</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
         <x:v>45888.154375</x:v>
       </x:c>
-      <x:c r="I10" s="42">
+      <x:c r="I12" s="18">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1215874</x:v>
       </x:c>
-      <x:c r="K10" s="43" t="n">
+      <x:c r="K12" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="44">
+      <x:c r="L12" s="20">
         <x:v>45902.050775463</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
+      <x:c r="M12" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>45877.1361111111</x:v>
       </x:c>
-      <x:c r="I11" s="42">
+      <x:c r="I13" s="18">
         <x:v>45909</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1346508</x:v>
       </x:c>
-      <x:c r="K11" s="43" t="n">
+      <x:c r="K13" s="19" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L11" s="44">
+      <x:c r="L13" s="20">
         <x:v>45908.1453009259</x:v>
       </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="39" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D12" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F12" s="39" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G12" s="39" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H12" s="41">
+      <x:c r="M13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
         <x:v>45924.1162962963</x:v>
       </x:c>
-      <x:c r="I12" s="42">
+      <x:c r="I14" s="18">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J12" s="40" t="n">
+      <x:c r="J14" s="16" t="n">
         <x:v>1215911</x:v>
       </x:c>
-      <x:c r="K12" s="43" t="n">
+      <x:c r="K14" s="19" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L12" s="44">
+      <x:c r="L14" s="20">
         <x:v>45930.063912037</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="26" t="s"/>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="26" t="s"/>
-      <x:c r="G13" s="26" t="s"/>
-      <x:c r="H13" s="26" t="s"/>
-      <x:c r="I13" s="26" t="s"/>
-      <x:c r="J13" s="26" t="s"/>
-      <x:c r="K13" s="26" t="s"/>
-      <x:c r="L13" s="26" t="s"/>
-      <x:c r="M13" s="26" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B14" s="26" t="s"/>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="26" t="s"/>
-      <x:c r="G14" s="26" t="s"/>
-      <x:c r="H14" s="26" t="s"/>
-      <x:c r="I14" s="26" t="s"/>
-      <x:c r="J14" s="26" t="s"/>
-      <x:c r="K14" s="26" t="s"/>
-      <x:c r="L14" s="26" t="s"/>
-      <x:c r="M14" s="26" t="s"/>
+      <x:c r="M14" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="29" t="s"/>
+      <x:c r="B17" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="23" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="s">
-        <x:v>17</x:v>
+      <x:c r="B18" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="33" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C19" s="34" t="s"/>
-      <x:c r="D19" s="34" t="s"/>
-      <x:c r="E19" s="34" t="s"/>
-      <x:c r="F19" s="35" t="n">
+      <x:c r="B19" s="27" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="33" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C20" s="34" t="s"/>
-      <x:c r="D20" s="34" t="s"/>
-      <x:c r="E20" s="34" t="s"/>
-      <x:c r="F20" s="35" t="n">
+      <x:c r="B20" s="27" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="34" t="s"/>
-      <x:c r="D21" s="34" t="s"/>
-      <x:c r="E21" s="34" t="s"/>
-      <x:c r="F21" s="35" t="n">
+      <x:c r="B21" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C22" s="37" t="s"/>
-      <x:c r="D22" s="37" t="s"/>
-      <x:c r="E22" s="37" t="s"/>
-      <x:c r="F22" s="38" t="n">
+      <x:c r="B22" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C22" s="31" t="s"/>
+      <x:c r="D22" s="31" t="s"/>
+      <x:c r="E22" s="31" t="s"/>
+      <x:c r="F22" s="32" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8206,18 +8174,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8235,240 +8191,252 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45947.5768287037</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>43437</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215960</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>17766</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45954.2191782407</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s"/>
-      <x:c r="H7" s="18">
-        <x:v>45925.0601967593</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>45922</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1215919</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45933.3037152778</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="B8" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45947.5768287037</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>43437</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215960</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>17766</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45954.2191782407</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s"/>
+      <x:c r="H9" s="12">
+        <x:v>45925.0601967593</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45922</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215919</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45933.3037152778</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45912.3032407407</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>45879</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1215920</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>4710</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>45933.3105324074</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>45931.5665277778</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>46297</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1215945</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>45940.1382060185</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="26" t="s"/>
-      <x:c r="C10" s="26" t="s"/>
-      <x:c r="D10" s="26" t="s"/>
-      <x:c r="E10" s="26" t="s"/>
-      <x:c r="F10" s="26" t="s"/>
-      <x:c r="G10" s="26" t="s"/>
-      <x:c r="H10" s="26" t="s"/>
-      <x:c r="I10" s="26" t="s"/>
-      <x:c r="J10" s="26" t="s"/>
-      <x:c r="K10" s="26" t="s"/>
-      <x:c r="L10" s="26" t="s"/>
-      <x:c r="M10" s="26" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="26" t="s"/>
-      <x:c r="C11" s="26" t="s"/>
-      <x:c r="D11" s="26" t="s"/>
-      <x:c r="E11" s="26" t="s"/>
-      <x:c r="F11" s="26" t="s"/>
-      <x:c r="G11" s="26" t="s"/>
-      <x:c r="H11" s="26" t="s"/>
-      <x:c r="I11" s="26" t="s"/>
-      <x:c r="J11" s="26" t="s"/>
-      <x:c r="K11" s="26" t="s"/>
-      <x:c r="L11" s="26" t="s"/>
-      <x:c r="M11" s="26" t="s"/>
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="29" t="s"/>
+      <x:c r="B14" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="31" t="s"/>
-      <x:c r="D15" s="31" t="s"/>
-      <x:c r="E15" s="31" t="s"/>
-      <x:c r="F15" s="32" t="s">
-        <x:v>17</x:v>
+      <x:c r="B15" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="33" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C16" s="34" t="s"/>
-      <x:c r="D16" s="34" t="s"/>
-      <x:c r="E16" s="34" t="s"/>
-      <x:c r="F16" s="35" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="34" t="s"/>
-      <x:c r="D17" s="34" t="s"/>
-      <x:c r="E17" s="34" t="s"/>
-      <x:c r="F17" s="35" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C18" s="37" t="s"/>
-      <x:c r="D18" s="37" t="s"/>
-      <x:c r="E18" s="37" t="s"/>
-      <x:c r="F18" s="38" t="n">
+      <x:c r="B18" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -9567,18 +9535,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9596,307 +9552,319 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45974.6184490741</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45682</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216021</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45986.0239236111</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45965.4411342593</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>45974</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216001</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45973.0179398148</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45974.6184490741</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45682</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216021</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45986.0239236111</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45965.4411342593</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45974</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216001</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45973.0179398148</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45971.2507291667</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1216006</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>45975.0756134259</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>45958.3516898148</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1215976</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>45967.2412384259</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
         <x:v>45954.2913425926</x:v>
       </x:c>
-      <x:c r="I10" s="42">
+      <x:c r="I12" s="18">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1216013</x:v>
       </x:c>
-      <x:c r="K10" s="43" t="n">
+      <x:c r="K12" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="44">
+      <x:c r="L12" s="20">
         <x:v>45975.3213541667</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
+      <x:c r="M12" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>45953.3174884259</x:v>
       </x:c>
-      <x:c r="I11" s="42">
+      <x:c r="I13" s="18">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1215996</x:v>
       </x:c>
-      <x:c r="K11" s="43" t="n">
+      <x:c r="K13" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="44">
+      <x:c r="L13" s="20">
         <x:v>45971.2990162037</x:v>
       </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="26" t="s"/>
-      <x:c r="C12" s="26" t="s"/>
-      <x:c r="D12" s="26" t="s"/>
-      <x:c r="E12" s="26" t="s"/>
-      <x:c r="F12" s="26" t="s"/>
-      <x:c r="G12" s="26" t="s"/>
-      <x:c r="H12" s="26" t="s"/>
-      <x:c r="I12" s="26" t="s"/>
-      <x:c r="J12" s="26" t="s"/>
-      <x:c r="K12" s="26" t="s"/>
-      <x:c r="L12" s="26" t="s"/>
-      <x:c r="M12" s="26" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="26" t="s"/>
-      <x:c r="C13" s="26" t="s"/>
-      <x:c r="D13" s="26" t="s"/>
-      <x:c r="E13" s="26" t="s"/>
-      <x:c r="F13" s="26" t="s"/>
-      <x:c r="G13" s="26" t="s"/>
-      <x:c r="H13" s="26" t="s"/>
-      <x:c r="I13" s="26" t="s"/>
-      <x:c r="J13" s="26" t="s"/>
-      <x:c r="K13" s="26" t="s"/>
-      <x:c r="L13" s="26" t="s"/>
-      <x:c r="M13" s="26" t="s"/>
+      <x:c r="M13" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="29" t="s"/>
+      <x:c r="B16" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="23" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="s">
-        <x:v>17</x:v>
+      <x:c r="B17" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="34" t="s"/>
-      <x:c r="D18" s="34" t="s"/>
-      <x:c r="E18" s="34" t="s"/>
-      <x:c r="F18" s="35" t="n">
+      <x:c r="B18" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C19" s="37" t="s"/>
-      <x:c r="D19" s="37" t="s"/>
-      <x:c r="E19" s="37" t="s"/>
-      <x:c r="F19" s="38" t="n">
+      <x:c r="B19" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="s"/>
+      <x:c r="D19" s="31" t="s"/>
+      <x:c r="E19" s="31" t="s"/>
+      <x:c r="F19" s="32" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -10993,18 +10961,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11022,242 +10978,254 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46000.4750694444</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216048</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46013.2950462963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46000.180775463</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46006.2645138889</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="B8" s="11" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46000.4750694444</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216048</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46013.2950462963</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46000.180775463</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46006.2645138889</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45972.0386111111</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1216033</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>46006.0795717593</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>45980.2173958333</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>45852</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1216027</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>45992.1151851852</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="26" t="s"/>
-      <x:c r="C10" s="26" t="s"/>
-      <x:c r="D10" s="26" t="s"/>
-      <x:c r="E10" s="26" t="s"/>
-      <x:c r="F10" s="26" t="s"/>
-      <x:c r="G10" s="26" t="s"/>
-      <x:c r="H10" s="26" t="s"/>
-      <x:c r="I10" s="26" t="s"/>
-      <x:c r="J10" s="26" t="s"/>
-      <x:c r="K10" s="26" t="s"/>
-      <x:c r="L10" s="26" t="s"/>
-      <x:c r="M10" s="26" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="26" t="s"/>
-      <x:c r="C11" s="26" t="s"/>
-      <x:c r="D11" s="26" t="s"/>
-      <x:c r="E11" s="26" t="s"/>
-      <x:c r="F11" s="26" t="s"/>
-      <x:c r="G11" s="26" t="s"/>
-      <x:c r="H11" s="26" t="s"/>
-      <x:c r="I11" s="26" t="s"/>
-      <x:c r="J11" s="26" t="s"/>
-      <x:c r="K11" s="26" t="s"/>
-      <x:c r="L11" s="26" t="s"/>
-      <x:c r="M11" s="26" t="s"/>
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="29" t="s"/>
+      <x:c r="B14" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="31" t="s"/>
-      <x:c r="D15" s="31" t="s"/>
-      <x:c r="E15" s="31" t="s"/>
-      <x:c r="F15" s="32" t="s">
-        <x:v>17</x:v>
+      <x:c r="B15" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="33" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C16" s="34" t="s"/>
-      <x:c r="D16" s="34" t="s"/>
-      <x:c r="E16" s="34" t="s"/>
-      <x:c r="F16" s="35" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="34" t="s"/>
-      <x:c r="D17" s="34" t="s"/>
-      <x:c r="E17" s="34" t="s"/>
-      <x:c r="F17" s="35" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C18" s="37" t="s"/>
-      <x:c r="D18" s="37" t="s"/>
-      <x:c r="E18" s="37" t="s"/>
-      <x:c r="F18" s="38" t="n">
+      <x:c r="B18" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12356,18 +12324,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -12385,231 +12341,243 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46007.1341435185</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216069</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46035.3042476852</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>173</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46034.1687615741</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216081</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46044.263275463</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46007.1341435185</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216069</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46035.3042476852</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46034.1687615741</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216081</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46044.263275463</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46014.1352083333</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1216066</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>46035.0802662037</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46014.4844097222</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1216060</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>46031.0514583333</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="26" t="s"/>
-      <x:c r="C10" s="26" t="s"/>
-      <x:c r="D10" s="26" t="s"/>
-      <x:c r="E10" s="26" t="s"/>
-      <x:c r="F10" s="26" t="s"/>
-      <x:c r="G10" s="26" t="s"/>
-      <x:c r="H10" s="26" t="s"/>
-      <x:c r="I10" s="26" t="s"/>
-      <x:c r="J10" s="26" t="s"/>
-      <x:c r="K10" s="26" t="s"/>
-      <x:c r="L10" s="26" t="s"/>
-      <x:c r="M10" s="26" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="26" t="s"/>
-      <x:c r="C11" s="26" t="s"/>
-      <x:c r="D11" s="26" t="s"/>
-      <x:c r="E11" s="26" t="s"/>
-      <x:c r="F11" s="26" t="s"/>
-      <x:c r="G11" s="26" t="s"/>
-      <x:c r="H11" s="26" t="s"/>
-      <x:c r="I11" s="26" t="s"/>
-      <x:c r="J11" s="26" t="s"/>
-      <x:c r="K11" s="26" t="s"/>
-      <x:c r="L11" s="26" t="s"/>
-      <x:c r="M11" s="26" t="s"/>
+      <x:c r="M11" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="29" t="s"/>
+      <x:c r="B14" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="31" t="s"/>
-      <x:c r="D15" s="31" t="s"/>
-      <x:c r="E15" s="31" t="s"/>
-      <x:c r="F15" s="32" t="s">
-        <x:v>17</x:v>
+      <x:c r="B15" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="34" t="s"/>
-      <x:c r="D16" s="34" t="s"/>
-      <x:c r="E16" s="34" t="s"/>
-      <x:c r="F16" s="35" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C17" s="37" t="s"/>
-      <x:c r="D17" s="37" t="s"/>
-      <x:c r="E17" s="37" t="s"/>
-      <x:c r="F17" s="38" t="n">
+      <x:c r="B17" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13708,18 +13676,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -13737,508 +13693,520 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46051.2691319444</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46051.2691550926</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216103</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>2070</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46057.9587152778</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46051.1259722222</x:v>
-      </x:c>
-      <x:c r="I7" s="19">
-        <x:v>46053</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216112</x:v>
-      </x:c>
-      <x:c r="K7" s="20" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46062.966400463</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="21" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="21" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F8" s="21" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G8" s="21" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H8" s="22">
+      <x:c r="B8" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46051.2691319444</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46051.2691550926</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216103</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46057.9587152778</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46051.1259722222</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46053</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216112</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46062.966400463</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46050.2853935185</x:v>
       </x:c>
-      <x:c r="I8" s="23">
+      <x:c r="I10" s="18">
         <x:v>45945</x:v>
       </x:c>
-      <x:c r="J8" s="21" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1216106</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="K10" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="22">
+      <x:c r="L10" s="20">
         <x:v>46058.0440046296</x:v>
       </x:c>
-      <x:c r="M8" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="21" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="21" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="21" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F9" s="21" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G9" s="21" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H9" s="22">
+      <x:c r="M10" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
         <x:v>46066.1892939815</x:v>
       </x:c>
-      <x:c r="I9" s="23">
+      <x:c r="I11" s="18">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J9" s="21" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1216131</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="K11" s="19" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L9" s="22">
+      <x:c r="L11" s="20">
         <x:v>46076.0521180556</x:v>
       </x:c>
-      <x:c r="M9" s="21" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="D10" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="39" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F10" s="39" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G10" s="39" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H10" s="41">
+      <x:c r="M11" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
         <x:v>46066.186087963</x:v>
       </x:c>
-      <x:c r="I10" s="42">
+      <x:c r="I12" s="18">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>1216130</x:v>
       </x:c>
-      <x:c r="K10" s="43" t="n">
+      <x:c r="K12" s="19" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L10" s="44">
+      <x:c r="L12" s="20">
         <x:v>46076.0476273148</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="39" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D11" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="39" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F11" s="39" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="G11" s="39" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="H11" s="41">
+      <x:c r="M12" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
         <x:v>46057.2800462963</x:v>
       </x:c>
-      <x:c r="I11" s="42">
+      <x:c r="I13" s="18">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>1216117</x:v>
       </x:c>
-      <x:c r="K11" s="43" t="n">
+      <x:c r="K13" s="19" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L11" s="44">
+      <x:c r="L13" s="20">
         <x:v>46065.2796412037</x:v>
       </x:c>
-      <x:c r="M11" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="39" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D12" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F12" s="39" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G12" s="39" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H12" s="41">
+      <x:c r="M13" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
         <x:v>46057.272025463</x:v>
       </x:c>
-      <x:c r="I12" s="42">
+      <x:c r="I14" s="18">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="J12" s="40" t="n">
+      <x:c r="J14" s="16" t="n">
         <x:v>1216121</x:v>
       </x:c>
-      <x:c r="K12" s="43" t="n">
+      <x:c r="K14" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="44">
+      <x:c r="L14" s="20">
         <x:v>46065.2951388889</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="39" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D13" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E13" s="39" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F13" s="39" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G13" s="39" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H13" s="41">
+      <x:c r="M14" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
         <x:v>46057.2657523148</x:v>
       </x:c>
-      <x:c r="I13" s="42">
+      <x:c r="I15" s="18">
         <x:v>46039</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>1216119</x:v>
       </x:c>
-      <x:c r="K13" s="43" t="n">
+      <x:c r="K15" s="19" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="44">
+      <x:c r="L15" s="20">
         <x:v>46065.285474537</x:v>
       </x:c>
-      <x:c r="M13" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="39" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D14" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="39" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F14" s="39" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G14" s="39" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H14" s="41">
+      <x:c r="M15" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
         <x:v>46056.1690046296</x:v>
       </x:c>
-      <x:c r="I14" s="42">
+      <x:c r="I16" s="18">
         <x:v>45716</x:v>
       </x:c>
-      <x:c r="J14" s="40" t="n">
+      <x:c r="J16" s="16" t="n">
         <x:v>1216107</x:v>
       </x:c>
-      <x:c r="K14" s="43" t="n">
+      <x:c r="K16" s="19" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L14" s="44">
+      <x:c r="L16" s="20">
         <x:v>46058.1034490741</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="39" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D15" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E15" s="39" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="F15" s="39" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G15" s="39" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="H15" s="41">
+      <x:c r="M16" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
         <x:v>46065.2312962963</x:v>
       </x:c>
-      <x:c r="I15" s="42">
+      <x:c r="I17" s="18">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J17" s="16" t="n">
         <x:v>1216134</x:v>
       </x:c>
-      <x:c r="K15" s="43" t="n">
+      <x:c r="K17" s="19" t="n">
         <x:v>2190</x:v>
       </x:c>
-      <x:c r="L15" s="44">
+      <x:c r="L17" s="20">
         <x:v>46076.0858333333</x:v>
       </x:c>
-      <x:c r="M15" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="39" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="D16" s="40" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E16" s="39" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F16" s="39" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G16" s="39" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H16" s="41">
+      <x:c r="M17" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
         <x:v>46063.0357060185</x:v>
       </x:c>
-      <x:c r="I16" s="42">
+      <x:c r="I18" s="18">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J16" s="40" t="n">
+      <x:c r="J18" s="16" t="n">
         <x:v>1216123</x:v>
       </x:c>
-      <x:c r="K16" s="43" t="n">
+      <x:c r="K18" s="19" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L16" s="44">
+      <x:c r="L18" s="20">
         <x:v>46066.0203819444</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B17" s="26" t="s"/>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="26" t="s"/>
-      <x:c r="G17" s="26" t="s"/>
-      <x:c r="H17" s="26" t="s"/>
-      <x:c r="I17" s="26" t="s"/>
-      <x:c r="J17" s="26" t="s"/>
-      <x:c r="K17" s="26" t="s"/>
-      <x:c r="L17" s="26" t="s"/>
-      <x:c r="M17" s="26" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B18" s="26" t="s"/>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="26" t="s"/>
-      <x:c r="G18" s="26" t="s"/>
-      <x:c r="H18" s="26" t="s"/>
-      <x:c r="I18" s="26" t="s"/>
-      <x:c r="J18" s="26" t="s"/>
-      <x:c r="K18" s="26" t="s"/>
-      <x:c r="L18" s="26" t="s"/>
-      <x:c r="M18" s="26" t="s"/>
+      <x:c r="M18" s="15" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="29" t="s"/>
+      <x:c r="B21" s="21" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="23" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C22" s="31" t="s"/>
-      <x:c r="D22" s="31" t="s"/>
-      <x:c r="E22" s="31" t="s"/>
-      <x:c r="F22" s="32" t="s">
-        <x:v>17</x:v>
+      <x:c r="B22" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="33" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C23" s="34" t="s"/>
-      <x:c r="D23" s="34" t="s"/>
-      <x:c r="E23" s="34" t="s"/>
-      <x:c r="F23" s="35" t="n">
+      <x:c r="B23" s="27" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C23" s="28" t="s"/>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="28" t="s"/>
+      <x:c r="F23" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C24" s="34" t="s"/>
-      <x:c r="D24" s="34" t="s"/>
-      <x:c r="E24" s="34" t="s"/>
-      <x:c r="F24" s="35" t="n">
+      <x:c r="B24" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C24" s="28" t="s"/>
+      <x:c r="D24" s="28" t="s"/>
+      <x:c r="E24" s="28" t="s"/>
+      <x:c r="F24" s="29" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C25" s="37" t="s"/>
-      <x:c r="D25" s="37" t="s"/>
-      <x:c r="E25" s="37" t="s"/>
-      <x:c r="F25" s="38" t="n">
+      <x:c r="B25" s="30" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C25" s="31" t="s"/>
+      <x:c r="D25" s="31" t="s"/>
+      <x:c r="E25" s="31" t="s"/>
+      <x:c r="F25" s="32" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1223,9 +1223,12 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1298,7 +1301,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1328,6 +1331,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1666,7 +1673,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1738,732 +1747,732 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46076.1792361111</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216147</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46090.2042708333</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46072.0333449074</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216156</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46090.2584837963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>46071.1677662037</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1216165</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>46091.1948842593</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="16" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="16" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="18">
         <x:v>46070.1768402778</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="19">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1216138</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="21">
         <x:v>46084.1495138889</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="16" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="16" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="16" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="16" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="18">
         <x:v>46076.1139583333</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="19">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="17" t="n">
         <x:v>1216146</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="21">
         <x:v>46090.1919444444</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="16" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="16" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="16" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="16" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="18">
         <x:v>46071.3305671296</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I13" s="19">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="17" t="n">
         <x:v>1216193</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="21">
         <x:v>46094.1906365741</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="16" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="16" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="16" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="16" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="18">
         <x:v>46072.0792939815</x:v>
       </x:c>
-      <x:c r="I14" s="18">
+      <x:c r="I14" s="19">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
+      <x:c r="J14" s="17" t="n">
         <x:v>1216150</x:v>
       </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="K14" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="20">
+      <x:c r="L14" s="21">
         <x:v>46090.220787037</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="16" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="16" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="16" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="16" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="18">
         <x:v>46077.2598726852</x:v>
       </x:c>
-      <x:c r="I15" s="18">
+      <x:c r="I15" s="19">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="n">
+      <x:c r="J15" s="17" t="n">
         <x:v>1216158</x:v>
       </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="K15" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="20">
+      <x:c r="L15" s="21">
         <x:v>46090.2758680556</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="16" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="16" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="16" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="16" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="18">
         <x:v>46072.1089467593</x:v>
       </x:c>
-      <x:c r="I16" s="18">
+      <x:c r="I16" s="19">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="n">
+      <x:c r="J16" s="17" t="n">
         <x:v>1216152</x:v>
       </x:c>
-      <x:c r="K16" s="19" t="n">
+      <x:c r="K16" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="20">
+      <x:c r="L16" s="21">
         <x:v>46090.2365046296</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="16" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="16" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="16" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="16" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="18">
         <x:v>46077.5191782407</x:v>
       </x:c>
-      <x:c r="I17" s="18">
+      <x:c r="I17" s="19">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="n">
+      <x:c r="J17" s="17" t="n">
         <x:v>1216163</x:v>
       </x:c>
-      <x:c r="K17" s="19" t="n">
+      <x:c r="K17" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="20">
+      <x:c r="L17" s="21">
         <x:v>46090.3154976852</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="16" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="16" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="16" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="16" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="18">
         <x:v>46077.4722337963</x:v>
       </x:c>
-      <x:c r="I18" s="18">
+      <x:c r="I18" s="19">
         <x:v>46030</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="n">
+      <x:c r="J18" s="17" t="n">
         <x:v>1216161</x:v>
       </x:c>
-      <x:c r="K18" s="19" t="n">
+      <x:c r="K18" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L18" s="20">
+      <x:c r="L18" s="21">
         <x:v>46090.2963078704</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="16" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="16" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="16" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="16" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="18">
         <x:v>46077.2024189815</x:v>
       </x:c>
-      <x:c r="I19" s="18">
+      <x:c r="I19" s="19">
         <x:v>45948</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="n">
+      <x:c r="J19" s="17" t="n">
         <x:v>1216154</x:v>
       </x:c>
-      <x:c r="K19" s="19" t="n">
+      <x:c r="K19" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L19" s="20">
+      <x:c r="L19" s="21">
         <x:v>46090.2495949074</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="16" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="16" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="16" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="16" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="18">
         <x:v>46072.0497337963</x:v>
       </x:c>
-      <x:c r="I20" s="18">
+      <x:c r="I20" s="19">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="n">
+      <x:c r="J20" s="17" t="n">
         <x:v>1216148</x:v>
       </x:c>
-      <x:c r="K20" s="19" t="n">
+      <x:c r="K20" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L20" s="20">
+      <x:c r="L20" s="21">
         <x:v>46090.2102430556</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="16" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="16" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="16" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="16" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="18">
         <x:v>46071.2285416667</x:v>
       </x:c>
-      <x:c r="I21" s="18">
+      <x:c r="I21" s="19">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="n">
+      <x:c r="J21" s="17" t="n">
         <x:v>1216143</x:v>
       </x:c>
-      <x:c r="K21" s="19" t="n">
+      <x:c r="K21" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L21" s="20">
+      <x:c r="L21" s="21">
         <x:v>46090.0772916667</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="16" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="16" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="16" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="16" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="18">
         <x:v>46071.2072569444</x:v>
       </x:c>
-      <x:c r="I22" s="18">
+      <x:c r="I22" s="19">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="n">
+      <x:c r="J22" s="17" t="n">
         <x:v>1216142</x:v>
       </x:c>
-      <x:c r="K22" s="19" t="n">
+      <x:c r="K22" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L22" s="20">
+      <x:c r="L22" s="21">
         <x:v>46090.0616666667</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="16" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
+      <x:c r="D23" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="E23" s="16" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="16" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="16" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="18">
         <x:v>46079.0151851852</x:v>
       </x:c>
-      <x:c r="I23" s="18">
+      <x:c r="I23" s="19">
         <x:v>45602</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="n">
+      <x:c r="J23" s="17" t="n">
         <x:v>1216174</x:v>
       </x:c>
-      <x:c r="K23" s="19" t="n">
+      <x:c r="K23" s="20" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L23" s="20">
+      <x:c r="L23" s="21">
         <x:v>46093.1514351852</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="16" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="16" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="16" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="16" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="18">
         <x:v>45988.1893402778</x:v>
       </x:c>
-      <x:c r="I24" s="18">
+      <x:c r="I24" s="19">
         <x:v>45973</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="n">
+      <x:c r="J24" s="17" t="n">
         <x:v>1216173</x:v>
       </x:c>
-      <x:c r="K24" s="19" t="n">
+      <x:c r="K24" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L24" s="20">
+      <x:c r="L24" s="21">
         <x:v>46093.1383912037</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="21" t="s">
+      <x:c r="B27" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C27" s="22" t="s"/>
-      <x:c r="D27" s="22" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="23" t="s"/>
+      <x:c r="C27" s="23" t="s"/>
+      <x:c r="D27" s="23" t="s"/>
+      <x:c r="E27" s="24" t="s"/>
+      <x:c r="F27" s="24" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="24" t="s">
+      <x:c r="B28" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C28" s="25" t="s"/>
-      <x:c r="D28" s="25" t="s"/>
-      <x:c r="E28" s="25" t="s"/>
-      <x:c r="F28" s="26" t="s">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="27" t="s">
+      <x:c r="B29" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
+      <x:c r="C29" s="29" t="s"/>
+      <x:c r="D29" s="29" t="s"/>
+      <x:c r="E29" s="29" t="s"/>
+      <x:c r="F29" s="30" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="30" t="s">
+      <x:c r="B30" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C30" s="31" t="s"/>
-      <x:c r="D30" s="31" t="s"/>
-      <x:c r="E30" s="31" t="s"/>
-      <x:c r="F30" s="32" t="n">
+      <x:c r="C30" s="32" t="s"/>
+      <x:c r="D30" s="32" t="s"/>
+      <x:c r="E30" s="32" t="s"/>
+      <x:c r="F30" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3499,7 +3508,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45839</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -3571,200 +3582,200 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45862.256875</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45908</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215838</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45862.3066319444</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45861.1595717593</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46238</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1215833</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45862.1034606481</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>45861.1361574074</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1215836</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>45862.1391203704</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="23" t="s"/>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="24" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="24" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="s">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
+      <x:c r="B15" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="29" t="s"/>
+      <x:c r="F15" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
+      <x:c r="B16" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="C16" s="32" t="s"/>
+      <x:c r="D16" s="32" t="s"/>
+      <x:c r="E16" s="32" t="s"/>
+      <x:c r="F16" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -4814,7 +4825,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45870</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -4886,722 +4899,722 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45877.1309490741</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>45877.1309606481</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1346451</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45877.1897222222</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45882.0658796296</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>45882.0658912037</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1195701</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>2496</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45883.2549537037</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>45881.0630902778</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>45885</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1346453</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>45881.0887037037</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="16" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="16" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="18">
         <x:v>45897.2535648148</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="19">
         <x:v>45847</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1346494</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="21">
         <x:v>45897.2982407407</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="16" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="16" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="16" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="18">
         <x:v>45881.3064236111</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="19">
         <x:v>45871</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="17" t="n">
         <x:v>1195693</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="20" t="n">
         <x:v>4275</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="21">
         <x:v>45897.0449189815</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="16" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="16" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="17" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="16" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="16" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="16" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="18">
         <x:v>45870.3069328704</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I13" s="19">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="17" t="n">
         <x:v>1346441</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="20" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="21">
         <x:v>45883.1603356482</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="16" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="16" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="17" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="16" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="16" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="16" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="18">
         <x:v>45874.1403125</x:v>
       </x:c>
-      <x:c r="I14" s="18">
+      <x:c r="I14" s="19">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
+      <x:c r="J14" s="17" t="n">
         <x:v>1346447</x:v>
       </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="K14" s="20" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L14" s="20">
+      <x:c r="L14" s="21">
         <x:v>45874.2281365741</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="16" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="16" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="16" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="16" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="16" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="18">
         <x:v>45883.1346180556</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="18">
         <x:v>45883.1346296296</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="n">
+      <x:c r="J15" s="17" t="n">
         <x:v>1346466</x:v>
       </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="K15" s="20" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L15" s="20">
+      <x:c r="L15" s="21">
         <x:v>45883.1693055556</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="16" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="16" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="16" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="16" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="18">
         <x:v>45887.5652430556</x:v>
       </x:c>
-      <x:c r="I16" s="18">
+      <x:c r="I16" s="19">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="n">
+      <x:c r="J16" s="17" t="n">
         <x:v>1215872</x:v>
       </x:c>
-      <x:c r="K16" s="19" t="n">
+      <x:c r="K16" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="20">
+      <x:c r="L16" s="21">
         <x:v>45896.2365393518</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="16" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="16" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="16" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="16" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="18">
         <x:v>45873.2842013889</x:v>
       </x:c>
-      <x:c r="I17" s="18">
+      <x:c r="I17" s="19">
         <x:v>45544</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="n">
+      <x:c r="J17" s="17" t="n">
         <x:v>1346446</x:v>
       </x:c>
-      <x:c r="K17" s="19" t="n">
+      <x:c r="K17" s="20" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L17" s="20">
+      <x:c r="L17" s="21">
         <x:v>45873.3539814815</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="16" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="16" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="16" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="16" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="18">
         <x:v>45891.1735648148</x:v>
       </x:c>
-      <x:c r="I18" s="18">
+      <x:c r="I18" s="19">
         <x:v>45765</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="n">
+      <x:c r="J18" s="17" t="n">
         <x:v>1215865</x:v>
       </x:c>
-      <x:c r="K18" s="19" t="n">
+      <x:c r="K18" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L18" s="20">
+      <x:c r="L18" s="21">
         <x:v>45898.0611111111</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="16" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="16" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="16" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="16" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="18">
         <x:v>45883.1535763889</x:v>
       </x:c>
-      <x:c r="I19" s="18">
+      <x:c r="I19" s="19">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="n">
+      <x:c r="J19" s="17" t="n">
         <x:v>1346468</x:v>
       </x:c>
-      <x:c r="K19" s="19" t="n">
+      <x:c r="K19" s="20" t="n">
         <x:v>4350</x:v>
       </x:c>
-      <x:c r="L19" s="20">
+      <x:c r="L19" s="21">
         <x:v>45883.2560300926</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="16" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="16" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="16" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="16" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="18">
         <x:v>45879.4885069444</x:v>
       </x:c>
-      <x:c r="I20" s="18">
+      <x:c r="I20" s="19">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="n">
+      <x:c r="J20" s="17" t="n">
         <x:v>1215863</x:v>
       </x:c>
-      <x:c r="K20" s="19" t="n">
+      <x:c r="K20" s="20" t="n">
         <x:v>1650</x:v>
       </x:c>
-      <x:c r="L20" s="20">
+      <x:c r="L20" s="21">
         <x:v>45884.277650463</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="16" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="16" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="16" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="16" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="18">
         <x:v>45887.5590162037</x:v>
       </x:c>
-      <x:c r="I21" s="18">
+      <x:c r="I21" s="19">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="n">
+      <x:c r="J21" s="17" t="n">
         <x:v>1215870</x:v>
       </x:c>
-      <x:c r="K21" s="19" t="n">
+      <x:c r="K21" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L21" s="20">
+      <x:c r="L21" s="21">
         <x:v>45896.237962963</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="16" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="16" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="16" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="16" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="18">
         <x:v>45881.2806365741</x:v>
       </x:c>
-      <x:c r="I22" s="18">
+      <x:c r="I22" s="19">
         <x:v>45892</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="n">
+      <x:c r="J22" s="17" t="n">
         <x:v>1346470</x:v>
       </x:c>
-      <x:c r="K22" s="19" t="n">
+      <x:c r="K22" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L22" s="20">
+      <x:c r="L22" s="21">
         <x:v>45883.2976041667</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="21" t="s">
+      <x:c r="B25" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="23" t="s"/>
-      <x:c r="F25" s="23" t="s"/>
+      <x:c r="C25" s="23" t="s"/>
+      <x:c r="D25" s="23" t="s"/>
+      <x:c r="E25" s="24" t="s"/>
+      <x:c r="F25" s="24" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="24" t="s">
+      <x:c r="B26" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C26" s="25" t="s"/>
-      <x:c r="D26" s="25" t="s"/>
-      <x:c r="E26" s="25" t="s"/>
-      <x:c r="F26" s="26" t="s">
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="27" t="s">
+      <x:c r="B27" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="27" t="s">
+      <x:c r="B28" s="28" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="n">
+      <x:c r="C28" s="29" t="s"/>
+      <x:c r="D28" s="29" t="s"/>
+      <x:c r="E28" s="29" t="s"/>
+      <x:c r="F28" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="27" t="s">
+      <x:c r="B29" s="28" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
+      <x:c r="C29" s="29" t="s"/>
+      <x:c r="D29" s="29" t="s"/>
+      <x:c r="E29" s="29" t="s"/>
+      <x:c r="F29" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="27" t="s">
+      <x:c r="B30" s="28" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C30" s="28" t="s"/>
-      <x:c r="D30" s="28" t="s"/>
-      <x:c r="E30" s="28" t="s"/>
-      <x:c r="F30" s="29" t="n">
+      <x:c r="C30" s="29" t="s"/>
+      <x:c r="D30" s="29" t="s"/>
+      <x:c r="E30" s="29" t="s"/>
+      <x:c r="F30" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="27" t="s">
+      <x:c r="B31" s="28" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C31" s="28" t="s"/>
-      <x:c r="D31" s="28" t="s"/>
-      <x:c r="E31" s="28" t="s"/>
-      <x:c r="F31" s="29" t="n">
+      <x:c r="C31" s="29" t="s"/>
+      <x:c r="D31" s="29" t="s"/>
+      <x:c r="E31" s="29" t="s"/>
+      <x:c r="F31" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="27" t="s">
+      <x:c r="B32" s="28" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C32" s="28" t="s"/>
-      <x:c r="D32" s="28" t="s"/>
-      <x:c r="E32" s="28" t="s"/>
-      <x:c r="F32" s="29" t="n">
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="27" t="s">
+      <x:c r="B33" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C33" s="28" t="s"/>
-      <x:c r="D33" s="28" t="s"/>
-      <x:c r="E33" s="28" t="s"/>
-      <x:c r="F33" s="29" t="n">
+      <x:c r="C33" s="29" t="s"/>
+      <x:c r="D33" s="29" t="s"/>
+      <x:c r="E33" s="29" t="s"/>
+      <x:c r="F33" s="30" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="30" t="s">
+      <x:c r="B34" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C34" s="31" t="s"/>
-      <x:c r="D34" s="31" t="s"/>
-      <x:c r="E34" s="31" t="s"/>
-      <x:c r="F34" s="32" t="n">
+      <x:c r="C34" s="32" t="s"/>
+      <x:c r="D34" s="32" t="s"/>
+      <x:c r="E34" s="32" t="s"/>
+      <x:c r="F34" s="33" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -6639,7 +6652,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45901</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -6711,374 +6726,374 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45883.0291898148</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45651</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1346465</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>642</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45929.2261805556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45883.0965162037</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="s">
+      <x:c r="J9" s="12" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>2592.56</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45930.3001388889</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>45908.5003472222</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>45790</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1215888</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>45911.952650463</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="16" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="16" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="18">
         <x:v>45916.1691666667</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="19">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1215908</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="21">
         <x:v>45929.1383449074</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="16" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="16" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="16" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="16" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="18">
         <x:v>45888.154375</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="19">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="17" t="n">
         <x:v>1215874</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="21">
         <x:v>45902.050775463</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="16" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="16" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="16" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="16" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="18">
         <x:v>45877.1361111111</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I13" s="19">
         <x:v>45909</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="17" t="n">
         <x:v>1346508</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="20" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="21">
         <x:v>45908.1453009259</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="16" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="16" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="16" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="16" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="18">
         <x:v>45924.1162962963</x:v>
       </x:c>
-      <x:c r="I14" s="18">
+      <x:c r="I14" s="19">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
+      <x:c r="J14" s="17" t="n">
         <x:v>1215911</x:v>
       </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="K14" s="20" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L14" s="20">
+      <x:c r="L14" s="21">
         <x:v>45930.063912037</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="21" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="23" t="s"/>
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="24" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="24" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="s">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
+      <x:c r="B19" s="28" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="27" t="s">
+      <x:c r="B20" s="28" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
+      <x:c r="B21" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
+      <x:c r="C21" s="29" t="s"/>
+      <x:c r="D21" s="29" t="s"/>
+      <x:c r="E21" s="29" t="s"/>
+      <x:c r="F21" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="30" t="s">
+      <x:c r="B22" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C22" s="31" t="s"/>
-      <x:c r="D22" s="31" t="s"/>
-      <x:c r="E22" s="31" t="s"/>
-      <x:c r="F22" s="32" t="n">
+      <x:c r="C22" s="32" t="s"/>
+      <x:c r="D22" s="32" t="s"/>
+      <x:c r="E22" s="32" t="s"/>
+      <x:c r="F22" s="33" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8124,7 +8139,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45931</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -8196,247 +8213,247 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45947.5768287037</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>43437</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215960</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>17766</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45954.2191782407</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s"/>
-      <x:c r="H9" s="12">
+      <x:c r="G9" s="12" t="s"/>
+      <x:c r="H9" s="13">
         <x:v>45925.0601967593</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45922</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1215919</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45933.3037152778</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>45912.3032407407</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>45879</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1215920</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>4710</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>45933.3105324074</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="16" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="16" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="18">
         <x:v>45931.5665277778</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="19">
         <x:v>46297</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1215945</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="21">
         <x:v>45940.1382060185</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="24" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="30" t="s">
+      <x:c r="B18" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -9485,7 +9502,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45962</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -9557,314 +9576,314 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45974.6184490741</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45682</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216021</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45986.0239236111</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45965.4411342593</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216001</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45973.0179398148</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>45971.2507291667</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1216006</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>45975.0756134259</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="16" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="16" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="18">
         <x:v>45958.3516898148</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="19">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1215976</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="21">
         <x:v>45967.2412384259</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="16" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="16" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="16" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="16" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="18">
         <x:v>45954.2913425926</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="19">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="17" t="n">
         <x:v>1216013</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="21">
         <x:v>45975.3213541667</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="16" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="16" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="16" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="16" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="18">
         <x:v>45953.3174884259</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I13" s="19">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="17" t="n">
         <x:v>1215996</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="21">
         <x:v>45971.2990162037</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="23" t="s"/>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="24" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="s">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="30" t="s">
+      <x:c r="B19" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C19" s="31" t="s"/>
-      <x:c r="D19" s="31" t="s"/>
-      <x:c r="E19" s="31" t="s"/>
-      <x:c r="F19" s="32" t="n">
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -10911,7 +10930,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45992</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -10983,249 +11004,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46000.4750694444</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216048</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>744</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46013.2950462963</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46000.180775463</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216037</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46006.2645138889</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>45972.0386111111</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1216033</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>46006.0795717593</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="16" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="16" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="18">
         <x:v>45980.2173958333</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="19">
         <x:v>45852</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1216027</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="21">
         <x:v>45992.1151851852</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="24" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="30" t="s">
+      <x:c r="B18" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="C18" s="32" t="s"/>
+      <x:c r="D18" s="32" t="s"/>
+      <x:c r="E18" s="32" t="s"/>
+      <x:c r="F18" s="33" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12274,7 +12295,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46023</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -12346,238 +12369,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46007.1341435185</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216069</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46035.3042476852</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46034.1687615741</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216081</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46044.263275463</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>46014.1352083333</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1216066</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>46035.0802662037</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="16" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="16" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="18">
         <x:v>46014.4844097222</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="19">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1216060</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="21">
         <x:v>46031.0514583333</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="16" t="s">
         <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="24" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="30" t="s">
+      <x:c r="B17" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
+      <x:c r="C17" s="32" t="s"/>
+      <x:c r="D17" s="32" t="s"/>
+      <x:c r="E17" s="32" t="s"/>
+      <x:c r="F17" s="33" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13626,7 +13649,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46054</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -13698,515 +13723,515 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46051.2691319444</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46051.2691550926</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216103</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46057.9587152778</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46051.1259722222</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216112</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46062.966400463</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="16" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="16" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="16" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="18">
         <x:v>46050.2853935185</x:v>
       </x:c>
-      <x:c r="I10" s="18">
+      <x:c r="I10" s="19">
         <x:v>45945</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>1216106</x:v>
       </x:c>
-      <x:c r="K10" s="19" t="n">
+      <x:c r="K10" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="20">
+      <x:c r="L10" s="21">
         <x:v>46058.0440046296</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="16" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="16" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="18">
         <x:v>46066.1892939815</x:v>
       </x:c>
-      <x:c r="I11" s="18">
+      <x:c r="I11" s="19">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>1216131</x:v>
       </x:c>
-      <x:c r="K11" s="19" t="n">
+      <x:c r="K11" s="20" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L11" s="20">
+      <x:c r="L11" s="21">
         <x:v>46076.0521180556</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="16" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="16" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="16" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="16" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="18">
         <x:v>46066.186087963</x:v>
       </x:c>
-      <x:c r="I12" s="18">
+      <x:c r="I12" s="19">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="n">
+      <x:c r="J12" s="17" t="n">
         <x:v>1216130</x:v>
       </x:c>
-      <x:c r="K12" s="19" t="n">
+      <x:c r="K12" s="20" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L12" s="20">
+      <x:c r="L12" s="21">
         <x:v>46076.0476273148</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="16" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="16" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="16" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="16" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="18">
         <x:v>46057.2800462963</x:v>
       </x:c>
-      <x:c r="I13" s="18">
+      <x:c r="I13" s="19">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="n">
+      <x:c r="J13" s="17" t="n">
         <x:v>1216117</x:v>
       </x:c>
-      <x:c r="K13" s="19" t="n">
+      <x:c r="K13" s="20" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L13" s="20">
+      <x:c r="L13" s="21">
         <x:v>46065.2796412037</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="16" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="16" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="16" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="16" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="18">
         <x:v>46057.272025463</x:v>
       </x:c>
-      <x:c r="I14" s="18">
+      <x:c r="I14" s="19">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="n">
+      <x:c r="J14" s="17" t="n">
         <x:v>1216121</x:v>
       </x:c>
-      <x:c r="K14" s="19" t="n">
+      <x:c r="K14" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="20">
+      <x:c r="L14" s="21">
         <x:v>46065.2951388889</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="16" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="16" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="16" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="16" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="18">
         <x:v>46057.2657523148</x:v>
       </x:c>
-      <x:c r="I15" s="18">
+      <x:c r="I15" s="19">
         <x:v>46039</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="n">
+      <x:c r="J15" s="17" t="n">
         <x:v>1216119</x:v>
       </x:c>
-      <x:c r="K15" s="19" t="n">
+      <x:c r="K15" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="20">
+      <x:c r="L15" s="21">
         <x:v>46065.285474537</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="16" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="16" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="16" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="16" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="18">
         <x:v>46056.1690046296</x:v>
       </x:c>
-      <x:c r="I16" s="18">
+      <x:c r="I16" s="19">
         <x:v>45716</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="n">
+      <x:c r="J16" s="17" t="n">
         <x:v>1216107</x:v>
       </x:c>
-      <x:c r="K16" s="19" t="n">
+      <x:c r="K16" s="20" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L16" s="20">
+      <x:c r="L16" s="21">
         <x:v>46058.1034490741</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="16" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="16" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="16" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="16" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="18">
         <x:v>46065.2312962963</x:v>
       </x:c>
-      <x:c r="I17" s="18">
+      <x:c r="I17" s="19">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="n">
+      <x:c r="J17" s="17" t="n">
         <x:v>1216134</x:v>
       </x:c>
-      <x:c r="K17" s="19" t="n">
+      <x:c r="K17" s="20" t="n">
         <x:v>2190</x:v>
       </x:c>
-      <x:c r="L17" s="20">
+      <x:c r="L17" s="21">
         <x:v>46076.0858333333</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="16" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="16" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="16" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="16" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="16" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="18">
         <x:v>46063.0357060185</x:v>
       </x:c>
-      <x:c r="I18" s="18">
+      <x:c r="I18" s="19">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="n">
+      <x:c r="J18" s="17" t="n">
         <x:v>1216123</x:v>
       </x:c>
-      <x:c r="K18" s="19" t="n">
+      <x:c r="K18" s="20" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L18" s="20">
+      <x:c r="L18" s="21">
         <x:v>46066.0203819444</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="23" t="s"/>
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="24" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="24" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="s">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="27" t="s">
+      <x:c r="B23" s="28" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C23" s="28" t="s"/>
-      <x:c r="D23" s="28" t="s"/>
-      <x:c r="E23" s="28" t="s"/>
-      <x:c r="F23" s="29" t="n">
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="27" t="s">
+      <x:c r="B24" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C24" s="28" t="s"/>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="28" t="s"/>
-      <x:c r="F24" s="29" t="n">
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="30" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="30" t="s">
+      <x:c r="B25" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C25" s="31" t="s"/>
-      <x:c r="D25" s="31" t="s"/>
-      <x:c r="E25" s="31" t="s"/>
-      <x:c r="F25" s="32" t="n">
+      <x:c r="C25" s="32" t="s"/>
+      <x:c r="D25" s="32" t="s"/>
+      <x:c r="E25" s="32" t="s"/>
+      <x:c r="F25" s="33" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,9 +30,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
-  <x:si>
-    <x:t>LICENSE SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
+  <x:si>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LICENSES SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | July 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -125,6 +131,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | August 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station License (NEW)</x:t>
   </x:si>
   <x:si>
@@ -332,6 +341,9 @@
     <x:t>61-8-2025-1113</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | September 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station License (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -422,6 +434,9 @@
     <x:t>61-9-2025-1174</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | October 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>JESSIE B. POLANCO</x:t>
   </x:si>
   <x:si>
@@ -464,6 +479,9 @@
     <x:t>61-10-2025-1182</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | November 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>DELFINA S. CORTINA &amp; MARCELINO G. CORTINA JR.</x:t>
   </x:si>
   <x:si>
@@ -533,6 +551,9 @@
     <x:t>61-10-2025-1204</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | December 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDILMAR VINCENT SAGUN ARAO</x:t>
   </x:si>
   <x:si>
@@ -578,6 +599,9 @@
     <x:t>61-11-2025-1246-597</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | January 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A Purok Bougainvilla, Bomba, Pagadian City (Capital), Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -623,6 +647,9 @@
     <x:t>61-12-2025-1266-301</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>MAT ANDREO A. DE LARA</x:t>
   </x:si>
   <x:si>
@@ -738,6 +765,9 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1319-115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>AL S. BURBURAN</x:t>
@@ -912,7 +942,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -952,6 +982,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1223,15 +1277,21 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1246,62 +1306,62 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1332,99 +1392,107 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1653,58 +1721,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1747,732 +1815,732 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="C8" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46076.1792361111</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216147</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46090.2042708333</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46072.0333449074</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216156</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>46090.2584837963</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
+      <x:c r="C10" s="18" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>46071.1677662037</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I10" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1216165</x:v>
       </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
+      <x:c r="L10" s="23">
         <x:v>46091.1948842593</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
+      <x:c r="C11" s="18" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>46070.1768402778</x:v>
       </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="I11" s="21">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J11" s="17" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1216138</x:v>
       </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="21">
+      <x:c r="L11" s="23">
         <x:v>46084.1495138889</x:v>
       </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
+      <x:c r="C12" s="18" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
         <x:v>46076.1139583333</x:v>
       </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="I12" s="21">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J12" s="17" t="n">
+      <x:c r="J12" s="19" t="n">
         <x:v>1216146</x:v>
       </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="K12" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="21">
+      <x:c r="L12" s="23">
         <x:v>46090.1919444444</x:v>
       </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M12" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
+      <x:c r="B13" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
+      <x:c r="C13" s="18" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D13" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H13" s="20">
         <x:v>46071.3305671296</x:v>
       </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="I13" s="21">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J13" s="17" t="n">
+      <x:c r="J13" s="19" t="n">
         <x:v>1216193</x:v>
       </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="K13" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L13" s="21">
+      <x:c r="L13" s="23">
         <x:v>46094.1906365741</x:v>
       </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M13" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s">
+      <x:c r="B14" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="16" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
+      <x:c r="C14" s="18" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H14" s="20">
         <x:v>46072.0792939815</x:v>
       </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="I14" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="17" t="n">
+      <x:c r="J14" s="19" t="n">
         <x:v>1216150</x:v>
       </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="K14" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="21">
+      <x:c r="L14" s="23">
         <x:v>46090.220787037</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M14" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s">
+      <x:c r="B15" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="16" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
+      <x:c r="C15" s="18" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D15" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H15" s="20">
         <x:v>46077.2598726852</x:v>
       </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="I15" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="17" t="n">
+      <x:c r="J15" s="19" t="n">
         <x:v>1216158</x:v>
       </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="K15" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="21">
+      <x:c r="L15" s="23">
         <x:v>46090.2758680556</x:v>
       </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M15" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s">
+      <x:c r="B16" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
+      <x:c r="C16" s="18" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D16" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="F16" s="18" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G16" s="18" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="H16" s="20">
         <x:v>46072.1089467593</x:v>
       </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="I16" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J16" s="17" t="n">
+      <x:c r="J16" s="19" t="n">
         <x:v>1216152</x:v>
       </x:c>
-      <x:c r="K16" s="20" t="n">
+      <x:c r="K16" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="21">
+      <x:c r="L16" s="23">
         <x:v>46090.2365046296</x:v>
       </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M16" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="s">
+      <x:c r="B17" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="16" t="s">
+      <x:c r="C17" s="18" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D17" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G17" s="18" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H17" s="20">
+        <x:v>46077.5191782407</x:v>
+      </x:c>
+      <x:c r="I17" s="21">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J17" s="19" t="n">
+        <x:v>1216163</x:v>
+      </x:c>
+      <x:c r="K17" s="22" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L17" s="23">
+        <x:v>46090.3154976852</x:v>
+      </x:c>
+      <x:c r="M17" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D18" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H18" s="20">
+        <x:v>46077.4722337963</x:v>
+      </x:c>
+      <x:c r="I18" s="21">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J18" s="19" t="n">
+        <x:v>1216161</x:v>
+      </x:c>
+      <x:c r="K18" s="22" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="23">
+        <x:v>46090.2963078704</x:v>
+      </x:c>
+      <x:c r="M18" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D19" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="H17" s="18">
-        <x:v>46077.5191782407</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="F19" s="18" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G19" s="18" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="H19" s="20">
+        <x:v>46077.2024189815</x:v>
+      </x:c>
+      <x:c r="I19" s="21">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J19" s="19" t="n">
+        <x:v>1216154</x:v>
+      </x:c>
+      <x:c r="K19" s="22" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L19" s="23">
+        <x:v>46090.2495949074</x:v>
+      </x:c>
+      <x:c r="M19" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D20" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G20" s="18" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H20" s="20">
+        <x:v>46072.0497337963</x:v>
+      </x:c>
+      <x:c r="I20" s="21">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:v>1216163</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="J20" s="19" t="n">
+        <x:v>1216148</x:v>
+      </x:c>
+      <x:c r="K20" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46090.3154976852</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
+      <x:c r="L20" s="23">
+        <x:v>46090.2102430556</x:v>
+      </x:c>
+      <x:c r="M20" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
-        <x:v>46077.4722337963</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J18" s="17" t="n">
-        <x:v>1216161</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="C21" s="18" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D21" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F21" s="18" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G21" s="18" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H21" s="20">
+        <x:v>46071.2285416667</x:v>
+      </x:c>
+      <x:c r="I21" s="21">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J21" s="19" t="n">
+        <x:v>1216143</x:v>
+      </x:c>
+      <x:c r="K21" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46090.2963078704</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
+      <x:c r="L21" s="23">
+        <x:v>46090.0772916667</x:v>
+      </x:c>
+      <x:c r="M21" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E19" s="16" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H19" s="18">
-        <x:v>46077.2024189815</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>45948</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:v>1216154</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
+      <x:c r="C22" s="18" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H22" s="20">
+        <x:v>46071.2072569444</x:v>
+      </x:c>
+      <x:c r="I22" s="21">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J22" s="19" t="n">
+        <x:v>1216142</x:v>
+      </x:c>
+      <x:c r="K22" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46090.2495949074</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="s">
+      <x:c r="L22" s="23">
+        <x:v>46090.0616666667</x:v>
+      </x:c>
+      <x:c r="M22" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E20" s="16" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H20" s="18">
-        <x:v>46072.0497337963</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J20" s="17" t="n">
-        <x:v>1216148</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
+      <x:c r="C23" s="18" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D23" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F23" s="18" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G23" s="18" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H23" s="20">
+        <x:v>46079.0151851852</x:v>
+      </x:c>
+      <x:c r="I23" s="21">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J23" s="19" t="n">
+        <x:v>1216174</x:v>
+      </x:c>
+      <x:c r="K23" s="22" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L23" s="23">
+        <x:v>46093.1514351852</x:v>
+      </x:c>
+      <x:c r="M23" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D24" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F24" s="18" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H24" s="20">
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I24" s="21">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J24" s="19" t="n">
+        <x:v>1216173</x:v>
+      </x:c>
+      <x:c r="K24" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46090.2102430556</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D21" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E21" s="16" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>46071.2285416667</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1216143</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46090.0772916667</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C22" s="16" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="D22" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E22" s="16" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="F22" s="16" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="H22" s="18">
-        <x:v>46071.2072569444</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J22" s="17" t="n">
-        <x:v>1216142</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46090.0616666667</x:v>
-      </x:c>
-      <x:c r="M22" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C23" s="16" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D23" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E23" s="16" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F23" s="16" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G23" s="16" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H23" s="18">
-        <x:v>46079.0151851852</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>45602</x:v>
-      </x:c>
-      <x:c r="J23" s="17" t="n">
-        <x:v>1216174</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3990</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46093.1514351852</x:v>
-      </x:c>
-      <x:c r="M23" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C24" s="16" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D24" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E24" s="16" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F24" s="16" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G24" s="16" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H24" s="18">
-        <x:v>45988.1893402778</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>45973</x:v>
-      </x:c>
-      <x:c r="J24" s="17" t="n">
-        <x:v>1216173</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
+      <x:c r="L24" s="23">
         <x:v>46093.1383912037</x:v>
       </x:c>
-      <x:c r="M24" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M24" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="24" t="s"/>
-      <x:c r="F27" s="24" t="s"/>
+      <x:c r="B27" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="26" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B28" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
+      <x:c r="B29" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C29" s="31" t="s"/>
+      <x:c r="D29" s="31" t="s"/>
+      <x:c r="E29" s="31" t="s"/>
+      <x:c r="F29" s="32" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C30" s="32" t="s"/>
-      <x:c r="D30" s="32" t="s"/>
-      <x:c r="E30" s="32" t="s"/>
-      <x:c r="F30" s="33" t="n">
+      <x:c r="B30" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C30" s="34" t="s"/>
+      <x:c r="D30" s="34" t="s"/>
+      <x:c r="E30" s="34" t="s"/>
+      <x:c r="F30" s="35" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3443,7 +3511,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
@@ -3488,58 +3556,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3582,200 +3650,200 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45862.256875</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>45908</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215838</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45862.3066319444</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
+      <x:c r="C9" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45861.1595717593</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215833</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45862.1034606481</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45861.1595717593</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1215833</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45862.1034606481</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
+      <x:c r="C10" s="18" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G10" s="16" t="s">
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H10" s="18">
+      <x:c r="F10" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>45861.1361574074</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I10" s="21">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1215836</x:v>
       </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L10" s="21">
+      <x:c r="L10" s="23">
         <x:v>45862.1391203704</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="24" t="s"/>
+      <x:c r="B13" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="26" t="s"/>
+      <x:c r="F13" s="26" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B14" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="30" t="n">
+      <x:c r="B15" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="31" t="s"/>
+      <x:c r="D15" s="31" t="s"/>
+      <x:c r="E15" s="31" t="s"/>
+      <x:c r="F15" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="32" t="s"/>
-      <x:c r="D16" s="32" t="s"/>
-      <x:c r="E16" s="32" t="s"/>
-      <x:c r="F16" s="33" t="n">
+      <x:c r="B16" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="34" t="s"/>
+      <x:c r="D16" s="34" t="s"/>
+      <x:c r="E16" s="34" t="s"/>
+      <x:c r="F16" s="35" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -4760,7 +4828,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
@@ -4805,58 +4873,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45870</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -4899,722 +4967,722 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="E8" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45877.1309490741</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>45877.1309606481</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1346451</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45877.1897222222</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>37</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45882.0658796296</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45882.0658912037</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1195701</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>2496</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45883.2549537037</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="18" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
+        <x:v>45881.0630902778</x:v>
+      </x:c>
+      <x:c r="I10" s="21">
+        <x:v>45885</x:v>
+      </x:c>
+      <x:c r="J10" s="19" t="n">
+        <x:v>1346453</x:v>
+      </x:c>
+      <x:c r="K10" s="22" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="23">
+        <x:v>45881.0887037037</x:v>
+      </x:c>
+      <x:c r="M10" s="18" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45882.0658796296</x:v>
-      </x:c>
-      <x:c r="I9" s="13">
-        <x:v>45882.0658912037</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1195701</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>2496</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45883.2549537037</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
+        <x:v>45897.2535648148</x:v>
+      </x:c>
+      <x:c r="I11" s="21">
+        <x:v>45847</x:v>
+      </x:c>
+      <x:c r="J11" s="19" t="n">
+        <x:v>1346494</x:v>
+      </x:c>
+      <x:c r="K11" s="22" t="n">
+        <x:v>2490</x:v>
+      </x:c>
+      <x:c r="L11" s="23">
+        <x:v>45897.2982407407</x:v>
+      </x:c>
+      <x:c r="M11" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="18" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
+        <x:v>45881.3064236111</x:v>
+      </x:c>
+      <x:c r="I12" s="21">
+        <x:v>45871</x:v>
+      </x:c>
+      <x:c r="J12" s="19" t="n">
+        <x:v>1195693</x:v>
+      </x:c>
+      <x:c r="K12" s="22" t="n">
+        <x:v>4275</x:v>
+      </x:c>
+      <x:c r="L12" s="23">
+        <x:v>45897.0449189815</x:v>
+      </x:c>
+      <x:c r="M12" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="18" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D13" s="19" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H13" s="20">
+        <x:v>45870.3069328704</x:v>
+      </x:c>
+      <x:c r="I13" s="21">
+        <x:v>46186</x:v>
+      </x:c>
+      <x:c r="J13" s="19" t="n">
+        <x:v>1346441</x:v>
+      </x:c>
+      <x:c r="K13" s="22" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L13" s="23">
+        <x:v>45883.1603356482</x:v>
+      </x:c>
+      <x:c r="M13" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="18" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H14" s="20">
+        <x:v>45874.1403125</x:v>
+      </x:c>
+      <x:c r="I14" s="21">
+        <x:v>46159</x:v>
+      </x:c>
+      <x:c r="J14" s="19" t="n">
+        <x:v>1346447</x:v>
+      </x:c>
+      <x:c r="K14" s="22" t="n">
+        <x:v>4230</x:v>
+      </x:c>
+      <x:c r="L14" s="23">
+        <x:v>45874.2281365741</x:v>
+      </x:c>
+      <x:c r="M14" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="18" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D15" s="19" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H15" s="20">
+        <x:v>45883.1346180556</x:v>
+      </x:c>
+      <x:c r="I15" s="20">
+        <x:v>45883.1346296296</x:v>
+      </x:c>
+      <x:c r="J15" s="19" t="n">
+        <x:v>1346466</x:v>
+      </x:c>
+      <x:c r="K15" s="22" t="n">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="L15" s="23">
+        <x:v>45883.1693055556</x:v>
+      </x:c>
+      <x:c r="M15" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
-        <x:v>45881.0630902778</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45885</x:v>
-      </x:c>
-      <x:c r="J10" s="17" t="n">
-        <x:v>1346453</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="C16" s="18" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D16" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F16" s="18" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G16" s="18" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H16" s="20">
+        <x:v>45887.5652430556</x:v>
+      </x:c>
+      <x:c r="I16" s="21">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J16" s="19" t="n">
+        <x:v>1215872</x:v>
+      </x:c>
+      <x:c r="K16" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45881.0887037037</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
+      <x:c r="L16" s="23">
+        <x:v>45896.2365393518</x:v>
+      </x:c>
+      <x:c r="M16" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
-        <x:v>45897.2535648148</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45847</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:v>1346494</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>2490</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45897.2982407407</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s">
+      <x:c r="C17" s="18" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D17" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G17" s="18" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H17" s="20">
+        <x:v>45873.2842013889</x:v>
+      </x:c>
+      <x:c r="I17" s="21">
+        <x:v>45544</x:v>
+      </x:c>
+      <x:c r="J17" s="19" t="n">
+        <x:v>1346446</x:v>
+      </x:c>
+      <x:c r="K17" s="22" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L17" s="23">
+        <x:v>45873.3539814815</x:v>
+      </x:c>
+      <x:c r="M17" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
-        <x:v>45881.3064236111</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>45871</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="n">
-        <x:v>1195693</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>4275</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45897.0449189815</x:v>
-      </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
-        <x:v>45870.3069328704</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46186</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:v>1346441</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45883.1603356482</x:v>
-      </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
-        <x:v>45874.1403125</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46159</x:v>
-      </x:c>
-      <x:c r="J14" s="17" t="n">
-        <x:v>1346447</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>4230</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>45874.2281365741</x:v>
-      </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
-        <x:v>45883.1346180556</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>45883.1346296296</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="n">
-        <x:v>1346466</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>2070</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>45883.1693055556</x:v>
-      </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s">
+      <x:c r="C18" s="18" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D18" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H18" s="20">
+        <x:v>45891.1735648148</x:v>
+      </x:c>
+      <x:c r="I18" s="21">
+        <x:v>45765</x:v>
+      </x:c>
+      <x:c r="J18" s="19" t="n">
+        <x:v>1215865</x:v>
+      </x:c>
+      <x:c r="K18" s="22" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="23">
+        <x:v>45898.0611111111</x:v>
+      </x:c>
+      <x:c r="M18" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
-        <x:v>45887.5652430556</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J16" s="17" t="n">
-        <x:v>1215872</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>45896.2365393518</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
+      <x:c r="C19" s="18" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D19" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G19" s="18" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H19" s="20">
+        <x:v>45883.1535763889</x:v>
+      </x:c>
+      <x:c r="I19" s="21">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J19" s="19" t="n">
+        <x:v>1346468</x:v>
+      </x:c>
+      <x:c r="K19" s="22" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="L19" s="23">
+        <x:v>45883.2560300926</x:v>
+      </x:c>
+      <x:c r="M19" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D20" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F20" s="18" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G20" s="18" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H20" s="20">
+        <x:v>45879.4885069444</x:v>
+      </x:c>
+      <x:c r="I20" s="21">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J20" s="19" t="n">
+        <x:v>1215863</x:v>
+      </x:c>
+      <x:c r="K20" s="22" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L20" s="23">
+        <x:v>45884.277650463</x:v>
+      </x:c>
+      <x:c r="M20" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D21" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D17" s="17" t="s">
+      <x:c r="F21" s="18" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G21" s="18" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H21" s="20">
+        <x:v>45887.5590162037</x:v>
+      </x:c>
+      <x:c r="I21" s="21">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J21" s="19" t="n">
+        <x:v>1215870</x:v>
+      </x:c>
+      <x:c r="K21" s="22" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L21" s="23">
+        <x:v>45896.237962963</x:v>
+      </x:c>
+      <x:c r="M21" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="16" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H17" s="18">
-        <x:v>45873.2842013889</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>45544</x:v>
-      </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:v>1346446</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>45873.3539814815</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
-        <x:v>45891.1735648148</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>45765</x:v>
-      </x:c>
-      <x:c r="J18" s="17" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>45898.0611111111</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="16" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H19" s="18">
-        <x:v>45883.1535763889</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:v>1346468</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>4350</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>45883.2560300926</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="16" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H20" s="18">
-        <x:v>45879.4885069444</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J20" s="17" t="n">
-        <x:v>1215863</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>45884.277650463</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D21" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E21" s="16" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>45887.5590162037</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1215870</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
+      <x:c r="C22" s="18" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H22" s="20">
+        <x:v>45881.2806365741</x:v>
+      </x:c>
+      <x:c r="I22" s="21">
+        <x:v>45892</x:v>
+      </x:c>
+      <x:c r="J22" s="19" t="n">
+        <x:v>1346470</x:v>
+      </x:c>
+      <x:c r="K22" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L21" s="21">
-        <x:v>45896.237962963</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C22" s="16" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D22" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E22" s="16" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F22" s="16" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H22" s="18">
-        <x:v>45881.2806365741</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>45892</x:v>
-      </x:c>
-      <x:c r="J22" s="17" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
+      <x:c r="L22" s="23">
         <x:v>45883.2976041667</x:v>
       </x:c>
-      <x:c r="M22" s="16" t="s">
-        <x:v>37</x:v>
+      <x:c r="M22" s="18" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C25" s="23" t="s"/>
-      <x:c r="D25" s="23" t="s"/>
-      <x:c r="E25" s="24" t="s"/>
-      <x:c r="F25" s="24" t="s"/>
+      <x:c r="B25" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C25" s="25" t="s"/>
+      <x:c r="D25" s="25" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="26" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B26" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C26" s="28" t="s"/>
+      <x:c r="D26" s="28" t="s"/>
+      <x:c r="E26" s="28" t="s"/>
+      <x:c r="F26" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="28" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="30" t="n">
+      <x:c r="B27" s="30" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C27" s="31" t="s"/>
+      <x:c r="D27" s="31" t="s"/>
+      <x:c r="E27" s="31" t="s"/>
+      <x:c r="F27" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="28" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C28" s="29" t="s"/>
-      <x:c r="D28" s="29" t="s"/>
-      <x:c r="E28" s="29" t="s"/>
-      <x:c r="F28" s="30" t="n">
+      <x:c r="B28" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C28" s="31" t="s"/>
+      <x:c r="D28" s="31" t="s"/>
+      <x:c r="E28" s="31" t="s"/>
+      <x:c r="F28" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="28" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
+      <x:c r="B29" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C29" s="31" t="s"/>
+      <x:c r="D29" s="31" t="s"/>
+      <x:c r="E29" s="31" t="s"/>
+      <x:c r="F29" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="28" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C30" s="29" t="s"/>
-      <x:c r="D30" s="29" t="s"/>
-      <x:c r="E30" s="29" t="s"/>
-      <x:c r="F30" s="30" t="n">
+      <x:c r="B30" s="30" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="s"/>
+      <x:c r="D30" s="31" t="s"/>
+      <x:c r="E30" s="31" t="s"/>
+      <x:c r="F30" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="28" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C31" s="29" t="s"/>
-      <x:c r="D31" s="29" t="s"/>
-      <x:c r="E31" s="29" t="s"/>
-      <x:c r="F31" s="30" t="n">
+      <x:c r="B31" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C31" s="31" t="s"/>
+      <x:c r="D31" s="31" t="s"/>
+      <x:c r="E31" s="31" t="s"/>
+      <x:c r="F31" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="28" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
+      <x:c r="B32" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C32" s="31" t="s"/>
+      <x:c r="D32" s="31" t="s"/>
+      <x:c r="E32" s="31" t="s"/>
+      <x:c r="F32" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C33" s="29" t="s"/>
-      <x:c r="D33" s="29" t="s"/>
-      <x:c r="E33" s="29" t="s"/>
-      <x:c r="F33" s="30" t="n">
+      <x:c r="B33" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C33" s="31" t="s"/>
+      <x:c r="D33" s="31" t="s"/>
+      <x:c r="E33" s="31" t="s"/>
+      <x:c r="F33" s="32" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C34" s="32" t="s"/>
-      <x:c r="D34" s="32" t="s"/>
-      <x:c r="E34" s="32" t="s"/>
-      <x:c r="F34" s="33" t="n">
+      <x:c r="B34" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C34" s="34" t="s"/>
+      <x:c r="D34" s="34" t="s"/>
+      <x:c r="E34" s="34" t="s"/>
+      <x:c r="F34" s="35" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -6581,7 +6649,7 @@
   <x:mergeCells count="13">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
@@ -6632,58 +6700,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45901</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -6726,374 +6794,374 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45883.0291898148</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1346465</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45929.2261805556</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45883.0965162037</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>2592.56</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45930.3001388889</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>45883.0291898148</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45651</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1346465</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>45929.2261805556</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="C10" s="18" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
+        <x:v>45908.5003472222</x:v>
+      </x:c>
+      <x:c r="I10" s="21">
+        <x:v>45790</x:v>
+      </x:c>
+      <x:c r="J10" s="19" t="n">
+        <x:v>1215888</x:v>
+      </x:c>
+      <x:c r="K10" s="22" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="23">
+        <x:v>45911.952650463</x:v>
+      </x:c>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45883.0965162037</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>2592.56</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45930.3001388889</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+      <x:c r="C11" s="18" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
+        <x:v>45916.1691666667</x:v>
+      </x:c>
+      <x:c r="I11" s="21">
+        <x:v>45949</x:v>
+      </x:c>
+      <x:c r="J11" s="19" t="n">
+        <x:v>1215908</x:v>
+      </x:c>
+      <x:c r="K11" s="22" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L11" s="23">
+        <x:v>45929.1383449074</x:v>
+      </x:c>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
-        <x:v>45908.5003472222</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45790</x:v>
-      </x:c>
-      <x:c r="J10" s="17" t="n">
-        <x:v>1215888</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="C12" s="18" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
+        <x:v>45888.154375</x:v>
+      </x:c>
+      <x:c r="I12" s="21">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="J12" s="19" t="n">
+        <x:v>1215874</x:v>
+      </x:c>
+      <x:c r="K12" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45911.952650463</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
+      <x:c r="L12" s="23">
+        <x:v>45902.050775463</x:v>
+      </x:c>
+      <x:c r="M12" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
-        <x:v>45916.1691666667</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45949</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:v>1215908</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45929.1383449074</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s">
+      <x:c r="C13" s="18" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D13" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H13" s="20">
+        <x:v>45877.1361111111</x:v>
+      </x:c>
+      <x:c r="I13" s="21">
+        <x:v>45909</x:v>
+      </x:c>
+      <x:c r="J13" s="19" t="n">
+        <x:v>1346508</x:v>
+      </x:c>
+      <x:c r="K13" s="22" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L13" s="23">
+        <x:v>45908.1453009259</x:v>
+      </x:c>
+      <x:c r="M13" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
-        <x:v>45888.154375</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>45870</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="n">
-        <x:v>1215874</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45902.050775463</x:v>
-      </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
-        <x:v>45877.1361111111</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>45909</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:v>1346508</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45908.1453009259</x:v>
-      </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="16" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
+      <x:c r="C14" s="18" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H14" s="20">
         <x:v>45924.1162962963</x:v>
       </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="I14" s="21">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J14" s="17" t="n">
+      <x:c r="J14" s="19" t="n">
         <x:v>1215911</x:v>
       </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="K14" s="22" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L14" s="21">
+      <x:c r="L14" s="23">
         <x:v>45930.063912037</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M14" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="24" t="s"/>
+      <x:c r="B17" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="26" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B18" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C19" s="31" t="s"/>
+      <x:c r="D19" s="31" t="s"/>
+      <x:c r="E19" s="31" t="s"/>
+      <x:c r="F19" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="B20" s="30" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="31" t="s"/>
+      <x:c r="D20" s="31" t="s"/>
+      <x:c r="E20" s="31" t="s"/>
+      <x:c r="F20" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="29" t="s"/>
-      <x:c r="D21" s="29" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="30" t="n">
+      <x:c r="B21" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="31" t="s"/>
+      <x:c r="D21" s="31" t="s"/>
+      <x:c r="E21" s="31" t="s"/>
+      <x:c r="F21" s="32" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C22" s="32" t="s"/>
-      <x:c r="D22" s="32" t="s"/>
-      <x:c r="E22" s="32" t="s"/>
-      <x:c r="F22" s="33" t="n">
+      <x:c r="B22" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C22" s="34" t="s"/>
+      <x:c r="D22" s="34" t="s"/>
+      <x:c r="E22" s="34" t="s"/>
+      <x:c r="F22" s="35" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8072,7 +8140,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
@@ -8119,58 +8187,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45931</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -8213,247 +8281,247 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="B8" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45947.5768287037</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>43437</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215960</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>17766</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45954.2191782407</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s"/>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="15">
         <x:v>45925.0601967593</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>45922</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1215919</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>45933.3037152778</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
+      <x:c r="C10" s="18" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>45912.3032407407</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I10" s="21">
         <x:v>45879</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1215920</x:v>
       </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>4710</x:v>
       </x:c>
-      <x:c r="L10" s="21">
+      <x:c r="L10" s="23">
         <x:v>45933.3105324074</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
+      <x:c r="C11" s="18" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>45931.5665277778</x:v>
       </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="I11" s="21">
         <x:v>46297</x:v>
       </x:c>
-      <x:c r="J11" s="17" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1215945</x:v>
       </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="21">
+      <x:c r="L11" s="23">
         <x:v>45940.1382060185</x:v>
       </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="26" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B15" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="B17" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
+      <x:c r="B18" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="s"/>
+      <x:c r="D18" s="34" t="s"/>
+      <x:c r="E18" s="34" t="s"/>
+      <x:c r="F18" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -9436,7 +9504,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
@@ -9482,58 +9550,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45962</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -9576,314 +9644,314 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="C8" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45974.6184490741</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>45682</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216021</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45986.0239236111</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45965.4411342593</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216001</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>45973.0179398148</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
+      <x:c r="C10" s="18" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>45971.2507291667</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I10" s="21">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1216006</x:v>
       </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="21">
+      <x:c r="L10" s="23">
         <x:v>45975.0756134259</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
+      <x:c r="C11" s="18" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>45958.3516898148</x:v>
       </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="I11" s="21">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J11" s="17" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1215976</x:v>
       </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L11" s="21">
+      <x:c r="L11" s="23">
         <x:v>45967.2412384259</x:v>
       </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
+      <x:c r="C12" s="18" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
         <x:v>45954.2913425926</x:v>
       </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="I12" s="21">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J12" s="17" t="n">
+      <x:c r="J12" s="19" t="n">
         <x:v>1216013</x:v>
       </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="K12" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="21">
+      <x:c r="L12" s="23">
         <x:v>45975.3213541667</x:v>
       </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M12" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
+      <x:c r="B13" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
+      <x:c r="C13" s="18" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D13" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H13" s="20">
         <x:v>45953.3174884259</x:v>
       </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="I13" s="21">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J13" s="17" t="n">
+      <x:c r="J13" s="19" t="n">
         <x:v>1215996</x:v>
       </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="K13" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="21">
+      <x:c r="L13" s="23">
         <x:v>45971.2990162037</x:v>
       </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M13" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="24" t="s"/>
+      <x:c r="B16" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="26" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B17" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
+      <x:c r="B19" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="34" t="s"/>
+      <x:c r="D19" s="34" t="s"/>
+      <x:c r="E19" s="34" t="s"/>
+      <x:c r="F19" s="35" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -10865,7 +10933,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
@@ -10910,58 +10978,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -11004,249 +11072,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46000.4750694444</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1216048</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46013.2950462963</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>46000.4750694444</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1216048</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>46013.2950462963</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="C9" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46000.180775463</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46006.2645138889</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46000.180775463</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46006.2645138889</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+      <x:c r="C10" s="18" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
+        <x:v>45972.0386111111</x:v>
+      </x:c>
+      <x:c r="I10" s="21">
+        <x:v>46337</x:v>
+      </x:c>
+      <x:c r="J10" s="19" t="n">
+        <x:v>1216033</x:v>
+      </x:c>
+      <x:c r="K10" s="22" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L10" s="23">
+        <x:v>46006.0795717593</x:v>
+      </x:c>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
-        <x:v>45972.0386111111</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46337</x:v>
-      </x:c>
-      <x:c r="J10" s="17" t="n">
-        <x:v>1216033</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46006.0795717593</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
+      <x:c r="C11" s="18" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>45980.2173958333</x:v>
       </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="I11" s="21">
         <x:v>45852</x:v>
       </x:c>
-      <x:c r="J11" s="17" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1216027</x:v>
       </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="21">
+      <x:c r="L11" s="23">
         <x:v>45992.1151851852</x:v>
       </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="26" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B15" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="B17" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
+      <x:c r="B18" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="s"/>
+      <x:c r="D18" s="34" t="s"/>
+      <x:c r="E18" s="34" t="s"/>
+      <x:c r="F18" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12229,7 +12297,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
@@ -12275,58 +12343,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -12369,238 +12437,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="C8" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46007.1341435185</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216069</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46035.3042476852</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>185</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46034.1687615741</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216081</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>46044.263275463</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
+      <x:c r="C10" s="18" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>46014.1352083333</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I10" s="21">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1216066</x:v>
       </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="21">
+      <x:c r="L10" s="23">
         <x:v>46035.0802662037</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>185</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
+      <x:c r="B11" s="18" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
+        <x:v>46014.4844097222</x:v>
+      </x:c>
+      <x:c r="I11" s="21">
+        <x:v>45786</x:v>
+      </x:c>
+      <x:c r="J11" s="19" t="n">
+        <x:v>1216060</x:v>
+      </x:c>
+      <x:c r="K11" s="22" t="n">
+        <x:v>2430</x:v>
+      </x:c>
+      <x:c r="L11" s="23">
+        <x:v>46031.0514583333</x:v>
+      </x:c>
+      <x:c r="M11" s="18" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
-        <x:v>46014.4844097222</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45786</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:v>1216060</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>2430</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46031.0514583333</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="26" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B15" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="32" t="s"/>
-      <x:c r="D17" s="32" t="s"/>
-      <x:c r="E17" s="32" t="s"/>
-      <x:c r="F17" s="33" t="n">
+      <x:c r="B17" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="34" t="s"/>
+      <x:c r="D17" s="34" t="s"/>
+      <x:c r="E17" s="34" t="s"/>
+      <x:c r="F17" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13584,7 +13652,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
@@ -13629,58 +13697,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -13723,515 +13791,515 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="B8" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46051.2691319444</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>46051.2691550926</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216103</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46057.9587152778</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46051.1259722222</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216112</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>46062.966400463</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s">
+      <x:c r="B10" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="16" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
+      <x:c r="C10" s="18" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H10" s="20">
         <x:v>46050.2853935185</x:v>
       </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="I10" s="21">
         <x:v>45945</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J10" s="19" t="n">
         <x:v>1216106</x:v>
       </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="K10" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
+      <x:c r="L10" s="23">
         <x:v>46058.0440046296</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
+      <x:c r="C11" s="18" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H11" s="20">
         <x:v>46066.1892939815</x:v>
       </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="I11" s="21">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J11" s="17" t="n">
+      <x:c r="J11" s="19" t="n">
         <x:v>1216131</x:v>
       </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="K11" s="22" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L11" s="21">
+      <x:c r="L11" s="23">
         <x:v>46076.0521180556</x:v>
       </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M11" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s">
+      <x:c r="B12" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="16" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
+      <x:c r="C12" s="18" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H12" s="20">
         <x:v>46066.186087963</x:v>
       </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="I12" s="21">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J12" s="17" t="n">
+      <x:c r="J12" s="19" t="n">
         <x:v>1216130</x:v>
       </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="K12" s="22" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L12" s="21">
+      <x:c r="L12" s="23">
         <x:v>46076.0476273148</x:v>
       </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M12" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
+      <x:c r="B13" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
+      <x:c r="C13" s="18" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D13" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H13" s="20">
         <x:v>46057.2800462963</x:v>
       </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="I13" s="21">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J13" s="17" t="n">
+      <x:c r="J13" s="19" t="n">
         <x:v>1216117</x:v>
       </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="K13" s="22" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L13" s="21">
+      <x:c r="L13" s="23">
         <x:v>46065.2796412037</x:v>
       </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M13" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s">
+      <x:c r="B14" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="16" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
+      <x:c r="C14" s="18" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H14" s="20">
         <x:v>46057.272025463</x:v>
       </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="I14" s="21">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="J14" s="17" t="n">
+      <x:c r="J14" s="19" t="n">
         <x:v>1216121</x:v>
       </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="K14" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="21">
+      <x:c r="L14" s="23">
         <x:v>46065.2951388889</x:v>
       </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M14" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s">
+      <x:c r="B15" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="16" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
+      <x:c r="C15" s="18" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D15" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H15" s="20">
         <x:v>46057.2657523148</x:v>
       </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="I15" s="21">
         <x:v>46039</x:v>
       </x:c>
-      <x:c r="J15" s="17" t="n">
+      <x:c r="J15" s="19" t="n">
         <x:v>1216119</x:v>
       </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="K15" s="22" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="21">
+      <x:c r="L15" s="23">
         <x:v>46065.285474537</x:v>
       </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M15" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s">
+      <x:c r="B16" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="16" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
+      <x:c r="C16" s="18" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D16" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F16" s="18" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G16" s="18" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="H16" s="20">
         <x:v>46056.1690046296</x:v>
       </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="I16" s="21">
         <x:v>45716</x:v>
       </x:c>
-      <x:c r="J16" s="17" t="n">
+      <x:c r="J16" s="19" t="n">
         <x:v>1216107</x:v>
       </x:c>
-      <x:c r="K16" s="20" t="n">
+      <x:c r="K16" s="22" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L16" s="21">
+      <x:c r="L16" s="23">
         <x:v>46058.1034490741</x:v>
       </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M16" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="s">
+      <x:c r="B17" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="16" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H17" s="18">
+      <x:c r="C17" s="18" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D17" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G17" s="18" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H17" s="20">
         <x:v>46065.2312962963</x:v>
       </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="I17" s="21">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J17" s="17" t="n">
+      <x:c r="J17" s="19" t="n">
         <x:v>1216134</x:v>
       </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="K17" s="22" t="n">
         <x:v>2190</x:v>
       </x:c>
-      <x:c r="L17" s="21">
+      <x:c r="L17" s="23">
         <x:v>46076.0858333333</x:v>
       </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M17" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
+      <x:c r="B18" s="18" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
+      <x:c r="C18" s="18" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D18" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H18" s="20">
         <x:v>46063.0357060185</x:v>
       </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="I18" s="21">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J18" s="17" t="n">
+      <x:c r="J18" s="19" t="n">
         <x:v>1216123</x:v>
       </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="K18" s="22" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L18" s="21">
+      <x:c r="L18" s="23">
         <x:v>46066.0203819444</x:v>
       </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>19</x:v>
+      <x:c r="M18" s="18" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="24" t="s"/>
+      <x:c r="B21" s="24" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="26" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="s">
-        <x:v>29</x:v>
+      <x:c r="B22" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s"/>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="29" t="s"/>
-      <x:c r="F23" s="30" t="n">
+      <x:c r="B23" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C23" s="31" t="s"/>
+      <x:c r="D23" s="31" t="s"/>
+      <x:c r="E23" s="31" t="s"/>
+      <x:c r="F23" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="30" t="n">
+      <x:c r="B24" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C24" s="31" t="s"/>
+      <x:c r="D24" s="31" t="s"/>
+      <x:c r="E24" s="31" t="s"/>
+      <x:c r="F24" s="32" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C25" s="32" t="s"/>
-      <x:c r="D25" s="32" t="s"/>
-      <x:c r="E25" s="32" t="s"/>
-      <x:c r="F25" s="33" t="n">
+      <x:c r="B25" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C25" s="34" t="s"/>
+      <x:c r="D25" s="34" t="s"/>
+      <x:c r="E25" s="34" t="s"/>
+      <x:c r="F25" s="35" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -15207,7 +15275,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B21:F21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -600,6 +600,24 @@
   </x:si>
   <x:si>
     <x:t>IX | January 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Certified True Copy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSEPH GEORGE QUEZON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>V.C.H. Block. 29, Lot.44 Mahogany, Obay, Polanco, Zamboanga Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-04182-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-12-2025-1261-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fortunata Postigo</x:t>
   </x:si>
   <x:si>
     <x:t>N/A Purok Bougainvilla, Bomba, Pagadian City (Capital), Zamboanga Del Sur</x:t>
@@ -1778,7 +1796,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>245</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -1857,19 +1875,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>246</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>247</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>248</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>249</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H8" s="15">
         <x:v>46076.1792361111</x:v>
@@ -1895,19 +1913,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>246</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>250</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>251</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>252</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46072.0333449074</x:v>
@@ -1933,19 +1951,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="17" t="s">
-        <x:v>253</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D10" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="17" t="s">
-        <x:v>254</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F10" s="17" t="s">
-        <x:v>255</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G10" s="17" t="s">
-        <x:v>256</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H10" s="19">
         <x:v>46071.1677662037</x:v>
@@ -1971,19 +1989,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
-        <x:v>257</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="17" t="s">
-        <x:v>258</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F11" s="17" t="s">
-        <x:v>259</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G11" s="17" t="s">
-        <x:v>260</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H11" s="19">
         <x:v>46070.1768402778</x:v>
@@ -2009,19 +2027,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="17" t="s">
-        <x:v>261</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D12" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="17" t="s">
-        <x:v>262</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="F12" s="17" t="s">
-        <x:v>263</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G12" s="17" t="s">
-        <x:v>264</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H12" s="19">
         <x:v>46076.1139583333</x:v>
@@ -2047,19 +2065,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D13" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s">
-        <x:v>265</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F13" s="17" t="s">
-        <x:v>266</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G13" s="17" t="s">
-        <x:v>267</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H13" s="19">
         <x:v>46071.3305671296</x:v>
@@ -2085,19 +2103,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D14" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="17" t="s">
-        <x:v>269</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F14" s="17" t="s">
-        <x:v>270</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="G14" s="17" t="s">
-        <x:v>271</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="H14" s="19">
         <x:v>46072.0792939815</x:v>
@@ -2123,19 +2141,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="17" t="s">
-        <x:v>272</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="F15" s="17" t="s">
-        <x:v>273</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="G15" s="17" t="s">
-        <x:v>274</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="H15" s="19">
         <x:v>46077.2598726852</x:v>
@@ -2161,19 +2179,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C16" s="17" t="s">
-        <x:v>268</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D16" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E16" s="17" t="s">
-        <x:v>275</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="F16" s="17" t="s">
-        <x:v>276</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="G16" s="17" t="s">
-        <x:v>277</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="H16" s="19">
         <x:v>46072.1089467593</x:v>
@@ -2199,19 +2217,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="17" t="s">
-        <x:v>278</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D17" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E17" s="17" t="s">
-        <x:v>279</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F17" s="17" t="s">
-        <x:v>280</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="G17" s="17" t="s">
-        <x:v>281</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="H17" s="19">
         <x:v>46077.5191782407</x:v>
@@ -2237,19 +2255,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C18" s="17" t="s">
-        <x:v>278</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D18" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="17" t="s">
-        <x:v>282</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="F18" s="17" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="G18" s="17" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="H18" s="19">
         <x:v>46077.4722337963</x:v>
@@ -2275,19 +2293,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C19" s="17" t="s">
-        <x:v>278</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D19" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E19" s="17" t="s">
-        <x:v>269</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F19" s="17" t="s">
-        <x:v>285</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="G19" s="17" t="s">
-        <x:v>286</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="H19" s="19">
         <x:v>46077.2024189815</x:v>
@@ -2313,19 +2331,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>278</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D20" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E20" s="17" t="s">
-        <x:v>287</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F20" s="17" t="s">
-        <x:v>288</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G20" s="17" t="s">
-        <x:v>289</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="H20" s="19">
         <x:v>46072.0497337963</x:v>
@@ -2351,19 +2369,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C21" s="17" t="s">
-        <x:v>290</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E21" s="17" t="s">
-        <x:v>269</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F21" s="17" t="s">
-        <x:v>291</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G21" s="17" t="s">
-        <x:v>292</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="H21" s="19">
         <x:v>46071.2285416667</x:v>
@@ -2389,19 +2407,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C22" s="17" t="s">
-        <x:v>290</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D22" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E22" s="17" t="s">
-        <x:v>293</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="F22" s="17" t="s">
-        <x:v>294</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="G22" s="17" t="s">
-        <x:v>295</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H22" s="19">
         <x:v>46071.2072569444</x:v>
@@ -2433,13 +2451,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E23" s="17" t="s">
-        <x:v>296</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F23" s="17" t="s">
-        <x:v>297</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="G23" s="17" t="s">
-        <x:v>298</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="H23" s="19">
         <x:v>46079.0151851852</x:v>
@@ -2474,10 +2492,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="F24" s="17" t="s">
-        <x:v>299</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="G24" s="17" t="s">
-        <x:v>300</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H24" s="19">
         <x:v>45988.1893402778</x:v>
@@ -12567,40 +12585,38 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>17</x:v>
-      </x:c>
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>190</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>191</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46007.1341435185</x:v>
+        <x:v>46007.2920138889</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>45942</x:v>
+        <x:v>46007.292037037</x:v>
       </x:c>
       <x:c r="J8" s="14" t="n">
-        <x:v>1216069</x:v>
+        <x:v>1195956</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
-        <x:v>2010</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46035.3042476852</x:v>
+        <x:v>46044.2434953704</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>195</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -12608,37 +12624,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>194</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H9" s="15">
-        <x:v>46034.1687615741</x:v>
+        <x:v>46007.1341435185</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>45944</x:v>
+        <x:v>45942</x:v>
       </x:c>
       <x:c r="J9" s="14" t="n">
-        <x:v>1216081</x:v>
+        <x:v>1216069</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
         <x:v>2010</x:v>
       </x:c>
       <x:c r="L9" s="15">
-        <x:v>46044.263275463</x:v>
+        <x:v>46035.3042476852</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
@@ -12646,37 +12662,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="17" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D10" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="17" t="s">
-        <x:v>123</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F10" s="17" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G10" s="17" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H10" s="19">
-        <x:v>46014.1352083333</x:v>
+        <x:v>46034.1687615741</x:v>
       </x:c>
       <x:c r="I10" s="19">
-        <x:v>46024</x:v>
+        <x:v>45944</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>1216066</x:v>
+        <x:v>1216081</x:v>
       </x:c>
       <x:c r="K10" s="20" t="n">
-        <x:v>1470</x:v>
+        <x:v>2010</x:v>
       </x:c>
       <x:c r="L10" s="21">
-        <x:v>46035.0802662037</x:v>
+        <x:v>46044.263275463</x:v>
       </x:c>
       <x:c r="M10" s="17" t="s">
-        <x:v>193</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
@@ -12684,85 +12700,132 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="17" t="s">
-        <x:v>202</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F11" s="17" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G11" s="17" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H11" s="19">
+        <x:v>46014.1352083333</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1216066</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46035.0802662037</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>46014.4844097222</x:v>
       </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="I12" s="19">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>1216060</x:v>
       </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="K12" s="20" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L11" s="21">
+      <x:c r="L12" s="21">
         <x:v>46031.0514583333</x:v>
       </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>193</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="M12" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="24" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="s">
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="28" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="31" t="s">
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="31" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C17" s="32" t="s"/>
-      <x:c r="D17" s="32" t="s"/>
-      <x:c r="E17" s="32" t="s"/>
-      <x:c r="F17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C19" s="32" t="s"/>
+      <x:c r="D19" s="32" t="s"/>
+      <x:c r="E19" s="32" t="s"/>
+      <x:c r="F19" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -13738,15 +13801,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -13858,7 +13922,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>205</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -13937,19 +14001,19 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>206</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>207</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>208</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>209</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H8" s="15">
         <x:v>46051.2691319444</x:v>
@@ -13975,19 +14039,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>210</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>211</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>212</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>213</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46051.1259722222</x:v>
@@ -14013,19 +14077,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="17" t="s">
-        <x:v>214</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D10" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="17" t="s">
-        <x:v>215</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F10" s="17" t="s">
-        <x:v>216</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G10" s="17" t="s">
-        <x:v>217</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H10" s="19">
         <x:v>46050.2853935185</x:v>
@@ -14051,19 +14115,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="17" t="s">
-        <x:v>218</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D11" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="17" t="s">
-        <x:v>219</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F11" s="17" t="s">
-        <x:v>220</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G11" s="17" t="s">
-        <x:v>221</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="H11" s="19">
         <x:v>46066.1892939815</x:v>
@@ -14089,19 +14153,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="17" t="s">
-        <x:v>218</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D12" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="17" t="s">
-        <x:v>219</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F12" s="17" t="s">
-        <x:v>222</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G12" s="17" t="s">
-        <x:v>223</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H12" s="19">
         <x:v>46066.186087963</x:v>
@@ -14127,19 +14191,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D13" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="17" t="s">
-        <x:v>225</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F13" s="17" t="s">
-        <x:v>226</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G13" s="17" t="s">
-        <x:v>227</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H13" s="19">
         <x:v>46057.2800462963</x:v>
@@ -14165,19 +14229,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D14" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="17" t="s">
-        <x:v>225</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F14" s="17" t="s">
-        <x:v>228</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G14" s="17" t="s">
-        <x:v>229</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H14" s="19">
         <x:v>46057.272025463</x:v>
@@ -14203,19 +14267,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="17" t="s">
-        <x:v>224</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D15" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="17" t="s">
-        <x:v>230</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="F15" s="17" t="s">
-        <x:v>231</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G15" s="17" t="s">
-        <x:v>232</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H15" s="19">
         <x:v>46057.2657523148</x:v>
@@ -14241,19 +14305,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C16" s="17" t="s">
-        <x:v>233</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D16" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E16" s="17" t="s">
-        <x:v>234</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F16" s="17" t="s">
-        <x:v>235</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G16" s="17" t="s">
-        <x:v>236</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="H16" s="19">
         <x:v>46056.1690046296</x:v>
@@ -14279,19 +14343,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="17" t="s">
-        <x:v>237</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D17" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E17" s="17" t="s">
-        <x:v>238</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F17" s="17" t="s">
-        <x:v>239</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="G17" s="17" t="s">
-        <x:v>240</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="H17" s="19">
         <x:v>46065.2312962963</x:v>
@@ -14317,19 +14381,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C18" s="17" t="s">
-        <x:v>241</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D18" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="17" t="s">
-        <x:v>242</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F18" s="17" t="s">
-        <x:v>243</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G18" s="17" t="s">
-        <x:v>244</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H18" s="19">
         <x:v>46063.0357060185</x:v>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="378">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -95,6 +95,9 @@
     <x:t>61-7-2025-1080</x:t>
   </x:si>
   <x:si>
+    <x:t>1215838</x:t>
+  </x:si>
+  <x:si>
     <x:t>Catalina EBON</x:t>
   </x:si>
   <x:si>
@@ -107,6 +110,9 @@
     <x:t>61-7-2025-1074</x:t>
   </x:si>
   <x:si>
+    <x:t>1215833</x:t>
+  </x:si>
+  <x:si>
     <x:t>FB"GENIZA"/ ELIZA G. LLABAN</x:t>
   </x:si>
   <x:si>
@@ -119,6 +125,9 @@
     <x:t>61-7-2025-1073</x:t>
   </x:si>
   <x:si>
+    <x:t>1215836</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -152,6 +161,9 @@
     <x:t>61-8-2025-1102</x:t>
   </x:si>
   <x:si>
+    <x:t>1346451</x:t>
+  </x:si>
+  <x:si>
     <x:t>Neil Jon Angeles</x:t>
   </x:si>
   <x:si>
@@ -170,6 +182,9 @@
     <x:t>61-8-2025-1116</x:t>
   </x:si>
   <x:si>
+    <x:t>1195701</x:t>
+  </x:si>
+  <x:si>
     <x:t>Alexander Tomales</x:t>
   </x:si>
   <x:si>
@@ -188,6 +203,9 @@
     <x:t>61-8-2025-1109</x:t>
   </x:si>
   <x:si>
+    <x:t>1346453</x:t>
+  </x:si>
+  <x:si>
     <x:t>THUNDER BRAVO NETWORK, INC</x:t>
   </x:si>
   <x:si>
@@ -200,6 +218,9 @@
     <x:t>61-8-2025-1140</x:t>
   </x:si>
   <x:si>
+    <x:t>1346494</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radio Station License - WDN (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -215,6 +236,9 @@
     <x:t>61-8-2025-1114</x:t>
   </x:si>
   <x:si>
+    <x:t>1195693</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (MODIFICATION)</x:t>
   </x:si>
   <x:si>
@@ -233,6 +257,9 @@
     <x:t>61-8-2025-1087</x:t>
   </x:si>
   <x:si>
+    <x:t>1346441</x:t>
+  </x:si>
+  <x:si>
     <x:t>RAWDA SHIPPING CORPORATION</x:t>
   </x:si>
   <x:si>
@@ -245,6 +272,9 @@
     <x:t>61-8-2025-1090</x:t>
   </x:si>
   <x:si>
+    <x:t>1346447</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (NEW) (WITHOUT originally-installed equipment)</x:t>
   </x:si>
   <x:si>
@@ -260,6 +290,9 @@
     <x:t>61-8-2025-1121</x:t>
   </x:si>
   <x:si>
+    <x:t>1346466</x:t>
+  </x:si>
+  <x:si>
     <x:t>ADELUISA S. VISANDE</x:t>
   </x:si>
   <x:si>
@@ -272,6 +305,9 @@
     <x:t>61-8-2025-1131</x:t>
   </x:si>
   <x:si>
+    <x:t>1215872</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARY BONSIL</x:t>
   </x:si>
   <x:si>
@@ -284,6 +320,9 @@
     <x:t>61-8-2025-1089</x:t>
   </x:si>
   <x:si>
+    <x:t>1346446</x:t>
+  </x:si>
+  <x:si>
     <x:t>HELEN A. DIANA</x:t>
   </x:si>
   <x:si>
@@ -296,6 +335,9 @@
     <x:t>61-8-2025-1137</x:t>
   </x:si>
   <x:si>
+    <x:t>1215865</x:t>
+  </x:si>
+  <x:si>
     <x:t>LLQ SEA TRANSPORT / LUCIA LAO QUE</x:t>
   </x:si>
   <x:si>
@@ -308,6 +350,9 @@
     <x:t>61-8-2025-1122</x:t>
   </x:si>
   <x:si>
+    <x:t>1346468</x:t>
+  </x:si>
+  <x:si>
     <x:t>LORNA Y. BALONGCAS</x:t>
   </x:si>
   <x:si>
@@ -320,6 +365,9 @@
     <x:t>61-8-2025-1107</x:t>
   </x:si>
   <x:si>
+    <x:t>1215863</x:t>
+  </x:si>
+  <x:si>
     <x:t>RAMIL S. VISANDE</x:t>
   </x:si>
   <x:si>
@@ -329,6 +377,9 @@
     <x:t>61-8-2025-1129</x:t>
   </x:si>
   <x:si>
+    <x:t>1215870</x:t>
+  </x:si>
+  <x:si>
     <x:t>SOUTHWEST PACIFIC SHIPPING LINES</x:t>
   </x:si>
   <x:si>
@@ -341,6 +392,9 @@
     <x:t>61-8-2025-1113</x:t>
   </x:si>
   <x:si>
+    <x:t>1346470</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | September 2025</x:t>
   </x:si>
   <x:si>
@@ -359,6 +413,9 @@
     <x:t>61-8-2025-1119</x:t>
   </x:si>
   <x:si>
+    <x:t>1346465</x:t>
+  </x:si>
+  <x:si>
     <x:t>PETRON CORPORATION - ZAMBOANGA TERMINAL</x:t>
   </x:si>
   <x:si>
@@ -386,6 +443,9 @@
     <x:t>61-9-2025-1148</x:t>
   </x:si>
   <x:si>
+    <x:t>1215888</x:t>
+  </x:si>
+  <x:si>
     <x:t>FB NOELIZA-1</x:t>
   </x:si>
   <x:si>
@@ -398,6 +458,9 @@
     <x:t>61-9-2025-1160</x:t>
   </x:si>
   <x:si>
+    <x:t>1215908</x:t>
+  </x:si>
+  <x:si>
     <x:t>RICO E. ACAIN</x:t>
   </x:si>
   <x:si>
@@ -410,6 +473,9 @@
     <x:t>61-8-2025-1133</x:t>
   </x:si>
   <x:si>
+    <x:t>1215874</x:t>
+  </x:si>
+  <x:si>
     <x:t>SOPHIA VALDEZ</x:t>
   </x:si>
   <x:si>
@@ -422,6 +488,9 @@
     <x:t>61-8-2025-1103</x:t>
   </x:si>
   <x:si>
+    <x:t>1346508</x:t>
+  </x:si>
+  <x:si>
     <x:t>VICENTE S. TORRES JR.</x:t>
   </x:si>
   <x:si>
@@ -434,6 +503,9 @@
     <x:t>61-9-2025-1174</x:t>
   </x:si>
   <x:si>
+    <x:t>1215911</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | October 2025</x:t>
   </x:si>
   <x:si>
@@ -449,6 +521,9 @@
     <x:t>61-10-2025-1196</x:t>
   </x:si>
   <x:si>
+    <x:t>1215960</x:t>
+  </x:si>
+  <x:si>
     <x:t>RHEINT JAY CENO</x:t>
   </x:si>
   <x:si>
@@ -458,6 +533,9 @@
     <x:t>MS9/FV-1346-24(MOD.)</x:t>
   </x:si>
   <x:si>
+    <x:t>1215919</x:t>
+  </x:si>
+  <x:si>
     <x:t>RICHARD L. CENO</x:t>
   </x:si>
   <x:si>
@@ -467,6 +545,9 @@
     <x:t>61-9-2025-1151</x:t>
   </x:si>
   <x:si>
+    <x:t>1215920</x:t>
+  </x:si>
+  <x:si>
     <x:t>RICHARD L. CEÑO</x:t>
   </x:si>
   <x:si>
@@ -479,6 +560,9 @@
     <x:t>61-10-2025-1182</x:t>
   </x:si>
   <x:si>
+    <x:t>1215945</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | November 2025</x:t>
   </x:si>
   <x:si>
@@ -491,6 +575,9 @@
     <x:t>61-11-2025-1241</x:t>
   </x:si>
   <x:si>
+    <x:t>1216021</x:t>
+  </x:si>
+  <x:si>
     <x:t>FAITH D. LAURE</x:t>
   </x:si>
   <x:si>
@@ -503,6 +590,9 @@
     <x:t>61-11-2025-1223</x:t>
   </x:si>
   <x:si>
+    <x:t>1216001</x:t>
+  </x:si>
+  <x:si>
     <x:t>MERIE ANN R. BARROS</x:t>
   </x:si>
   <x:si>
@@ -515,6 +605,9 @@
     <x:t>61-11-2025-1232</x:t>
   </x:si>
   <x:si>
+    <x:t>1216006</x:t>
+  </x:si>
+  <x:si>
     <x:t>RENEWAL</x:t>
   </x:si>
   <x:si>
@@ -527,6 +620,9 @@
     <x:t>61-10-2025-1214</x:t>
   </x:si>
   <x:si>
+    <x:t>1215976</x:t>
+  </x:si>
+  <x:si>
     <x:t>RUEL B. BALILI</x:t>
   </x:si>
   <x:si>
@@ -539,6 +635,9 @@
     <x:t>61-10-2025-1207</x:t>
   </x:si>
   <x:si>
+    <x:t>1216013</x:t>
+  </x:si>
+  <x:si>
     <x:t>VENANCIO V. GALLARDO</x:t>
   </x:si>
   <x:si>
@@ -551,6 +650,9 @@
     <x:t>61-10-2025-1204</x:t>
   </x:si>
   <x:si>
+    <x:t>1215996</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | December 2025</x:t>
   </x:si>
   <x:si>
@@ -566,6 +668,9 @@
     <x:t>61-12-2025-1259-416</x:t>
   </x:si>
   <x:si>
+    <x:t>1216048</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRESENCIO C. JUSAY</x:t>
   </x:si>
   <x:si>
@@ -578,6 +683,9 @@
     <x:t>61-12-2025-1258-218</x:t>
   </x:si>
   <x:si>
+    <x:t>1216037</x:t>
+  </x:si>
+  <x:si>
     <x:t>FREDDIE ALIVIO</x:t>
   </x:si>
   <x:si>
@@ -590,6 +698,9 @@
     <x:t>61-11-2025-1234</x:t>
   </x:si>
   <x:si>
+    <x:t>1216033</x:t>
+  </x:si>
+  <x:si>
     <x:t>MADELYN L. DAPITAN</x:t>
   </x:si>
   <x:si>
@@ -599,6 +710,9 @@
     <x:t>61-11-2025-1246-597</x:t>
   </x:si>
   <x:si>
+    <x:t>1216027</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | January 2026</x:t>
   </x:si>
   <x:si>
@@ -617,6 +731,9 @@
     <x:t>61-12-2025-1261-872</x:t>
   </x:si>
   <x:si>
+    <x:t>1195956</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fortunata Postigo</x:t>
   </x:si>
   <x:si>
@@ -629,6 +746,9 @@
     <x:t>61-12-2025-1260-990</x:t>
   </x:si>
   <x:si>
+    <x:t>1216069</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier 9</x:t>
   </x:si>
   <x:si>
@@ -644,6 +764,9 @@
     <x:t>61-1-2026-1272-159</x:t>
   </x:si>
   <x:si>
+    <x:t>1216081</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROVEL R. AMANIA SR.</x:t>
   </x:si>
   <x:si>
@@ -653,6 +776,9 @@
     <x:t>61-12-2025-1265-514</x:t>
   </x:si>
   <x:si>
+    <x:t>1216066</x:t>
+  </x:si>
+  <x:si>
     <x:t>SPAMPI/ANDROCLES A. PEPITO</x:t>
   </x:si>
   <x:si>
@@ -665,6 +791,9 @@
     <x:t>61-12-2025-1266-301</x:t>
   </x:si>
   <x:si>
+    <x:t>1216060</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | February 2026</x:t>
   </x:si>
   <x:si>
@@ -680,6 +809,9 @@
     <x:t>61-1-2026-1301-032</x:t>
   </x:si>
   <x:si>
+    <x:t>1216103</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANALZA Y. PALAPAR</x:t>
   </x:si>
   <x:si>
@@ -692,6 +824,9 @@
     <x:t>61-1-2026-1300-537</x:t>
   </x:si>
   <x:si>
+    <x:t>1216112</x:t>
+  </x:si>
+  <x:si>
     <x:t>DANVIL OCEAN FISHING/PETER JHON G. YANOC</x:t>
   </x:si>
   <x:si>
@@ -704,6 +839,9 @@
     <x:t>61-1-2026-1299-653</x:t>
   </x:si>
   <x:si>
+    <x:t>1216106</x:t>
+  </x:si>
+  <x:si>
     <x:t>FRANKLIN S. LABOR</x:t>
   </x:si>
   <x:si>
@@ -716,12 +854,18 @@
     <x:t>61-2-2026-1328-050</x:t>
   </x:si>
   <x:si>
+    <x:t>1216131</x:t>
+  </x:si>
+  <x:si>
     <x:t>MS9/FV-1152-21</x:t>
   </x:si>
   <x:si>
     <x:t>61-2-2026-1327-547</x:t>
   </x:si>
   <x:si>
+    <x:t>1216130</x:t>
+  </x:si>
+  <x:si>
     <x:t>NDC FISHING CORPORATION</x:t>
   </x:si>
   <x:si>
@@ -734,12 +878,18 @@
     <x:t>61-2-2026-1312-079</x:t>
   </x:si>
   <x:si>
+    <x:t>1216117</x:t>
+  </x:si>
+  <x:si>
     <x:t>MS9/FV-0860-18</x:t>
   </x:si>
   <x:si>
     <x:t>61-2-2026-1311-296</x:t>
   </x:si>
   <x:si>
+    <x:t>1216121</x:t>
+  </x:si>
+  <x:si>
     <x:t>Kamanggahan, Curvada, Tukuran, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -749,6 +899,9 @@
     <x:t>61-2-2026-1310-247</x:t>
   </x:si>
   <x:si>
+    <x:t>1216119</x:t>
+  </x:si>
+  <x:si>
     <x:t>REX M. ALBAÑO</x:t>
   </x:si>
   <x:si>
@@ -761,6 +914,9 @@
     <x:t>61-2-2026-1308-069</x:t>
   </x:si>
   <x:si>
+    <x:t>1216107</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROLANDO P. ORTEGA</x:t>
   </x:si>
   <x:si>
@@ -773,6 +929,10 @@
     <x:t>61-2-2026-1321-824</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">1216134
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>SERGIA D. LLABAN</x:t>
   </x:si>
   <x:si>
@@ -785,6 +945,9 @@
     <x:t>61-2-2026-1319-115</x:t>
   </x:si>
   <x:si>
+    <x:t>1216123</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
@@ -800,6 +963,9 @@
     <x:t>61-2-2026-1354-796</x:t>
   </x:si>
   <x:si>
+    <x:t>1216147</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -809,6 +975,9 @@
     <x:t>61-2-2026-1340-327</x:t>
   </x:si>
   <x:si>
+    <x:t>1216156</x:t>
+  </x:si>
+  <x:si>
     <x:t>FEY S. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -821,6 +990,9 @@
     <x:t>61-2-2026-1332-813</x:t>
   </x:si>
   <x:si>
+    <x:t>1216165</x:t>
+  </x:si>
+  <x:si>
     <x:t>JUDELYN B. AMANIA</x:t>
   </x:si>
   <x:si>
@@ -833,6 +1005,9 @@
     <x:t>61-2-2026-1331-064</x:t>
   </x:si>
   <x:si>
+    <x:t>1216138</x:t>
+  </x:si>
+  <x:si>
     <x:t>LUCERO R. ALBARACIN</x:t>
   </x:si>
   <x:si>
@@ -845,6 +1020,9 @@
     <x:t>61-2-2026-1352-743</x:t>
   </x:si>
   <x:si>
+    <x:t>1216146</x:t>
+  </x:si>
+  <x:si>
     <x:t>PRK. KAMANGGAHAN, CURVADA, Tukuran, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -854,6 +1032,9 @@
     <x:t>61-2-2026-1337-307</x:t>
   </x:si>
   <x:si>
+    <x:t>1216193</x:t>
+  </x:si>
+  <x:si>
     <x:t>REMEGIO T. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -866,6 +1047,9 @@
     <x:t>61-2-2026-1343-619</x:t>
   </x:si>
   <x:si>
+    <x:t>1216150</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -875,6 +1059,9 @@
     <x:t>61-2-2026-1364-213</x:t>
   </x:si>
   <x:si>
+    <x:t>1216158</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/a Prk.Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -884,6 +1071,9 @@
     <x:t>61-2-2026-1344-597</x:t>
   </x:si>
   <x:si>
+    <x:t>1216152</x:t>
+  </x:si>
+  <x:si>
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
   </x:si>
   <x:si>
@@ -896,6 +1086,9 @@
     <x:t>61-2-2026-1369-049</x:t>
   </x:si>
   <x:si>
+    <x:t>1216163</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -905,12 +1098,18 @@
     <x:t>61-2-2026-1367-348</x:t>
   </x:si>
   <x:si>
+    <x:t>1216161</x:t>
+  </x:si>
+  <x:si>
     <x:t>MS-4878-23</x:t>
   </x:si>
   <x:si>
     <x:t>61-2-2026-1362-288</x:t>
   </x:si>
   <x:si>
+    <x:t>1216154</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/a Prk.daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -920,6 +1119,9 @@
     <x:t>61-2-2026-1342-435</x:t>
   </x:si>
   <x:si>
+    <x:t>1216148</x:t>
+  </x:si>
+  <x:si>
     <x:t>REY S. BURBURAN</x:t>
   </x:si>
   <x:si>
@@ -929,6 +1131,9 @@
     <x:t>61-2-2026-1334-066</x:t>
   </x:si>
   <x:si>
+    <x:t>1216143</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A Prk Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -938,6 +1143,9 @@
     <x:t>61-2-2026-1333-303</x:t>
   </x:si>
   <x:si>
+    <x:t>1216142</x:t>
+  </x:si>
+  <x:si>
     <x:t>zone 9, tiguma, Pagadian City (Capital), Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -947,10 +1155,16 @@
     <x:t>61-2-2026-1372-847</x:t>
   </x:si>
   <x:si>
+    <x:t>1216174</x:t>
+  </x:si>
+  <x:si>
     <x:t>MS9/FV-1283-23</x:t>
   </x:si>
   <x:si>
     <x:t>61-11-2025-1252-294</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216173</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -962,7 +1176,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1024,13 +1238,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -1289,7 +1496,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1330,50 +1537,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1421,6 +1619,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1432,71 +1634,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1796,7 +1982,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>251</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -1875,37 +2061,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>253</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>254</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46076.1792361111</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46076.1792420602</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216147</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46090.2042708333</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46090.204281088</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1913,650 +2099,650 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>256</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>257</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46072.0333449074</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46072.0333546991</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216156</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46090.2584837963</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46090.2584930556</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46071.1677662037</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46071.1677711806</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1216165</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46091.1948842593</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46091.1948946528</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46070.1768402778</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46070.1768476389</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1216138</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46084.1495138889</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46084.1495253588</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46076.1139583333</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="E12" s="14" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46076.1139638194</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1216146</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46090.1919444444</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46090.1919488889</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
+      <x:c r="C13" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46071.3305671296</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="E13" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46071.3305731597</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1216193</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="J13" s="15" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46094.1906365741</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L13" s="18">
+        <x:v>46094.1906452199</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
+      <x:c r="C14" s="14" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46072.0792939815</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="E14" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46072.0792950116</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1216150</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="J14" s="15" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46090.220787037</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L14" s="18">
+        <x:v>46090.220792662</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
+      <x:c r="C15" s="14" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46077.2598726852</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="E15" s="14" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46077.2598841551</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1216158</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="J15" s="15" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46090.2758680556</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L15" s="18">
+        <x:v>46090.2758708681</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
+      <x:c r="C16" s="14" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46072.1089467593</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="E16" s="14" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46072.1089512963</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1216152</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
+      <x:c r="J16" s="15" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46090.2365046296</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L16" s="18">
+        <x:v>46090.2365117824</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
+      <x:c r="C17" s="14" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46077.5191782407</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="E17" s="14" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46077.5191885417</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1216163</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="J17" s="15" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46090.3154976852</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L17" s="18">
+        <x:v>46090.3155018056</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
+      <x:c r="C18" s="14" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46077.4722337963</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="E18" s="14" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46077.4722378472</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
         <x:v>46030</x:v>
       </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1216161</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="J18" s="15" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46090.2963078704</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L18" s="18">
+        <x:v>46090.2963156019</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
+      <x:c r="C19" s="14" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46077.2024189815</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="E19" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46077.2024189931</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
         <x:v>45948</x:v>
       </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1216154</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
+      <x:c r="J19" s="15" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46090.2495949074</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L19" s="18">
+        <x:v>46090.2496018056</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
+      <x:c r="C20" s="14" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46072.0497337963</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="E20" s="14" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46072.0497342708</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1216148</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
+      <x:c r="J20" s="15" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46090.2102430556</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L20" s="18">
+        <x:v>46090.2102464352</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
+      <x:c r="C21" s="14" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46071.2285416667</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
+      <x:c r="E21" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46071.2285509838</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1216143</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
+      <x:c r="J21" s="15" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46090.0772916667</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L21" s="18">
+        <x:v>46090.0772934491</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
+      <x:c r="C22" s="14" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46071.2072569444</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
+      <x:c r="E22" s="14" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46071.2072683796</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1216142</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
+      <x:c r="J22" s="15" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46090.0616666667</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L22" s="18">
+        <x:v>46090.0616673032</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
+      <x:c r="C23" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46079.0151851852</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
+      <x:c r="E23" s="14" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46079.0151889352</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
         <x:v>45602</x:v>
       </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1216174</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
+      <x:c r="J23" s="15" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46093.1514351852</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L23" s="18">
+        <x:v>46093.1514429977</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
+      <x:c r="C24" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>45988.1893402778</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
+      <x:c r="E24" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>45988.189350544</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
         <x:v>45973</x:v>
       </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1216173</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
+      <x:c r="J24" s="15" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46093.1383912037</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L24" s="18">
+        <x:v>46093.1383928935</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="24" t="s"/>
-      <x:c r="F27" s="24" t="s"/>
+      <x:c r="B27" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="s"/>
+      <x:c r="D27" s="20" t="s"/>
+      <x:c r="E27" s="21" t="s"/>
+      <x:c r="F27" s="21" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B28" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="28" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C30" s="32" t="s"/>
-      <x:c r="D30" s="32" t="s"/>
-      <x:c r="E30" s="32" t="s"/>
-      <x:c r="F30" s="33" t="n">
+      <x:c r="B30" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C30" s="29" t="s"/>
+      <x:c r="D30" s="29" t="s"/>
+      <x:c r="E30" s="29" t="s"/>
+      <x:c r="F30" s="30" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3725,7 +3911,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
@@ -3737,23 +3923,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45862.256875</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="H8" s="16">
+        <x:v>45862.2568792245</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45908</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215838</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45862.3066319444</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45862.3066347569</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -3763,116 +3949,116 @@
       <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45861.1595728241</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45862.1034618403</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45861.1595717593</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215833</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45862.1034606481</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45861.1361574074</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45861.1361588889</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1215836</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45862.1391203704</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45862.1391293403</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="24" t="s"/>
+      <x:c r="B13" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B14" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="28" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="30" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="32" t="s"/>
-      <x:c r="D16" s="32" t="s"/>
-      <x:c r="E16" s="32" t="s"/>
-      <x:c r="F16" s="33" t="n">
+      <x:c r="B16" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -4974,7 +5160,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -5050,681 +5236,681 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45877.1309490741</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45877.1309606481</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346451</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45877.1309514815</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45877.1309607176</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45877.1897222222</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45877.1897291782</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45882.0658894792</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45882.0658987847</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>2496</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45883.2549618287</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45881.0630940972</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45885</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>45881.0887125926</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45882.0658796296</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45882.0658912037</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1195701</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>2496</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45883.2549537037</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45881.0630902778</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>45885</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1346453</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="E11" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45897.2535684028</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45847</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>2490</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>45897.2982517014</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45881.3064282755</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45871</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>4275</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45897.0449253125</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45870.3069341667</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46186</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>45883.1603418287</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45874.1403126505</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46159</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>4230</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>45874.2281447685</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45883.1346279514</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>45883.1346371065</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>45883.1693142593</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>45887.5652509954</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45881.0887037037</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="L16" s="18">
+        <x:v>45896.2365416898</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45897.2535648148</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>45847</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1346494</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>2490</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45897.2982407407</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
+      <x:c r="E17" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>45873.2842121644</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>45544</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>45873.3539853356</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45881.3064236111</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
-        <x:v>45871</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1195693</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>4275</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45897.0449189815</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>45870.3069328704</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46186</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1346441</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45883.1603356482</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>45874.1403125</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46159</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1346447</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>4230</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>45874.2281365741</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>45883.1346180556</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>45883.1346296296</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1346466</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>2070</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>45883.1693055556</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
+      <x:c r="E18" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>45891.1735682407</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>45765</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>45898.0611189931</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
+      <x:c r="C19" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>45887.5652430556</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1215872</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>45896.2365393518</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
+      <x:c r="E19" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>45883.1535775463</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>45883.2560389931</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
+      <x:c r="C20" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>45873.2842013889</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>45544</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1346446</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>45873.3539814815</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
+      <x:c r="E20" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>45879.4885117361</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>45884.2776561458</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
+      <x:c r="C21" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>45891.1735648148</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>45765</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>45898.0611111111</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
+      <x:c r="E21" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>45887.559024537</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>45896.2379658681</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
+      <x:c r="C22" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>45883.1535763889</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1346468</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>4350</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>45883.2560300926</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>45879.4885069444</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1215863</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>45884.277650463</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>45887.5590162037</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1215870</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
+      <x:c r="E22" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>45881.2806375231</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>45892</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L21" s="21">
-        <x:v>45896.237962963</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>45881.2806365741</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>45892</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1346470</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>45883.2976041667</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>40</x:v>
+      <x:c r="L22" s="18">
+        <x:v>45883.297613287</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C25" s="23" t="s"/>
-      <x:c r="D25" s="23" t="s"/>
-      <x:c r="E25" s="24" t="s"/>
-      <x:c r="F25" s="24" t="s"/>
+      <x:c r="B25" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="s"/>
+      <x:c r="D25" s="20" t="s"/>
+      <x:c r="E25" s="21" t="s"/>
+      <x:c r="F25" s="21" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B26" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C26" s="23" t="s"/>
+      <x:c r="D26" s="23" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="28" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="30" t="n">
+      <x:c r="B27" s="25" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="28" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C28" s="29" t="s"/>
-      <x:c r="D28" s="29" t="s"/>
-      <x:c r="E28" s="29" t="s"/>
-      <x:c r="F28" s="30" t="n">
+      <x:c r="B28" s="25" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
+      <x:c r="B29" s="25" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="28" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C30" s="29" t="s"/>
-      <x:c r="D30" s="29" t="s"/>
-      <x:c r="E30" s="29" t="s"/>
-      <x:c r="F30" s="30" t="n">
+      <x:c r="B30" s="25" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="28" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C31" s="29" t="s"/>
-      <x:c r="D31" s="29" t="s"/>
-      <x:c r="E31" s="29" t="s"/>
-      <x:c r="F31" s="30" t="n">
+      <x:c r="B31" s="25" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="28" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
+      <x:c r="B32" s="25" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="28" t="s">
+      <x:c r="B33" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C33" s="29" t="s"/>
-      <x:c r="D33" s="29" t="s"/>
-      <x:c r="E33" s="29" t="s"/>
-      <x:c r="F33" s="30" t="n">
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C34" s="32" t="s"/>
-      <x:c r="D34" s="32" t="s"/>
-      <x:c r="E34" s="32" t="s"/>
-      <x:c r="F34" s="33" t="n">
+      <x:c r="B34" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -6814,7 +7000,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -6890,333 +7076,333 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>107</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45883.0291898148</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45883.0291937384</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45651</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346465</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>642</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45929.2261805556</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45929.2261818403</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45883.0965162037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45883.0965271296</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>2592.56</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45930.3001388889</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45930.3001440509</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45908.5003472222</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45908.5003548611</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45790</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1215888</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45911.952650463</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45911.9526579514</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45916.1691666667</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45916.1691749537</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1215908</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45929.1383449074</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45929.1383451968</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45888.154375</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="E12" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45888.1543781134</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1215874</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45902.050775463</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L12" s="18">
+        <x:v>45902.0507853472</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
+      <x:c r="C13" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>45877.1361111111</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="E13" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45877.1361117824</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
         <x:v>45909</x:v>
       </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1346508</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="J13" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45908.1453009259</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>40</x:v>
+      <x:c r="L13" s="18">
+        <x:v>45908.1453025926</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
+      <x:c r="C14" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>45924.1162962963</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="E14" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45924.1163046412</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1215911</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="J14" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L14" s="21">
-        <x:v>45930.063912037</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L14" s="18">
+        <x:v>45930.0639154051</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="24" t="s"/>
+      <x:c r="B17" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="s"/>
+      <x:c r="D17" s="20" t="s"/>
+      <x:c r="E17" s="21" t="s"/>
+      <x:c r="F17" s="21" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B18" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="B19" s="25" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
+      <x:c r="B20" s="25" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="28" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C21" s="29" t="s"/>
-      <x:c r="D21" s="29" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="30" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C22" s="32" t="s"/>
-      <x:c r="D22" s="32" t="s"/>
-      <x:c r="E22" s="32" t="s"/>
-      <x:c r="F22" s="33" t="n">
+      <x:c r="B22" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="30" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8314,7 +8500,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>134</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -8390,40 +8576,40 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>136</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45947.5768287037</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45947.5768402431</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>43437</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215960</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>17766</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45954.2191782407</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45954.219187662</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -8431,165 +8617,165 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>140</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>141</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="15">
-        <x:v>45925.0601967593</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="H9" s="16">
+        <x:v>45925.0602006481</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45922</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215919</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45933.3037152778</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45933.3037187384</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45912.3032407407</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45912.3032409491</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45879</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1215920</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>4710</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45933.3105324074</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45933.3105378819</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45931.5665277778</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45931.5665387384</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>46297</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1215945</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45940.1382060185</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45940.1382142824</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B15" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -9690,7 +9876,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>149</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -9769,37 +9955,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>151</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45974.6184490741</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45974.6184602778</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45682</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216021</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45986.0239236111</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45986.0239280787</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -9807,232 +9993,232 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>154</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>155</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45965.4411342593</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45965.4411408796</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216001</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45973.0179398148</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45973.017945463</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45971.2507291667</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45971.2507406366</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1216006</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>45975.0756134259</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45975.0756137384</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45958.3516898148</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45958.3516981366</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1215976</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45967.2412384259</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45967.2412429051</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>45954.2913425926</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="E12" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45954.2913455787</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1216013</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>45975.3213541667</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L12" s="18">
+        <x:v>45975.3213612153</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
+      <x:c r="C13" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>45953.3174884259</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="E13" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45953.3174921644</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1215996</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="J13" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>45971.2990162037</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L13" s="18">
+        <x:v>45971.2990240856</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="24" t="s"/>
+      <x:c r="B16" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B17" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
+      <x:c r="B19" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -11131,7 +11317,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>173</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -11207,40 +11393,40 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>175</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46000.4750694444</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46000.4750792361</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216048</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>744</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46013.2950462963</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46013.2950574421</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -11248,167 +11434,167 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>180</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46000.180775463</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46000.1807785301</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46006.2645138889</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46006.2645192361</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>45972.0386111111</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45972.0386162384</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1216033</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46006.0795717593</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46006.0795786111</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="H11" s="19">
-        <x:v>45980.2173958333</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="F11" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45980.2174048843</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45852</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1216027</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>45992.1151851852</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45992.1151937269</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="24" t="s"/>
+      <x:c r="B14" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B15" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="32" t="s"/>
-      <x:c r="D18" s="32" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="33" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12509,7 +12695,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>189</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -12585,38 +12771,38 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>190</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46007.2920138889</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46007.292037037</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1195956</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46007.2920235301</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46007.2920389699</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46044.2434953704</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46044.2435002662</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>195</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -12624,205 +12810,205 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>196</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46007.1341435185</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46007.1341463773</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216069</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46035.3042476852</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46035.3042477199</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46034.1687615741</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46034.1687700231</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1216081</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46044.263275463</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46044.2632803241</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46014.1352083333</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46014.1352096759</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1216066</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46035.0802662037</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>199</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46035.0802777199</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46014.4844097222</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="E12" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46014.4844165162</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1216060</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46031.0514583333</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>199</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46031.0514651852</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="24" t="s"/>
+      <x:c r="B15" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B16" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="B17" s="25" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="28" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C19" s="32" t="s"/>
-      <x:c r="D19" s="32" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="33" t="n">
+      <x:c r="B19" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -13922,7 +14108,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>211</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -13998,40 +14184,40 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>213</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>214</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46051.2691319444</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46051.2691550926</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216103</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46051.2691346181</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46051.2691569676</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46057.9587152778</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46057.9587264699</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -14039,433 +14225,433 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>217</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46051.1259722222</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46051.1259765394</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216112</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46062.966400463</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46062.9664110648</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46050.2853935185</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
+      <x:c r="E10" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46050.2853992708</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45945</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1216106</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46058.0440046296</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46058.044006875</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46066.1892939815</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E11" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46066.1893041088</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1216131</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46076.0521180556</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46076.0521240394</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46066.186087963</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="E12" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46066.1860957755</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1216130</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46076.0476273148</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46076.0476356713</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
+      <x:c r="C13" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46057.2800462963</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="E13" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46057.2800557755</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1216117</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="J13" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46065.2796412037</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L13" s="18">
+        <x:v>46065.279651412</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
+      <x:c r="C14" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46057.272025463</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
+      <x:c r="E14" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46057.2720317477</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1216121</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="J14" s="15" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46065.2951388889</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L14" s="18">
+        <x:v>46065.2951402431</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
+      <x:c r="C15" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46057.2657523148</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
+      <x:c r="E15" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46057.2657532407</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
         <x:v>46039</x:v>
       </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1216119</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="J15" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46065.285474537</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L15" s="18">
+        <x:v>46065.2854801042</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
+      <x:c r="C16" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46056.1690046296</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
+      <x:c r="E16" s="14" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46056.1690134606</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
         <x:v>45716</x:v>
       </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1216107</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
+      <x:c r="J16" s="15" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46058.1034490741</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
+      <x:c r="L16" s="18">
+        <x:v>46058.1034575694</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="33.597656" customHeight="1">
+      <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
+      <x:c r="C17" s="14" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46065.2312962963</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
+      <x:c r="E17" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46065.2313001968</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1216134</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="J17" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>2190</x:v>
       </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46076.0858333333</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L17" s="18">
+        <x:v>46076.0858435648</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
+      <x:c r="C18" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46063.0357060185</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
+      <x:c r="E18" s="14" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46063.0357172222</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1216123</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="J18" s="15" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46066.0203819444</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L18" s="18">
+        <x:v>46066.0203850694</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="24" t="s"/>
+      <x:c r="B21" s="19" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="s"/>
+      <x:c r="D21" s="20" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="21" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="s">
-        <x:v>31</x:v>
+      <x:c r="B22" s="22" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s"/>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="29" t="s"/>
-      <x:c r="F23" s="30" t="n">
+      <x:c r="B23" s="25" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="28" t="s">
+      <x:c r="B24" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="30" t="n">
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="31" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C25" s="32" t="s"/>
-      <x:c r="D25" s="32" t="s"/>
-      <x:c r="E25" s="32" t="s"/>
-      <x:c r="F25" s="33" t="n">
+      <x:c r="B25" s="28" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="30" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -2015,7 +2015,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2055,7 +2055,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -2094,7 +2094,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2132,7 +2132,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2170,7 +2170,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2208,7 +2208,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2246,7 +2246,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2284,7 +2284,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2322,7 +2322,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2360,7 +2360,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2398,7 +2398,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2436,7 +2436,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2474,7 +2474,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2512,7 +2512,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2550,7 +2550,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2588,7 +2588,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2626,7 +2626,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2664,7 +2664,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3863,7 +3863,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3903,7 +3903,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -3942,7 +3942,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3980,7 +3980,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5193,7 +5193,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -5233,7 +5233,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>37</x:v>
@@ -5272,7 +5272,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
@@ -5310,7 +5310,7 @@
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
@@ -5348,7 +5348,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
@@ -5386,7 +5386,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
@@ -5424,7 +5424,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
@@ -5462,7 +5462,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
@@ -5500,7 +5500,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>81</x:v>
       </x:c>
@@ -5538,7 +5538,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5576,7 +5576,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5614,7 +5614,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5652,7 +5652,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5690,7 +5690,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5728,7 +5728,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5766,7 +5766,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -7033,7 +7033,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -7073,7 +7073,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>122</x:v>
@@ -7112,7 +7112,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
@@ -7150,7 +7150,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -7188,7 +7188,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -7226,7 +7226,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -7264,7 +7264,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -7302,7 +7302,7 @@
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -8533,7 +8533,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -8573,7 +8573,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>69</x:v>
@@ -8612,7 +8612,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -8648,7 +8648,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -8686,7 +8686,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -9909,7 +9909,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -9949,7 +9949,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -9988,7 +9988,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -10026,7 +10026,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -10064,7 +10064,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -10102,7 +10102,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -10140,7 +10140,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11350,7 +11350,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -11390,7 +11390,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>122</x:v>
@@ -11429,7 +11429,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11467,7 +11467,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11505,7 +11505,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12728,7 +12728,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -12768,7 +12768,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>228</x:v>
@@ -12805,7 +12805,7 @@
         <x:v>234</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12843,7 +12843,7 @@
         <x:v>239</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12881,7 +12881,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12919,7 +12919,7 @@
         <x:v>239</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14141,7 +14141,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -14181,7 +14181,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>81</x:v>
@@ -14220,7 +14220,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14258,7 +14258,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14296,7 +14296,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14334,7 +14334,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14372,7 +14372,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14410,7 +14410,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14448,7 +14448,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14486,7 +14486,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14524,7 +14524,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="33.597656" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -14562,7 +14562,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="378">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -38,9 +38,6 @@
     <x:t>LICENSES SUMMARY</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | July 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -140,9 +137,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | August 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Amateur Radio Station License (NEW)</x:t>
   </x:si>
   <x:si>
@@ -395,9 +389,6 @@
     <x:t>1346470</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | September 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Amateur Radio Station License (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -506,9 +497,6 @@
     <x:t>1215911</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | October 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>JESSIE B. POLANCO</x:t>
   </x:si>
   <x:si>
@@ -563,9 +551,6 @@
     <x:t>1215945</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | November 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>DELFINA S. CORTINA &amp; MARCELINO G. CORTINA JR.</x:t>
   </x:si>
   <x:si>
@@ -653,9 +638,6 @@
     <x:t>1215996</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | December 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>EDILMAR VINCENT SAGUN ARAO</x:t>
   </x:si>
   <x:si>
@@ -713,9 +695,6 @@
     <x:t>1216027</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | January 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>Certified True Copy</x:t>
   </x:si>
   <x:si>
@@ -792,9 +771,6 @@
   </x:si>
   <x:si>
     <x:t>1216060</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IX | February 2026</x:t>
   </x:si>
   <x:si>
     <x:t>MAT ANDREO A. DE LARA</x:t>
@@ -946,9 +922,6 @@
   </x:si>
   <x:si>
     <x:t>1216123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>AL S. BURBURAN</x:t>
@@ -1496,7 +1469,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1511,6 +1484,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1571,7 +1547,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1607,6 +1583,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1981,20 +1961,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2017,732 +1997,732 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46076.1792420602</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46090.204281088</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46072.0333546991</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46090.2584930556</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46076.1792420602</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="H10" s="17">
+        <x:v>46071.1677711806</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J10" s="16" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46090.204281088</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="L10" s="19">
+        <x:v>46091.1948946528</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46072.0333546991</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="G11" s="15" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46070.1768476389</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46084.1495253588</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46076.1139638194</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46090.1919488889</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46071.3305731597</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46094.1906452199</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46072.0792950116</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="J14" s="16" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46090.2584930556</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46071.1677711806</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="L14" s="19">
+        <x:v>46090.220792662</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46077.2598841551</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="J15" s="16" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46091.1948946528</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46070.1768476389</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46084.1495253588</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="L15" s="19">
+        <x:v>46090.2758708681</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="D16" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46072.1089512963</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46090.2365117824</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46077.5191885417</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46090.3155018056</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46077.4722378472</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46090.2963156019</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46076.1139638194</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46084</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46090.1919488889</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46071.3305731597</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46094.1906452199</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46072.0792950116</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
+      <x:c r="F19" s="15" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46077.2024189931</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46090.2496018056</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46072.0497342708</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="J20" s="16" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46090.220792662</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>339</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46077.2598841551</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
+      <x:c r="L20" s="19">
+        <x:v>46090.2102464352</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46071.2285509838</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="J21" s="16" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46090.2758708681</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46072.1089512963</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
+      <x:c r="L21" s="19">
+        <x:v>46090.0772934491</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46071.2072683796</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>346</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="J22" s="16" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46090.2365117824</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46077.5191885417</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="L22" s="19">
+        <x:v>46090.0616673032</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46079.0151889352</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>45602</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46093.1514429977</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>45988.189350544</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46090.3155018056</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46077.4722378472</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46090.2963156019</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46077.2024189931</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>45948</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46090.2496018056</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46072.0497342708</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46090.2102464352</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46071.2285509838</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>366</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46090.0772934491</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>367</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>369</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46071.2072683796</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46058</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>370</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46090.0616673032</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>371</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>372</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46079.0151889352</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>45602</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>374</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3990</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46093.1514429977</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>45988.189350544</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>45973</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>377</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
+      <x:c r="L24" s="19">
         <x:v>46093.1383928935</x:v>
       </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M24" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="19" t="s">
+      <x:c r="B27" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C27" s="21" t="s"/>
+      <x:c r="D27" s="21" t="s"/>
+      <x:c r="E27" s="22" t="s"/>
+      <x:c r="F27" s="22" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C27" s="20" t="s"/>
-      <x:c r="D27" s="20" t="s"/>
-      <x:c r="E27" s="21" t="s"/>
-      <x:c r="F27" s="21" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="22" t="s">
+      <x:c r="C28" s="24" t="s"/>
+      <x:c r="D28" s="24" t="s"/>
+      <x:c r="E28" s="24" t="s"/>
+      <x:c r="F28" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C28" s="23" t="s"/>
-      <x:c r="D28" s="23" t="s"/>
-      <x:c r="E28" s="23" t="s"/>
-      <x:c r="F28" s="24" t="s">
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B30" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C30" s="29" t="s"/>
-      <x:c r="D30" s="29" t="s"/>
-      <x:c r="E30" s="29" t="s"/>
-      <x:c r="F30" s="30" t="n">
+      <x:c r="C30" s="30" t="s"/>
+      <x:c r="D30" s="30" t="s"/>
+      <x:c r="E30" s="30" t="s"/>
+      <x:c r="F30" s="31" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3829,20 +3809,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3865,200 +3845,200 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45862.2568792245</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45908</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45862.2568792245</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45908</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45862.3066347569</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>45861.1595728241</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45862.3066347569</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="L9" s="19">
+        <x:v>45862.1034618403</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45861.1595728241</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45862.1034618403</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="E10" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45861.1361588889</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45861.1361588889</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45862.1391293403</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
+      <x:c r="B13" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -5159,20 +5139,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5195,722 +5175,722 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45877.1309514815</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45877.1309607176</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45877.1897291782</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45877.1309514815</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45877.1309607176</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45877.1897291782</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="C9" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45882.0658894792</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45882.0658987847</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>2496</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45883.2549618287</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45882.0658894792</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45882.0658987847</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>2496</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45883.2549618287</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45881.0630940972</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45885</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45881.0887125926</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45881.0630940972</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45885</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="F11" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45897.2535684028</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45847</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>2490</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45897.2982517014</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45881.3064282755</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45871</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>4275</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45897.0449253125</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>45870.3069341667</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46186</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45883.1603418287</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>45874.1403126505</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46159</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>4230</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>45874.2281447685</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>45883.1346279514</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>45883.1346371065</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>45883.1693142593</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>45887.5652509954</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45881.0887125926</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45897.2535684028</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45847</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>2490</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45897.2982517014</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45881.3064282755</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45871</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>4275</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45897.0449253125</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45870.3069341667</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46186</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>45883.1603418287</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45874.1403126505</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46159</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>4230</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>45874.2281447685</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45883.1346279514</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>45883.1346371065</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
+      <x:c r="L16" s="19">
+        <x:v>45896.2365416898</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>45873.2842121644</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>45544</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>45873.3539853356</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>45891.1735682407</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>45765</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>45898.0611189931</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>45883.1535775463</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>4350</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>45883.2560389931</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>45879.4885117361</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>45884.2776561458</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>2070</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>45883.1693142593</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>45887.5652509954</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>45896.2365416898</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>45873.2842121644</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>45544</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>45873.3539853356</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>45891.1735682407</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>45765</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>45898.0611189931</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>45883.1535775463</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>4350</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>45883.2560389931</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>45879.4885117361</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
+      <x:c r="F21" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>45887.559024537</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>45884.2776561458</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="J21" s="16" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="K21" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>45896.2379658681</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H21" s="16">
-        <x:v>45887.559024537</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
+      <x:c r="D22" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="F22" s="15" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>45881.2806375231</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>45892</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L21" s="18">
-        <x:v>45896.2379658681</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>45881.2806375231</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>45892</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
+      <x:c r="L22" s="19">
         <x:v>45883.297613287</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>44</x:v>
+      <x:c r="M22" s="15" t="s">
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="19" t="s">
+      <x:c r="B25" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C25" s="21" t="s"/>
+      <x:c r="D25" s="21" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="22" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C25" s="20" t="s"/>
-      <x:c r="D25" s="20" t="s"/>
-      <x:c r="E25" s="21" t="s"/>
-      <x:c r="F25" s="21" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="22" t="s">
+      <x:c r="C26" s="24" t="s"/>
+      <x:c r="D26" s="24" t="s"/>
+      <x:c r="E26" s="24" t="s"/>
+      <x:c r="F26" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C26" s="23" t="s"/>
-      <x:c r="D26" s="23" t="s"/>
-      <x:c r="E26" s="23" t="s"/>
-      <x:c r="F26" s="24" t="s">
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="26" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B34" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C27" s="26" t="s"/>
-      <x:c r="D27" s="26" t="s"/>
-      <x:c r="E27" s="26" t="s"/>
-      <x:c r="F27" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="25" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C30" s="26" t="s"/>
-      <x:c r="D30" s="26" t="s"/>
-      <x:c r="E30" s="26" t="s"/>
-      <x:c r="F30" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="25" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C32" s="26" t="s"/>
-      <x:c r="D32" s="26" t="s"/>
-      <x:c r="E32" s="26" t="s"/>
-      <x:c r="F32" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C33" s="26" t="s"/>
-      <x:c r="D33" s="26" t="s"/>
-      <x:c r="E33" s="26" t="s"/>
-      <x:c r="F33" s="27" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C34" s="29" t="s"/>
-      <x:c r="D34" s="29" t="s"/>
-      <x:c r="E34" s="29" t="s"/>
-      <x:c r="F34" s="30" t="n">
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -6999,20 +6979,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45901</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -7035,374 +7015,374 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45883.0291937384</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45651</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45929.2261818403</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45883.0291937384</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45651</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45929.2261818403</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45883.0965271296</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>2592.56</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45930.3001440509</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45883.0965271296</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>2592.56</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45930.3001440509</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45908.5003548611</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45790</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45911.9526579514</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45908.5003548611</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45790</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="G11" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45916.1691749537</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45949</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45929.1383451968</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45888.1543781134</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45911.9526579514</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45916.1691749537</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45949</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45929.1383451968</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="L12" s="19">
+        <x:v>45902.0507853472</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45888.1543781134</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45870</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45902.0507853472</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="H13" s="17">
+        <x:v>45877.1361117824</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45909</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="K13" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45908.1453025926</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45877.1361117824</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45909</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
+      <x:c r="F14" s="15" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>45908.1453025926</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="H14" s="17">
+        <x:v>45924.1163046412</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45902</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45924.1163046412</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45902</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="19">
         <x:v>45930.0639154051</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="19" t="s">
+      <x:c r="B17" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="22" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C17" s="20" t="s"/>
-      <x:c r="D17" s="20" t="s"/>
-      <x:c r="E17" s="21" t="s"/>
-      <x:c r="F17" s="21" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="22" t="s">
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="23" t="s"/>
-      <x:c r="F18" s="24" t="s">
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="30" t="n">
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8499,20 +8479,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45931</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8535,247 +8515,247 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>45947.5768402431</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>43437</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>17766</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45954.219187662</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45947.5768402431</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>43437</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="G9" s="15" t="s"/>
+      <x:c r="H9" s="17">
+        <x:v>45925.0602006481</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45922</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>17766</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45954.219187662</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45933.3037187384</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="16">
-        <x:v>45925.0602006481</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45922</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45912.3032409491</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45879</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
+        <x:v>4710</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45933.3105378819</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45931.5665387384</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45933.3037187384</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45912.3032409491</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45879</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>4710</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45933.3105378819</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45931.5665387384</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45940.1382142824</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+      <x:c r="B14" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -9875,20 +9855,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45962</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9911,314 +9891,314 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>45974.6184602778</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45682</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45986.0239280787</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45974.6184602778</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45682</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45965.4411408796</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45974</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45986.0239280787</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45973.017945463</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45965.4411408796</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45974</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45971.2507406366</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45973.017945463</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="L10" s="19">
+        <x:v>45975.0756137384</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45971.2507406366</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45991</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="H11" s="17">
+        <x:v>45958.3516981366</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
+        <x:v>3990</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45967.2412429051</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45954.2913455787</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45975.0756137384</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45958.3516981366</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3990</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45967.2412429051</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="L12" s="19">
+        <x:v>45975.3213612153</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45954.2913455787</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="H13" s="17">
+        <x:v>45953.3174921644</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45911</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45975.3213612153</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45953.3174921644</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45911</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>45971.2990240856</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
+      <x:c r="B16" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -11316,20 +11296,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11352,249 +11332,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46000.4750792361</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46013.2950574421</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46000.1807785301</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46000.4750792361</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46006.2645192361</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46013.2950574421</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45972.0386162384</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46337</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46000.1807785301</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46006.0795786111</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46006.2645192361</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>45980.2174048843</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45852</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45972.0386162384</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46337</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46006.0795786111</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45980.2174048843</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45852</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45992.1151937269</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+      <x:c r="B14" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12694,20 +12674,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -12730,285 +12710,285 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46007.2920235301</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46007.2920389699</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46044.2435002662</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46007.1341463773</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46035.3042477199</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46007.2920235301</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46007.2920389699</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46044.2435002662</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>234</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>46034.1687700231</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45944</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46007.1341463773</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46044.2632803241</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46035.3042477199</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>239</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>46014.1352096759</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="K11" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46035.0802777199</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46034.1687700231</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45944</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46044.2632803241</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="H12" s="17">
+        <x:v>46014.4844165162</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45786</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46014.1352096759</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46035.0802777199</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46014.4844165162</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45786</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>46031.0514651852</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>239</x:v>
+      <x:c r="M12" s="15" t="s">
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="19" t="s">
+      <x:c r="B15" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="21" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="22" t="s">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s"/>
-      <x:c r="D19" s="29" t="s"/>
-      <x:c r="E19" s="29" t="s"/>
-      <x:c r="F19" s="30" t="n">
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -14107,20 +14087,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -14143,515 +14123,515 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46051.2691346181</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46051.2691569676</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46057.9587264699</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46051.1259765394</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46053</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46062.9664110648</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46051.2691346181</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46051.2691569676</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>2070</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46057.9587264699</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>46050.2853992708</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45945</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46058.044006875</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46051.1259765394</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="F11" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46066.1893041088</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45695</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46076.0521240394</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46066.1860957755</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45695</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46076.0476356713</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46057.2800557755</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46052</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46065.279651412</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46057.2720317477</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46045</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46065.2951402431</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46057.2657532407</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46039</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46065.2854801042</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46056.1690134606</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>45716</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46058.1034575694</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46065.2313001968</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="J17" s="16" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>2190</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46076.0858435648</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46063.0357172222</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46066</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46062.9664110648</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46050.2853992708</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45945</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46058.044006875</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46066.1893041088</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45695</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46076.0521240394</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46066.1860957755</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45695</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46076.0476356713</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46057.2800557755</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46052</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46065.279651412</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46057.2720317477</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46045</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46065.2951402431</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46057.2657532407</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46039</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46065.2854801042</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46056.1690134606</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>45716</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3630</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46058.1034575694</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46065.2313001968</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46053</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>2190</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46076.0858435648</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46063.0357172222</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46066</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
+      <x:c r="L18" s="19">
         <x:v>46066.0203850694</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M18" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="19" t="s">
+      <x:c r="B21" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C21" s="21" t="s"/>
+      <x:c r="D21" s="21" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="22" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C21" s="20" t="s"/>
-      <x:c r="D21" s="20" t="s"/>
-      <x:c r="E21" s="21" t="s"/>
-      <x:c r="F21" s="21" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="22" t="s">
+      <x:c r="C22" s="24" t="s"/>
+      <x:c r="D22" s="24" t="s"/>
+      <x:c r="E22" s="24" t="s"/>
+      <x:c r="F22" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C22" s="23" t="s"/>
-      <x:c r="D22" s="23" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="24" t="s">
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B25" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C25" s="29" t="s"/>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="30" t="n">
+      <x:c r="C25" s="30" t="s"/>
+      <x:c r="D25" s="30" t="s"/>
+      <x:c r="E25" s="30" t="s"/>
+      <x:c r="F25" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -15,6 +15,7 @@
     <x:sheet name="January 2026" sheetId="13" r:id="rId13"/>
     <x:sheet name="February 2026" sheetId="14" r:id="rId14"/>
     <x:sheet name="March 2026" sheetId="15" r:id="rId15"/>
+    <x:sheet name="April 2026" sheetId="16" r:id="rId16"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="379">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1138,6 +1139,36 @@
   </x:si>
   <x:si>
     <x:t>1216173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHRISTOPHER P. RODA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Kahayag, Dumagoc, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0719-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1411-353</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBEN S. TAMULA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DISTRICT KAWASHI, POBLACION, Tabina, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1316-24(REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1394-597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216214</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3699,6 +3730,1299 @@
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="20" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B15" s="29" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="379">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="384">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1139,6 +1139,21 @@
   </x:si>
   <x:si>
     <x:t>1216173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEONILO V. MARTEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK SANTAN, BALANGASAN, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AT-II-91634-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1415-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216220</x:t>
   </x:si>
   <x:si>
     <x:t>CHRISTOPHER P. RODA</x:t>
@@ -3917,7 +3932,7 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="15" t="s">
-        <x:v>14</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
         <x:v>369</x:v>
@@ -3935,19 +3950,19 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46100.1333120023</x:v>
+        <x:v>46104.0644558912</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46115</x:v>
+        <x:v>45902</x:v>
       </x:c>
       <x:c r="J8" s="16" t="s">
         <x:v>373</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46120.3413710417</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
@@ -3973,10 +3988,10 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46093.1047457407</x:v>
+        <x:v>46100.1333120023</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46123</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="J9" s="16" t="s">
         <x:v>378</x:v>
@@ -3985,58 +4000,105 @@
         <x:v>1590</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46118.9999416204</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5014,15 +5076,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="384">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1169,6 +1169,21 @@
   </x:si>
   <x:si>
     <x:t>1216212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NOEMA M.MORGIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1 purok santan, bomba, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1022-19(MOD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1429-605</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216224</x:t>
   </x:si>
   <x:si>
     <x:t>RUBEN S. TAMULA</x:t>
@@ -4026,80 +4041,117 @@
         <x:v>382</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46093.1047457407</x:v>
+        <x:v>46107.098771794</x:v>
       </x:c>
       <x:c r="I10" s="17">
-        <x:v>46123</x:v>
+        <x:v>46161</x:v>
       </x:c>
       <x:c r="J10" s="16" t="s">
         <x:v>383</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46126.1382984606</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="20" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="26" t="s">
-        <x:v>14</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s"/>
       <x:c r="D16" s="27" t="s"/>
       <x:c r="E16" s="27" t="s"/>
       <x:c r="F16" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5081,11 +5133,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="407">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1156,6 +1156,42 @@
     <x:t>1216220</x:t>
   </x:si>
   <x:si>
+    <x:t>AMANUDIN U.BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1 purok santan, bomba, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1020-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1431-614</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1017-19(REN/MOD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1418-218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMANUDIN UNGAD BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1018-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1413-402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216223</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHRISTOPHER P. RODA</x:t>
   </x:si>
   <x:si>
@@ -1171,10 +1207,28 @@
     <x:t>1216212</x:t>
   </x:si>
   <x:si>
+    <x:t>NOEMA M.BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1019-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1430-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1016-19(DUP/REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1419-204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216226</x:t>
+  </x:si>
+  <x:si>
     <x:t>NOEMA M.MORGIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1 purok santan, bomba, Pagadian City (Capital), Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
     <x:t>MS9/FV-1022-19(MOD)</x:t>
@@ -4003,10 +4057,10 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46100.1333120023</x:v>
+        <x:v>46107.1169023495</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46115</x:v>
+        <x:v>46127</x:v>
       </x:c>
       <x:c r="J9" s="16" t="s">
         <x:v>378</x:v>
@@ -4015,7 +4069,7 @@
         <x:v>1590</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46126.1914953241</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>21</x:v>
@@ -4026,34 +4080,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>379</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="15" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="H10" s="17">
+        <x:v>46105.2495215509</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46107.098771794</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46161</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="s">
-        <x:v>383</x:v>
-      </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>1470</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46126.1382984606</x:v>
+        <x:v>46126.1951014005</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>21</x:v>
@@ -4064,99 +4118,284 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46102.5247719444</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>386</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>387</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46093.1047457407</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="s">
-        <x:v>388</x:v>
-      </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L11" s="19">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46126.1550669907</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46107.1054781366</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46126.1858600463</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46107.0809005093</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46126.1597197801</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46107.098771794</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46161</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46126.1382984606</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="20" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="22" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="23" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5133,11 +5372,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:F19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1264,7 +1264,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1304,14 +1304,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1584,7 +1576,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1595,16 +1587,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1616,53 +1605,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1697,87 +1686,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2079,17 +2064,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2112,732 +2097,732 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46076.1792420602</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46090.204281088</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46072.0333546991</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46090.2584930556</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46071.1677711806</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46091.1948946528</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46070.1768476389</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46084.1495253588</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46076.1139638194</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46090.1919488889</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46071.3305731597</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46094.1906452199</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46072.0792950116</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46090.220792662</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46077.2598841551</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46090.2758708681</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46072.1089512963</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46090.2365117824</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46077.5191885417</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46090.3155018056</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46077.4722378472</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46030</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46090.2963156019</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46077.2024189931</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>45948</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46090.2496018056</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46072.0497342708</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46090.2102464352</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>355</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>46071.2285509838</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>46090.0772934491</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>46071.2072683796</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>46090.0616673032</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="14" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
+      <x:c r="D23" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="E23" s="14" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="14" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="16">
         <x:v>46079.0151889352</x:v>
       </x:c>
-      <x:c r="I23" s="17">
+      <x:c r="I23" s="16">
         <x:v>45602</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="s">
+      <x:c r="J23" s="15" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="17" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="18">
         <x:v>46093.1514429977</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="14" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="14" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="14" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="16">
         <x:v>45988.189350544</x:v>
       </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="I24" s="16">
         <x:v>45973</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="s">
+      <x:c r="J24" s="15" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L24" s="19">
+      <x:c r="L24" s="18">
         <x:v>46093.1383928935</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="20" t="s">
+      <x:c r="B27" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C27" s="21" t="s"/>
-      <x:c r="D27" s="21" t="s"/>
-      <x:c r="E27" s="22" t="s"/>
-      <x:c r="F27" s="22" t="s"/>
+      <x:c r="C27" s="20" t="s"/>
+      <x:c r="D27" s="20" t="s"/>
+      <x:c r="E27" s="21" t="s"/>
+      <x:c r="F27" s="21" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="23" t="s">
+      <x:c r="B28" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C28" s="24" t="s"/>
-      <x:c r="D28" s="24" t="s"/>
-      <x:c r="E28" s="24" t="s"/>
-      <x:c r="F28" s="25" t="s">
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="29" t="s">
+      <x:c r="B30" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C30" s="30" t="s"/>
-      <x:c r="D30" s="30" t="s"/>
-      <x:c r="E30" s="30" t="s"/>
-      <x:c r="F30" s="31" t="n">
+      <x:c r="C30" s="29" t="s"/>
+      <x:c r="D30" s="29" t="s"/>
+      <x:c r="E30" s="29" t="s"/>
+      <x:c r="F30" s="30" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -3927,17 +3912,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3960,439 +3945,439 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46104.0644558912</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>798</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46120.3413710417</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46107.1169023495</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46126.1914953241</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46105.2495215509</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46126.1951014005</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46102.5247719444</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46126.1550669907</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46100.1333120023</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46118.9999416204</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46107.1054781366</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46126.1858600463</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46107.0809005093</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46126.1597197801</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46107.098771794</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46161</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>401</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46126.1382984606</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>402</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46093.1047457407</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46119.1181697338</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="20" t="s">
+      <x:c r="B19" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="22" t="s"/>
+      <x:c r="C19" s="20" t="s"/>
+      <x:c r="D19" s="20" t="s"/>
+      <x:c r="E19" s="21" t="s"/>
+      <x:c r="F19" s="21" t="s"/>
     </x:row>
     <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="23" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="s">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
+      <x:c r="B23" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -5490,17 +5475,17 @@
       <x:c r="B5" s="12">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5523,200 +5508,200 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45862.2568792245</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45908</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45862.3066347569</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45861.1595728241</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46238</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45862.1034618403</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45861.1361588889</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>7950</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45862.1391293403</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -6820,17 +6805,17 @@
       <x:c r="B5" s="12">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6853,722 +6838,722 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45877.1309514815</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45877.1309607176</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45877.1897291782</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45882.0658894792</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45882.0658987847</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>2496</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45883.2549618287</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45881.0630940972</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45885</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45881.0887125926</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45897.2535684028</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45847</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>2490</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45897.2982517014</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45881.3064282755</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45871</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>4275</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45897.0449253125</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45870.3069341667</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46186</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45883.1603418287</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45874.1403126505</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46159</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>4230</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45874.2281447685</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>45883.1346279514</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>45883.1346371065</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>45883.1693142593</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>45887.5652509954</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>45896.2365416898</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>45873.2842121644</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>45544</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>45873.3539853356</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>45891.1735682407</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>45765</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>45898.0611189931</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>45883.1535775463</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>4350</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>45883.2560389931</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>45879.4885117361</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>1650</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>45884.2776561458</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>45887.559024537</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>45896.2379658681</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>45881.2806375231</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>45892</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>45883.297613287</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="20" t="s">
+      <x:c r="B25" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C25" s="21" t="s"/>
-      <x:c r="D25" s="21" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="22" t="s"/>
+      <x:c r="C25" s="20" t="s"/>
+      <x:c r="D25" s="20" t="s"/>
+      <x:c r="E25" s="21" t="s"/>
+      <x:c r="F25" s="21" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="23" t="s">
+      <x:c r="B26" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C26" s="24" t="s"/>
-      <x:c r="D26" s="24" t="s"/>
-      <x:c r="E26" s="24" t="s"/>
-      <x:c r="F26" s="25" t="s">
+      <x:c r="C26" s="23" t="s"/>
+      <x:c r="D26" s="23" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
+      <x:c r="B27" s="25" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
+      <x:c r="B28" s="25" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+      <x:c r="B30" s="25" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
+      <x:c r="B31" s="25" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
+      <x:c r="B32" s="25" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
+      <x:c r="B33" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="29" t="s">
+      <x:c r="B34" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C34" s="30" t="s"/>
-      <x:c r="D34" s="30" t="s"/>
-      <x:c r="E34" s="30" t="s"/>
-      <x:c r="F34" s="31" t="n">
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -8660,17 +8645,17 @@
       <x:c r="B5" s="12">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8693,374 +8678,374 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45883.0291937384</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45651</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>642</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45929.2261818403</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45883.0965271296</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>2592.56</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45930.3001440509</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45908.5003548611</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45790</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45911.9526579514</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45916.1691749537</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45929.1383451968</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45888.1543781134</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45902.0507853472</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45877.1361117824</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45909</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45908.1453025926</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45924.1163046412</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45930.0639154051</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
+      <x:c r="B17" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
+      <x:c r="C17" s="20" t="s"/>
+      <x:c r="D17" s="20" t="s"/>
+      <x:c r="E17" s="21" t="s"/>
+      <x:c r="F17" s="21" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="23" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="29" t="s">
+      <x:c r="B22" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="30" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -10160,17 +10145,17 @@
       <x:c r="B5" s="12">
         <x:v>45931</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -10193,247 +10178,247 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45947.5768402431</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>43437</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>17766</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45954.219187662</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s"/>
-      <x:c r="H9" s="17">
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="16">
         <x:v>45925.0602006481</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45922</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45933.3037187384</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45912.3032409491</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45879</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>4710</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45933.3105378819</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45931.5665387384</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46297</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45940.1382142824</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -11536,17 +11521,17 @@
       <x:c r="B5" s="12">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11569,314 +11554,314 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45974.6184602778</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45682</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45986.0239280787</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45965.4411408796</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45973.017945463</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45971.2507406366</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45975.0756137384</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45958.3516981366</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45967.2412429051</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45954.2913455787</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45975.3213612153</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45953.3174921644</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45971.2990240856</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="B16" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+      <x:c r="B19" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -12977,17 +12962,17 @@
       <x:c r="B5" s="12">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -13010,249 +12995,249 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46000.4750792361</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>744</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46013.2950574421</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46000.1807785301</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46006.2645192361</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45972.0386162384</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46006.0795786111</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45980.2174048843</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45852</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45992.1151937269</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -14355,17 +14340,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -14388,285 +14373,285 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46007.2920235301</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46007.2920389699</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46044.2435002662</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46007.1341463773</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46035.3042477199</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46034.1687700231</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45944</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46044.2632803241</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46014.1352096759</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46035.0802777199</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46014.4844165162</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46031.0514651852</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+      <x:c r="B15" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="21" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+      <x:c r="B19" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -15768,17 +15753,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -15801,515 +15786,515 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46051.2691346181</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46051.2691569676</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46057.9587264699</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46051.1259765394</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46062.9664110648</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46050.2853992708</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45945</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46058.044006875</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46066.1893041088</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46076.0521240394</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46066.1860957755</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45695</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46076.0476356713</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46057.2800557755</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46065.279651412</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46057.2720317477</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46065.2951402431</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46057.2657532407</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46039</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46065.2854801042</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46056.1690134606</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>45716</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46058.1034575694</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46065.2313001968</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>2190</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46076.0858435648</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46063.0357172222</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46066.0203850694</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="20" t="s">
+      <x:c r="B21" s="19" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C21" s="21" t="s"/>
-      <x:c r="D21" s="21" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="22" t="s"/>
+      <x:c r="C21" s="20" t="s"/>
+      <x:c r="D21" s="20" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="21" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="23" t="s">
+      <x:c r="B22" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C22" s="24" t="s"/>
-      <x:c r="D22" s="24" t="s"/>
-      <x:c r="E22" s="24" t="s"/>
-      <x:c r="F22" s="25" t="s">
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="B24" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="29" t="s">
+      <x:c r="B25" s="28" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C25" s="30" t="s"/>
-      <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="30" t="s"/>
-      <x:c r="F25" s="31" t="n">
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="30" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
